--- a/data-cleaning/verified/导入_2026年1号机C修.xlsx
+++ b/data-cleaning/verified/导入_2026年1号机C修.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F004-W001</t>
+          <t>1G-GGRQ-GQ-L002-F004-W</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
@@ -700,7 +700,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F005-W002</t>
+          <t>1G-GGRQ-GQ-L002-F005-W</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr"/>
@@ -784,7 +784,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F006-W003</t>
+          <t>1G-GGRQ-GQ-L002-F006-W</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
@@ -868,7 +868,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F007-W004</t>
+          <t>1G-GGRQ-GQ-L002-F007-W</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr"/>
@@ -952,7 +952,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F008-W005</t>
+          <t>1G-GGRQ-GQ-L002-F008-W</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F009-W006</t>
+          <t>1G-GGRQ-GQ-L002-F009-W</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr"/>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F010-W007</t>
+          <t>1G-GGRQ-GQ-L002-F010-W</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F014-W008</t>
+          <t>1G-GGRQ-GQ-L002-F014-W</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr"/>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F015-W009</t>
+          <t>1G-GGRQ-GQ-L002-F015-W</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F016-W010</t>
+          <t>1G-GGRQ-GQ-L002-F016-W</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr"/>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F017-W011</t>
+          <t>1G-GGRQ-GQ-L002-F017-W</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F018-W012</t>
+          <t>1G-GGRQ-GQ-L002-F018-W</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr"/>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F019-W013</t>
+          <t>1G-GGRQ-GQ-L002-F019-W</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F020-W014</t>
+          <t>1G-GGRQ-GQ-L002-F020-W</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr"/>
@@ -1792,7 +1792,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F021-W015</t>
+          <t>1G-GGRQ-GQ-L002-F021-W</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F022-W016</t>
+          <t>1G-GGRQ-GQ-L002-F022-W</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr"/>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F004-W017</t>
+          <t>1G-GGRQ-GQ-L031-F004-W</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr"/>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F005-W018</t>
+          <t>1G-GGRQ-GQ-L031-F005-W</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr"/>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F006-W019</t>
+          <t>1G-GGRQ-GQ-L031-F006-W</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F007-W020</t>
+          <t>1G-GGRQ-GQ-L031-F007-W</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr"/>
@@ -2296,7 +2296,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F008-W021</t>
+          <t>1G-GGRQ-GQ-L031-F008-W</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr"/>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F009-W022</t>
+          <t>1G-GGRQ-GQ-L031-F009-W</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr"/>
@@ -2464,7 +2464,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F010-W023</t>
+          <t>1G-GGRQ-GQ-L031-F010-W</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr"/>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F014-W024</t>
+          <t>1G-GGRQ-GQ-L031-F014-W</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr"/>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F015-W025</t>
+          <t>1G-GGRQ-GQ-L031-F015-W</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F016-W026</t>
+          <t>1G-GGRQ-GQ-L031-F016-W</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr"/>
@@ -2800,7 +2800,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F017-W027</t>
+          <t>1G-GGRQ-GQ-L031-F017-W</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr"/>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F018-W028</t>
+          <t>1G-GGRQ-GQ-L031-F018-W</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr"/>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F019-W029</t>
+          <t>1G-GGRQ-GQ-L031-F019-W</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F020-W030</t>
+          <t>1G-GGRQ-GQ-L031-F020-W</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr"/>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F021-W031</t>
+          <t>1G-GGRQ-GQ-L031-F021-W</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr"/>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F022-W032</t>
+          <t>1G-GGRQ-GQ-L031-F022-W</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr"/>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L001-F001-W033</t>
+          <t>1G-GGRQ-GQ-L001-F001-W</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F001-W034</t>
+          <t>1G-GGRQ-GQ-L002-F001-W</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L003-F001-W035</t>
+          <t>1G-GGRQ-GQ-L003-F001-W</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -3580,7 +3580,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L004-F001-W036</t>
+          <t>1G-GGRQ-GQ-L004-F001-W</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L005-F001-W037</t>
+          <t>1G-GGRQ-GQ-L005-F001-W</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L006-F001-W038</t>
+          <t>1G-GGRQ-GQ-L006-F001-W</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L007-F001-W039</t>
+          <t>1G-GGRQ-GQ-L007-F001-W</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L008-F001-W040</t>
+          <t>1G-GGRQ-GQ-L008-F001-W</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L009-F001-W041</t>
+          <t>1G-GGRQ-GQ-L009-F001-W</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L010-F001-W042</t>
+          <t>1G-GGRQ-GQ-L010-F001-W</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L011-F001-W043</t>
+          <t>1G-GGRQ-GQ-L011-F001-W</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L012-F001-W044</t>
+          <t>1G-GGRQ-GQ-L012-F001-W</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L013-F001-W045</t>
+          <t>1G-GGRQ-GQ-L013-F001-W</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L014-F001-W046</t>
+          <t>1G-GGRQ-GQ-L014-F001-W</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L015-F001-W047</t>
+          <t>1G-GGRQ-GQ-L015-F001-W</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L016-F001-W048</t>
+          <t>1G-GGRQ-GQ-L016-F001-W</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
@@ -4776,7 +4776,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L017-F001-W049</t>
+          <t>1G-GGRQ-GQ-L017-F001-W</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L018-F001-W050</t>
+          <t>1G-GGRQ-GQ-L018-F001-W</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L019-F001-W051</t>
+          <t>1G-GGRQ-GQ-L019-F001-W</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L020-F001-W052</t>
+          <t>1G-GGRQ-GQ-L020-F001-W</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
@@ -5144,7 +5144,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L021-F001-W053</t>
+          <t>1G-GGRQ-GQ-L021-F001-W</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L022-F001-W054</t>
+          <t>1G-GGRQ-GQ-L022-F001-W</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L023-F001-W055</t>
+          <t>1G-GGRQ-GQ-L023-F001-W</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -5420,7 +5420,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L024-F001-W056</t>
+          <t>1G-GGRQ-GQ-L024-F001-W</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L025-F001-W057</t>
+          <t>1G-GGRQ-GQ-L025-F001-W</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -5604,7 +5604,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L026-F001-W058</t>
+          <t>1G-GGRQ-GQ-L026-F001-W</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L028-F001-W059</t>
+          <t>1G-GGRQ-GQ-L028-F001-W</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L029-F001-W060</t>
+          <t>1G-GGRQ-GQ-L029-F001-W</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L030-F001-W061</t>
+          <t>1G-GGRQ-GQ-L030-F001-W</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -5972,7 +5972,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F001-W062</t>
+          <t>1G-GGRQ-GQ-L031-F001-W</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
@@ -6064,7 +6064,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L032-F001-W063</t>
+          <t>1G-GGRQ-GQ-L032-F001-W</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L001-F002-W064</t>
+          <t>1G-GGRQ-GQ-L001-F002-W</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L001-F003-W065</t>
+          <t>1G-GGRQ-GQ-L001-F003-W</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -6332,7 +6332,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F002-W066</t>
+          <t>1G-GGRQ-GQ-L002-F002-W</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
@@ -6420,7 +6420,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F003-W067</t>
+          <t>1G-GGRQ-GQ-L002-F003-W</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L003-F002-W068</t>
+          <t>1G-GGRQ-GQ-L003-F002-W</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
@@ -6596,7 +6596,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L003-F003-W069</t>
+          <t>1G-GGRQ-GQ-L003-F003-W</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -6684,7 +6684,7 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L004-F002-W070</t>
+          <t>1G-GGRQ-GQ-L004-F002-W</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
@@ -6772,7 +6772,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L004-F003-W071</t>
+          <t>1G-GGRQ-GQ-L004-F003-W</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -6864,7 +6864,7 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L005-F002-W072</t>
+          <t>1G-GGRQ-GQ-L005-F002-W</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
@@ -6956,7 +6956,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L005-F003-W073</t>
+          <t>1G-GGRQ-GQ-L005-F003-W</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -7044,7 +7044,7 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L006-F002-W074</t>
+          <t>1G-GGRQ-GQ-L006-F002-W</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
@@ -7132,7 +7132,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L006-F003-W075</t>
+          <t>1G-GGRQ-GQ-L006-F003-W</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -7220,7 +7220,7 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L007-F002-W076</t>
+          <t>1G-GGRQ-GQ-L007-F002-W</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
@@ -7308,7 +7308,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L007-F003-W077</t>
+          <t>1G-GGRQ-GQ-L007-F003-W</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -7396,7 +7396,7 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L008-F002-W078</t>
+          <t>1G-GGRQ-GQ-L008-F002-W</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
@@ -7484,7 +7484,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L008-F003-W079</t>
+          <t>1G-GGRQ-GQ-L008-F003-W</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -7572,7 +7572,7 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L009-F002-W080</t>
+          <t>1G-GGRQ-GQ-L009-F002-W</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
@@ -7660,7 +7660,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L009-F003-W081</t>
+          <t>1G-GGRQ-GQ-L009-F003-W</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -7748,7 +7748,7 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L010-F002-W082</t>
+          <t>1G-GGRQ-GQ-L010-F002-W</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
@@ -7840,7 +7840,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L010-F003-W083</t>
+          <t>1G-GGRQ-GQ-L010-F003-W</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L011-F002-W084</t>
+          <t>1G-GGRQ-GQ-L011-F002-W</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
@@ -8016,7 +8016,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L011-F003-W085</t>
+          <t>1G-GGRQ-GQ-L011-F003-W</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -8104,7 +8104,7 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L012-F002-W086</t>
+          <t>1G-GGRQ-GQ-L012-F002-W</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
@@ -8192,7 +8192,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L012-F003-W087</t>
+          <t>1G-GGRQ-GQ-L012-F003-W</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -8280,7 +8280,7 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L013-F002-W088</t>
+          <t>1G-GGRQ-GQ-L013-F002-W</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
@@ -8372,7 +8372,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L013-F003-W089</t>
+          <t>1G-GGRQ-GQ-L013-F003-W</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -8460,7 +8460,7 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L014-F002-W090</t>
+          <t>1G-GGRQ-GQ-L014-F002-W</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
@@ -8548,7 +8548,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L014-F003-W091</t>
+          <t>1G-GGRQ-GQ-L014-F003-W</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -8636,7 +8636,7 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L015-F002-W092</t>
+          <t>1G-GGRQ-GQ-L015-F002-W</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
@@ -8724,7 +8724,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L015-F003-W093</t>
+          <t>1G-GGRQ-GQ-L015-F003-W</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -8812,7 +8812,7 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L016-F002-W094</t>
+          <t>1G-GGRQ-GQ-L016-F002-W</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
@@ -8900,7 +8900,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L016-F003-W095</t>
+          <t>1G-GGRQ-GQ-L016-F003-W</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -8988,7 +8988,7 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L017-F002-W096</t>
+          <t>1G-GGRQ-GQ-L017-F002-W</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
@@ -9076,7 +9076,7 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L017-F003-W097</t>
+          <t>1G-GGRQ-GQ-L017-F003-W</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -9164,7 +9164,7 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L018-F002-W098</t>
+          <t>1G-GGRQ-GQ-L018-F002-W</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
@@ -9252,7 +9252,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L018-F003-W099</t>
+          <t>1G-GGRQ-GQ-L018-F003-W</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -9340,7 +9340,7 @@
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L019-F002-W100</t>
+          <t>1G-GGRQ-GQ-L019-F002-W</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
@@ -9428,7 +9428,7 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L019-F003-W101</t>
+          <t>1G-GGRQ-GQ-L019-F003-W</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L020-F002-W102</t>
+          <t>1G-GGRQ-GQ-L020-F002-W</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L020-F003-W103</t>
+          <t>1G-GGRQ-GQ-L020-F003-W</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L021-F002-W104</t>
+          <t>1G-GGRQ-GQ-L021-F002-W</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
@@ -9780,7 +9780,7 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L021-F003-W105</t>
+          <t>1G-GGRQ-GQ-L021-F003-W</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -9868,7 +9868,7 @@
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L022-F002-W106</t>
+          <t>1G-GGRQ-GQ-L022-F002-W</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
@@ -9956,7 +9956,7 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L022-F003-W107</t>
+          <t>1G-GGRQ-GQ-L022-F003-W</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L023-F002-W108</t>
+          <t>1G-GGRQ-GQ-L023-F002-W</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
@@ -10132,7 +10132,7 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L023-F003-W109</t>
+          <t>1G-GGRQ-GQ-L023-F003-W</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -10220,7 +10220,7 @@
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L024-F002-W110</t>
+          <t>1G-GGRQ-GQ-L024-F002-W</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L024-F003-W111</t>
+          <t>1G-GGRQ-GQ-L024-F003-W</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -10396,7 +10396,7 @@
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L025-F002-W112</t>
+          <t>1G-GGRQ-GQ-L025-F002-W</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L025-F003-W113</t>
+          <t>1G-GGRQ-GQ-L025-F003-W</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -10576,7 +10576,7 @@
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L026-F002-W114</t>
+          <t>1G-GGRQ-GQ-L026-F002-W</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L026-F003-W115</t>
+          <t>1G-GGRQ-GQ-L026-F003-W</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -10752,7 +10752,7 @@
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L027-F002-W116</t>
+          <t>1G-GGRQ-GQ-L027-F002-W</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
@@ -10840,7 +10840,7 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L027-F003-W117</t>
+          <t>1G-GGRQ-GQ-L027-F003-W</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -10928,7 +10928,7 @@
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L028-F002-W118</t>
+          <t>1G-GGRQ-GQ-L028-F002-W</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
@@ -11016,7 +11016,7 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L028-F003-W119</t>
+          <t>1G-GGRQ-GQ-L028-F003-W</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -11104,7 +11104,7 @@
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L029-F002-W120</t>
+          <t>1G-GGRQ-GQ-L029-F002-W</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
@@ -11192,7 +11192,7 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L029-F003-W121</t>
+          <t>1G-GGRQ-GQ-L029-F003-W</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -11280,7 +11280,7 @@
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L030-F002-W122</t>
+          <t>1G-GGRQ-GQ-L030-F002-W</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
@@ -11368,7 +11368,7 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L030-F003-W123</t>
+          <t>1G-GGRQ-GQ-L030-F003-W</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -11456,7 +11456,7 @@
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F002-W124</t>
+          <t>1G-GGRQ-GQ-L031-F002-W</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
@@ -11544,7 +11544,7 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F003-W125</t>
+          <t>1G-GGRQ-GQ-L031-F003-W</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -11632,7 +11632,7 @@
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L032-F002-W126</t>
+          <t>1G-GGRQ-GQ-L032-F002-W</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
@@ -11720,7 +11720,7 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L032-F003-W127</t>
+          <t>1G-GGRQ-GQ-L032-F003-W</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -11808,7 +11808,7 @@
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L001-B001-W128</t>
+          <t>1G-GGRQ-GQ-L001-B001-W</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
@@ -11896,7 +11896,7 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-B001-W129</t>
+          <t>1G-GGRQ-GQ-L002-B001-W</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -11984,7 +11984,7 @@
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L003-B001-W130</t>
+          <t>1G-GGRQ-GQ-L003-B001-W</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
@@ -12072,7 +12072,7 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L004-B001-W131</t>
+          <t>1G-GGRQ-GQ-L004-B001-W</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -12160,7 +12160,7 @@
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L005-B001-W132</t>
+          <t>1G-GGRQ-GQ-L005-B001-W</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
@@ -12248,7 +12248,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L006-B001-W133</t>
+          <t>1G-GGRQ-GQ-L006-B001-W</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -12336,7 +12336,7 @@
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L007-B001-W134</t>
+          <t>1G-GGRQ-GQ-L007-B001-W</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr">
@@ -12424,7 +12424,7 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L008-B001-W135</t>
+          <t>1G-GGRQ-GQ-L008-B001-W</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -12512,7 +12512,7 @@
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L009-B001-W136</t>
+          <t>1G-GGRQ-GQ-L009-B001-W</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr">
@@ -12600,7 +12600,7 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L010-B001-W137</t>
+          <t>1G-GGRQ-GQ-L010-B001-W</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
@@ -12688,7 +12688,7 @@
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L011-B001-W138</t>
+          <t>1G-GGRQ-GQ-L011-B001-W</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr">
@@ -12776,7 +12776,7 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L012-B001-W139</t>
+          <t>1G-GGRQ-GQ-L012-B001-W</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -12864,7 +12864,7 @@
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L013-B001-W140</t>
+          <t>1G-GGRQ-GQ-L013-B001-W</t>
         </is>
       </c>
       <c r="E141" s="4" t="inlineStr">
@@ -12952,7 +12952,7 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L014-B001-W141</t>
+          <t>1G-GGRQ-GQ-L014-B001-W</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
@@ -13040,7 +13040,7 @@
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L015-B001-W142</t>
+          <t>1G-GGRQ-GQ-L015-B001-W</t>
         </is>
       </c>
       <c r="E143" s="4" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L016-B001-W143</t>
+          <t>1G-GGRQ-GQ-L016-B001-W</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -13216,7 +13216,7 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L017-B001-W144</t>
+          <t>1G-GGRQ-GQ-L017-B001-W</t>
         </is>
       </c>
       <c r="E145" s="4" t="inlineStr">
@@ -13304,7 +13304,7 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L018-B001-W145</t>
+          <t>1G-GGRQ-GQ-L018-B001-W</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -13392,7 +13392,7 @@
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L019-B001-W146</t>
+          <t>1G-GGRQ-GQ-L019-B001-W</t>
         </is>
       </c>
       <c r="E147" s="4" t="inlineStr">
@@ -13480,7 +13480,7 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L020-B001-W147</t>
+          <t>1G-GGRQ-GQ-L020-B001-W</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
@@ -13568,7 +13568,7 @@
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L021-B001-W148</t>
+          <t>1G-GGRQ-GQ-L021-B001-W</t>
         </is>
       </c>
       <c r="E149" s="4" t="inlineStr">
@@ -13656,7 +13656,7 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L022-B001-W149</t>
+          <t>1G-GGRQ-GQ-L022-B001-W</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
@@ -13744,7 +13744,7 @@
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L023-B001-W150</t>
+          <t>1G-GGRQ-GQ-L023-B001-W</t>
         </is>
       </c>
       <c r="E151" s="4" t="inlineStr">
@@ -13832,7 +13832,7 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L024-B001-W151</t>
+          <t>1G-GGRQ-GQ-L024-B001-W</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
@@ -13920,7 +13920,7 @@
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L025-B001-W152</t>
+          <t>1G-GGRQ-GQ-L025-B001-W</t>
         </is>
       </c>
       <c r="E153" s="4" t="inlineStr">
@@ -14008,7 +14008,7 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L026-B001-W153</t>
+          <t>1G-GGRQ-GQ-L026-B001-W</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
@@ -14096,7 +14096,7 @@
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L027-B001-W154</t>
+          <t>1G-GGRQ-GQ-L027-B001-W</t>
         </is>
       </c>
       <c r="E155" s="4" t="inlineStr">
@@ -14184,7 +14184,7 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L028-B001-W155</t>
+          <t>1G-GGRQ-GQ-L028-B001-W</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
@@ -14272,7 +14272,7 @@
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L029-B001-W156</t>
+          <t>1G-GGRQ-GQ-L029-B001-W</t>
         </is>
       </c>
       <c r="E157" s="4" t="inlineStr">
@@ -14360,7 +14360,7 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L030-B001-W157</t>
+          <t>1G-GGRQ-GQ-L030-B001-W</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
@@ -14448,7 +14448,7 @@
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-B001-W158</t>
+          <t>1G-GGRQ-GQ-L031-B001-W</t>
         </is>
       </c>
       <c r="E159" s="4" t="inlineStr">
@@ -14536,7 +14536,7 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L032-B001-W159</t>
+          <t>1G-GGRQ-GQ-L032-B001-W</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">

--- a/data-cleaning/verified/导入_2026年1号机C修.xlsx
+++ b/data-cleaning/verified/导入_2026年1号机C修.xlsx
@@ -600,7 +600,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="145" customHeight="1">
+    <row r="2" ht="107" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -619,8 +619,16 @@
           <t>1G-GGRQ-GQ-L002-F004-W</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×8</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>SA-213TP304H</t>
+        </is>
+      </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr">
@@ -631,7 +639,7 @@
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#001；位置：L002-F004；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#001；位置：L002-F004；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F004=炉后第21弯头→304H</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -684,7 +692,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="145" customHeight="1">
+    <row r="3" ht="107" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -703,8 +711,16 @@
           <t>1G-GGRQ-GQ-L002-F005-W</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr"/>
-      <c r="F3" s="4" t="inlineStr"/>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G3" s="4" t="inlineStr"/>
       <c r="H3" s="4" t="inlineStr"/>
       <c r="I3" s="4" t="inlineStr">
@@ -715,7 +731,7 @@
       <c r="J3" s="4" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#002；位置：L002-F005；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#002；位置：L002-F005；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F005=炉后第20弯头→T91</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -768,7 +784,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="145" customHeight="1">
+    <row r="4" ht="107" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -787,8 +803,16 @@
           <t>1G-GGRQ-GQ-L002-F006-W</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
@@ -799,7 +823,7 @@
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#003；位置：L002-F006；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#003；位置：L002-F006；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F006=炉后第19弯头→T91</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -852,7 +876,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="145" customHeight="1">
+    <row r="5" ht="107" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -871,8 +895,16 @@
           <t>1G-GGRQ-GQ-L002-F007-W</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr"/>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G5" s="4" t="inlineStr"/>
       <c r="H5" s="4" t="inlineStr"/>
       <c r="I5" s="4" t="inlineStr">
@@ -883,7 +915,7 @@
       <c r="J5" s="4" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#004；位置：L002-F007；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#004；位置：L002-F007；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F007=炉后第18弯头→T91</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -936,7 +968,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="145" customHeight="1">
+    <row r="6" ht="107" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -955,8 +987,16 @@
           <t>1G-GGRQ-GQ-L002-F008-W</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr">
@@ -967,7 +1007,7 @@
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#005；位置：L002-F008；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#005；位置：L002-F008；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F008=炉后第17弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -1020,7 +1060,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="145" customHeight="1">
+    <row r="7" ht="107" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1039,8 +1079,16 @@
           <t>1G-GGRQ-GQ-L002-F009-W</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr"/>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G7" s="4" t="inlineStr"/>
       <c r="H7" s="4" t="inlineStr"/>
       <c r="I7" s="4" t="inlineStr">
@@ -1051,7 +1099,7 @@
       <c r="J7" s="4" t="inlineStr"/>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#006；位置：L002-F009；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#006；位置：L002-F009；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F009=炉后第16弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -1104,7 +1152,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="145" customHeight="1">
+    <row r="8" ht="107" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1123,8 +1171,16 @@
           <t>1G-GGRQ-GQ-L002-F010-W</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr">
@@ -1135,7 +1191,7 @@
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#007；位置：L002-F010；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#007；位置：L002-F010；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F010=炉后第15弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1188,7 +1244,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="145" customHeight="1">
+    <row r="9" ht="107" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1207,8 +1263,16 @@
           <t>1G-GGRQ-GQ-L002-F014-W</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr"/>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G9" s="4" t="inlineStr"/>
       <c r="H9" s="4" t="inlineStr"/>
       <c r="I9" s="4" t="inlineStr">
@@ -1219,7 +1283,7 @@
       <c r="J9" s="4" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#008；位置：L002-F014；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#008；位置：L002-F014；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F014=炉后第11弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -1272,7 +1336,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="145" customHeight="1">
+    <row r="10" ht="107" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1291,8 +1355,16 @@
           <t>1G-GGRQ-GQ-L002-F015-W</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr"/>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr">
@@ -1303,7 +1375,7 @@
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#009；位置：L002-F015；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#009；位置：L002-F015；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F015=炉后第10弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1356,7 +1428,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="145" customHeight="1">
+    <row r="11" ht="107" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1375,8 +1447,16 @@
           <t>1G-GGRQ-GQ-L002-F016-W</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr"/>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G11" s="4" t="inlineStr"/>
       <c r="H11" s="4" t="inlineStr"/>
       <c r="I11" s="4" t="inlineStr">
@@ -1387,7 +1467,7 @@
       <c r="J11" s="4" t="inlineStr"/>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#010；位置：L002-F016；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#010；位置：L002-F016；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F016=炉后第9弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -1440,7 +1520,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="145" customHeight="1">
+    <row r="12" ht="107" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1459,8 +1539,16 @@
           <t>1G-GGRQ-GQ-L002-F017-W</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="2" t="inlineStr"/>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr">
@@ -1471,7 +1559,7 @@
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#011；位置：L002-F017；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#011；位置：L002-F017；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F017=炉后第8弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1524,7 +1612,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="145" customHeight="1">
+    <row r="13" ht="107" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1543,8 +1631,16 @@
           <t>1G-GGRQ-GQ-L002-F018-W</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr"/>
-      <c r="F13" s="4" t="inlineStr"/>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G13" s="4" t="inlineStr"/>
       <c r="H13" s="4" t="inlineStr"/>
       <c r="I13" s="4" t="inlineStr">
@@ -1555,7 +1651,7 @@
       <c r="J13" s="4" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#012；位置：L002-F018；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#012；位置：L002-F018；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F018=炉后第7弯头→T91</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -1608,7 +1704,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="145" customHeight="1">
+    <row r="14" ht="107" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1627,8 +1723,16 @@
           <t>1G-GGRQ-GQ-L002-F019-W</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="2" t="inlineStr"/>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr">
@@ -1639,7 +1743,7 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#013；位置：L002-F019；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#013；位置：L002-F019；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F019=炉后第6弯头→T91</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1692,7 +1796,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="145" customHeight="1">
+    <row r="15" ht="107" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1711,8 +1815,16 @@
           <t>1G-GGRQ-GQ-L002-F020-W</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr"/>
-      <c r="F15" s="4" t="inlineStr"/>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G15" s="4" t="inlineStr"/>
       <c r="H15" s="4" t="inlineStr"/>
       <c r="I15" s="4" t="inlineStr">
@@ -1723,7 +1835,7 @@
       <c r="J15" s="4" t="inlineStr"/>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#014；位置：L002-F020；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#014；位置：L002-F020；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F020=炉后第5弯头→T91</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -1776,7 +1888,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="145" customHeight="1">
+    <row r="16" ht="107" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1795,8 +1907,16 @@
           <t>1G-GGRQ-GQ-L002-F021-W</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr"/>
-      <c r="F16" s="2" t="inlineStr"/>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×8</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>SA-213TP304H</t>
+        </is>
+      </c>
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr">
@@ -1807,7 +1927,7 @@
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#015；位置：L002-F021；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#015；位置：L002-F021；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F021=炉后第4弯头→304H</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -1860,7 +1980,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="145" customHeight="1">
+    <row r="17" ht="107" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1879,8 +1999,16 @@
           <t>1G-GGRQ-GQ-L002-F022-W</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr"/>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×8</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>SA-213TP304H</t>
+        </is>
+      </c>
       <c r="G17" s="4" t="inlineStr"/>
       <c r="H17" s="4" t="inlineStr"/>
       <c r="I17" s="4" t="inlineStr">
@@ -1891,7 +2019,7 @@
       <c r="J17" s="4" t="inlineStr"/>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#016；位置：L002-F022；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#016；位置：L002-F022；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F022=炉后第3弯头→304H</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -1944,7 +2072,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="145" customHeight="1">
+    <row r="18" ht="107" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1963,8 +2091,16 @@
           <t>1G-GGRQ-GQ-L031-F004-W</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr"/>
-      <c r="F18" s="2" t="inlineStr"/>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×8</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>SA-213TP304H</t>
+        </is>
+      </c>
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr">
@@ -1975,7 +2111,7 @@
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#001；位置：L031-F004；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#001；位置：L031-F004；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F004=炉后第21弯头→304H</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2028,7 +2164,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="145" customHeight="1">
+    <row r="19" ht="107" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2047,8 +2183,16 @@
           <t>1G-GGRQ-GQ-L031-F005-W</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr"/>
-      <c r="F19" s="4" t="inlineStr"/>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G19" s="4" t="inlineStr"/>
       <c r="H19" s="4" t="inlineStr"/>
       <c r="I19" s="4" t="inlineStr">
@@ -2059,7 +2203,7 @@
       <c r="J19" s="4" t="inlineStr"/>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#002；位置：L031-F005；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#002；位置：L031-F005；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F005=炉后第20弯头→T91</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -2112,7 +2256,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="145" customHeight="1">
+    <row r="20" ht="107" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2131,8 +2275,16 @@
           <t>1G-GGRQ-GQ-L031-F006-W</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr"/>
-      <c r="F20" s="2" t="inlineStr"/>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr">
@@ -2143,7 +2295,7 @@
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#003；位置：L031-F006；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#003；位置：L031-F006；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F006=炉后第19弯头→T91</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2196,7 +2348,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="145" customHeight="1">
+    <row r="21" ht="107" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2215,8 +2367,16 @@
           <t>1G-GGRQ-GQ-L031-F007-W</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr"/>
-      <c r="F21" s="4" t="inlineStr"/>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G21" s="4" t="inlineStr"/>
       <c r="H21" s="4" t="inlineStr"/>
       <c r="I21" s="4" t="inlineStr">
@@ -2227,7 +2387,7 @@
       <c r="J21" s="4" t="inlineStr"/>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#004；位置：L031-F007；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#004；位置：L031-F007；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F007=炉后第18弯头→T91</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
@@ -2280,7 +2440,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="145" customHeight="1">
+    <row r="22" ht="107" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2299,8 +2459,16 @@
           <t>1G-GGRQ-GQ-L031-F008-W</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr"/>
-      <c r="F22" s="2" t="inlineStr"/>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr">
@@ -2311,7 +2479,7 @@
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#005；位置：L031-F008；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#005；位置：L031-F008；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F008=炉后第17弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2364,7 +2532,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="145" customHeight="1">
+    <row r="23" ht="107" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2383,8 +2551,16 @@
           <t>1G-GGRQ-GQ-L031-F009-W</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr"/>
-      <c r="F23" s="4" t="inlineStr"/>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G23" s="4" t="inlineStr"/>
       <c r="H23" s="4" t="inlineStr"/>
       <c r="I23" s="4" t="inlineStr">
@@ -2395,7 +2571,7 @@
       <c r="J23" s="4" t="inlineStr"/>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#006；位置：L031-F009；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#006；位置：L031-F009；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F009=炉后第16弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
@@ -2448,7 +2624,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="145" customHeight="1">
+    <row r="24" ht="107" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2467,8 +2643,16 @@
           <t>1G-GGRQ-GQ-L031-F010-W</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr"/>
-      <c r="F24" s="2" t="inlineStr"/>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr">
@@ -2479,7 +2663,7 @@
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#007；位置：L031-F010；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#007；位置：L031-F010；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F010=炉后第15弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -2532,7 +2716,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="145" customHeight="1">
+    <row r="25" ht="107" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2551,8 +2735,16 @@
           <t>1G-GGRQ-GQ-L031-F014-W</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr"/>
-      <c r="F25" s="4" t="inlineStr"/>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G25" s="4" t="inlineStr"/>
       <c r="H25" s="4" t="inlineStr"/>
       <c r="I25" s="4" t="inlineStr">
@@ -2563,7 +2755,7 @@
       <c r="J25" s="4" t="inlineStr"/>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#008；位置：L031-F014；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#008；位置：L031-F014；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F014=炉后第11弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
@@ -2616,7 +2808,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="145" customHeight="1">
+    <row r="26" ht="107" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2635,8 +2827,16 @@
           <t>1G-GGRQ-GQ-L031-F015-W</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr"/>
-      <c r="F26" s="2" t="inlineStr"/>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr">
@@ -2647,7 +2847,7 @@
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#009；位置：L031-F015；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#009；位置：L031-F015；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F015=炉后第10弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -2700,7 +2900,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="145" customHeight="1">
+    <row r="27" ht="107" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2719,8 +2919,16 @@
           <t>1G-GGRQ-GQ-L031-F016-W</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr"/>
-      <c r="F27" s="4" t="inlineStr"/>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G27" s="4" t="inlineStr"/>
       <c r="H27" s="4" t="inlineStr"/>
       <c r="I27" s="4" t="inlineStr">
@@ -2731,7 +2939,7 @@
       <c r="J27" s="4" t="inlineStr"/>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#010；位置：L031-F016；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#010；位置：L031-F016；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F016=炉后第9弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
@@ -2784,7 +2992,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="145" customHeight="1">
+    <row r="28" ht="107" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2803,8 +3011,16 @@
           <t>1G-GGRQ-GQ-L031-F017-W</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr"/>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>12CrMoVG</t>
+        </is>
+      </c>
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr"/>
       <c r="I28" s="2" t="inlineStr">
@@ -2815,7 +3031,7 @@
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#011；位置：L031-F017；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#011；位置：L031-F017；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F017=炉后第8弯头→12CrMoVG</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -2868,7 +3084,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="145" customHeight="1">
+    <row r="29" ht="107" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2887,8 +3103,16 @@
           <t>1G-GGRQ-GQ-L031-F018-W</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr"/>
-      <c r="F29" s="4" t="inlineStr"/>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G29" s="4" t="inlineStr"/>
       <c r="H29" s="4" t="inlineStr"/>
       <c r="I29" s="4" t="inlineStr">
@@ -2899,7 +3123,7 @@
       <c r="J29" s="4" t="inlineStr"/>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#012；位置：L031-F018；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#012；位置：L031-F018；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F018=炉后第7弯头→T91</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
@@ -2952,7 +3176,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="145" customHeight="1">
+    <row r="30" ht="107" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2971,8 +3195,16 @@
           <t>1G-GGRQ-GQ-L031-F019-W</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr"/>
-      <c r="F30" s="2" t="inlineStr"/>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr">
@@ -2983,7 +3215,7 @@
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#013；位置：L031-F019；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#013；位置：L031-F019；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F019=炉后第6弯头→T91</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -3036,7 +3268,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="145" customHeight="1">
+    <row r="31" ht="107" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3055,8 +3287,16 @@
           <t>1G-GGRQ-GQ-L031-F020-W</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr"/>
-      <c r="F31" s="4" t="inlineStr"/>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×9</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
       <c r="G31" s="4" t="inlineStr"/>
       <c r="H31" s="4" t="inlineStr"/>
       <c r="I31" s="4" t="inlineStr">
@@ -3067,7 +3307,7 @@
       <c r="J31" s="4" t="inlineStr"/>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#014；位置：L031-F020；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#014；位置：L031-F020；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F020=炉后第5弯头→T91</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
@@ -3120,7 +3360,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="145" customHeight="1">
+    <row r="32" ht="107" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3139,8 +3379,16 @@
           <t>1G-GGRQ-GQ-L031-F021-W</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr"/>
-      <c r="F32" s="2" t="inlineStr"/>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Φ51×8</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>SA-213TP304H</t>
+        </is>
+      </c>
       <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr">
@@ -3151,7 +3399,7 @@
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#015；位置：L031-F021；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#015；位置：L031-F021；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F021=炉后第4弯头→304H</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -3204,7 +3452,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="145" customHeight="1">
+    <row r="33" ht="107" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3223,8 +3471,16 @@
           <t>1G-GGRQ-GQ-L031-F022-W</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr"/>
-      <c r="F33" s="4" t="inlineStr"/>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>Φ51×8</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>SA-213TP304H</t>
+        </is>
+      </c>
       <c r="G33" s="4" t="inlineStr"/>
       <c r="H33" s="4" t="inlineStr"/>
       <c r="I33" s="4" t="inlineStr">
@@ -3235,7 +3491,7 @@
       <c r="J33" s="4" t="inlineStr"/>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#016；位置：L031-F022；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；材质待确认；源候选：SA-213TP347H / SA-213TP304H / T91 / 12CrMoVG；规格待确认；源候选：Φ54×7.5 / Φ51×8 / Φ51×9；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；源备注物理弯头计数与F/B几何关系未确认，材质不按清单流水推断</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#016；位置：L031-F022；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F022=炉后第3弯头→304H</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
@@ -6179,7 +6435,7 @@
       <c r="J65" s="4" t="inlineStr"/>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#001；位置：L001-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#001；位置：L001-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
@@ -6267,7 +6523,7 @@
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#002；位置：L001-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#002；位置：L001-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
@@ -6355,7 +6611,7 @@
       <c r="J67" s="4" t="inlineStr"/>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#003；位置：L002-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#003；位置：L002-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L67" s="4" t="inlineStr">
@@ -6443,7 +6699,7 @@
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#004；位置：L002-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#004；位置：L002-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
@@ -6531,7 +6787,7 @@
       <c r="J69" s="4" t="inlineStr"/>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#005；位置：L003-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#005；位置：L003-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L69" s="4" t="inlineStr">
@@ -6619,7 +6875,7 @@
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#006；位置：L003-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#006；位置：L003-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
@@ -6707,7 +6963,7 @@
       <c r="J71" s="4" t="inlineStr"/>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#007；位置：L004-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#007；位置：L004-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
@@ -6756,7 +7012,7 @@
       </c>
       <c r="V71" s="4" t="inlineStr"/>
     </row>
-    <row r="72" ht="88" customHeight="1">
+    <row r="72" ht="107" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6795,7 +7051,7 @@
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#008；位置：L004-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：发现异物，割开检查为氧化皮；结果性质：异常观察；仅转录异常观察，未新增质量合格/不合格判定或处置闭环；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#008；位置：L004-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：发现异物，割开检查为氧化皮；结果性质：异常观察；仅转录异常观察，未新增质量合格/不合格判定或处置闭环；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
@@ -6848,7 +7104,7 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="88" customHeight="1">
+    <row r="73" ht="107" customHeight="1">
       <c r="A73" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6887,7 +7143,7 @@
       <c r="J73" s="4" t="inlineStr"/>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#009；位置：L005-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：发现异物，割开检查为氧化皮；结果性质：异常观察；仅转录异常观察，未新增质量合格/不合格判定或处置闭环；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#009；位置：L005-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：发现异物，割开检查为氧化皮；结果性质：异常观察；仅转录异常观察，未新增质量合格/不合格判定或处置闭环；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L73" s="4" t="inlineStr">
@@ -6979,7 +7235,7 @@
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#010；位置：L005-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#010；位置：L005-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
@@ -7067,7 +7323,7 @@
       <c r="J75" s="4" t="inlineStr"/>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#011；位置：L006-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#011；位置：L006-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L75" s="4" t="inlineStr">
@@ -7155,7 +7411,7 @@
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#012；位置：L006-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#012；位置：L006-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
@@ -7243,7 +7499,7 @@
       <c r="J77" s="4" t="inlineStr"/>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#013；位置：L007-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#013；位置：L007-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L77" s="4" t="inlineStr">
@@ -7331,7 +7587,7 @@
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#014；位置：L007-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#014；位置：L007-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
@@ -7419,7 +7675,7 @@
       <c r="J79" s="4" t="inlineStr"/>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#015；位置：L008-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#015；位置：L008-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L79" s="4" t="inlineStr">
@@ -7507,7 +7763,7 @@
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#016；位置：L008-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#016；位置：L008-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
@@ -7595,7 +7851,7 @@
       <c r="J81" s="4" t="inlineStr"/>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#017；位置：L009-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#017；位置：L009-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L81" s="4" t="inlineStr">
@@ -7683,7 +7939,7 @@
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#018；位置：L009-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#018；位置：L009-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
@@ -7732,7 +7988,7 @@
       </c>
       <c r="V82" s="2" t="inlineStr"/>
     </row>
-    <row r="83" ht="88" customHeight="1">
+    <row r="83" ht="107" customHeight="1">
       <c r="A83" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7771,7 +8027,7 @@
       <c r="J83" s="4" t="inlineStr"/>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#019；位置：L010-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：发现异物，割开检查为氧化皮；结果性质：异常观察；仅转录异常观察，未新增质量合格/不合格判定或处置闭环；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#019；位置：L010-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：发现异物，割开检查为氧化皮；结果性质：异常观察；仅转录异常观察，未新增质量合格/不合格判定或处置闭环；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L83" s="4" t="inlineStr">
@@ -7863,7 +8119,7 @@
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#020；位置：L010-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#020；位置：L010-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
@@ -7951,7 +8207,7 @@
       <c r="J85" s="4" t="inlineStr"/>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#021；位置：L011-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#021；位置：L011-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L85" s="4" t="inlineStr">
@@ -8039,7 +8295,7 @@
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#022；位置：L011-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#022；位置：L011-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
@@ -8127,7 +8383,7 @@
       <c r="J87" s="4" t="inlineStr"/>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#023；位置：L012-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#023；位置：L012-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L87" s="4" t="inlineStr">
@@ -8215,7 +8471,7 @@
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#024；位置：L012-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#024；位置：L012-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
@@ -8264,7 +8520,7 @@
       </c>
       <c r="V88" s="2" t="inlineStr"/>
     </row>
-    <row r="89" ht="88" customHeight="1">
+    <row r="89" ht="107" customHeight="1">
       <c r="A89" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8303,7 +8559,7 @@
       <c r="J89" s="4" t="inlineStr"/>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#025；位置：L013-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：发现异物，割开检查为氧化皮；结果性质：异常观察；仅转录异常观察，未新增质量合格/不合格判定或处置闭环；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#025；位置：L013-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：发现异物，割开检查为氧化皮；结果性质：异常观察；仅转录异常观察，未新增质量合格/不合格判定或处置闭环；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L89" s="4" t="inlineStr">
@@ -8395,7 +8651,7 @@
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#026；位置：L013-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#026；位置：L013-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
@@ -8483,7 +8739,7 @@
       <c r="J91" s="4" t="inlineStr"/>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#027；位置：L014-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#027；位置：L014-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L91" s="4" t="inlineStr">
@@ -8571,7 +8827,7 @@
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#028；位置：L014-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#028；位置：L014-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
@@ -8659,7 +8915,7 @@
       <c r="J93" s="4" t="inlineStr"/>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#029；位置：L015-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#029；位置：L015-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L93" s="4" t="inlineStr">
@@ -8747,7 +9003,7 @@
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#030；位置：L015-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#030；位置：L015-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
@@ -8835,7 +9091,7 @@
       <c r="J95" s="4" t="inlineStr"/>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#031；位置：L016-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#031；位置：L016-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L95" s="4" t="inlineStr">
@@ -8923,7 +9179,7 @@
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#032；位置：L016-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#032；位置：L016-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
@@ -9011,7 +9267,7 @@
       <c r="J97" s="4" t="inlineStr"/>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#033；位置：L017-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#033；位置：L017-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L97" s="4" t="inlineStr">
@@ -9099,7 +9355,7 @@
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#034；位置：L017-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#034；位置：L017-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
@@ -9187,7 +9443,7 @@
       <c r="J99" s="4" t="inlineStr"/>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#035；位置：L018-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#035；位置：L018-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L99" s="4" t="inlineStr">
@@ -9275,7 +9531,7 @@
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#036；位置：L018-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#036；位置：L018-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
@@ -9363,7 +9619,7 @@
       <c r="J101" s="4" t="inlineStr"/>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#037；位置：L019-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#037；位置：L019-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L101" s="4" t="inlineStr">
@@ -9451,7 +9707,7 @@
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#038；位置：L019-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#038；位置：L019-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
@@ -9539,7 +9795,7 @@
       <c r="J103" s="4" t="inlineStr"/>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#039；位置：L020-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#039；位置：L020-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L103" s="4" t="inlineStr">
@@ -9627,7 +9883,7 @@
       <c r="J104" s="2" t="inlineStr"/>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#040；位置：L020-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#040；位置：L020-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
@@ -9715,7 +9971,7 @@
       <c r="J105" s="4" t="inlineStr"/>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#041；位置：L021-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#041；位置：L021-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L105" s="4" t="inlineStr">
@@ -9803,7 +10059,7 @@
       <c r="J106" s="2" t="inlineStr"/>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#042；位置：L021-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#042；位置：L021-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L106" s="2" t="inlineStr">
@@ -9891,7 +10147,7 @@
       <c r="J107" s="4" t="inlineStr"/>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#043；位置：L022-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#043；位置：L022-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L107" s="4" t="inlineStr">
@@ -9979,7 +10235,7 @@
       <c r="J108" s="2" t="inlineStr"/>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#044；位置：L022-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#044；位置：L022-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L108" s="2" t="inlineStr">
@@ -10067,7 +10323,7 @@
       <c r="J109" s="4" t="inlineStr"/>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#045；位置：L023-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#045；位置：L023-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L109" s="4" t="inlineStr">
@@ -10155,7 +10411,7 @@
       <c r="J110" s="2" t="inlineStr"/>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#046；位置：L023-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#046；位置：L023-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L110" s="2" t="inlineStr">
@@ -10243,7 +10499,7 @@
       <c r="J111" s="4" t="inlineStr"/>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#047；位置：L024-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#047；位置：L024-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L111" s="4" t="inlineStr">
@@ -10331,7 +10587,7 @@
       <c r="J112" s="2" t="inlineStr"/>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#048；位置：L024-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#048；位置：L024-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L112" s="2" t="inlineStr">
@@ -10380,7 +10636,7 @@
       </c>
       <c r="V112" s="2" t="inlineStr"/>
     </row>
-    <row r="113" ht="88" customHeight="1">
+    <row r="113" ht="107" customHeight="1">
       <c r="A113" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10419,7 +10675,7 @@
       <c r="J113" s="4" t="inlineStr"/>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#049；位置：L025-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：发现异物，割开检查为氧化皮；结果性质：异常观察；仅转录异常观察，未新增质量合格/不合格判定或处置闭环；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#049；位置：L025-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：发现异物，割开检查为氧化皮；结果性质：异常观察；仅转录异常观察，未新增质量合格/不合格判定或处置闭环；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L113" s="4" t="inlineStr">
@@ -10511,7 +10767,7 @@
       <c r="J114" s="2" t="inlineStr"/>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#050；位置：L025-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#050；位置：L025-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L114" s="2" t="inlineStr">
@@ -10599,7 +10855,7 @@
       <c r="J115" s="4" t="inlineStr"/>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#051；位置：L026-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#051；位置：L026-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L115" s="4" t="inlineStr">
@@ -10687,7 +10943,7 @@
       <c r="J116" s="2" t="inlineStr"/>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#052；位置：L026-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#052；位置：L026-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L116" s="2" t="inlineStr">
@@ -10775,7 +11031,7 @@
       <c r="J117" s="4" t="inlineStr"/>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#053；位置：L027-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#053；位置：L027-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L117" s="4" t="inlineStr">
@@ -10863,7 +11119,7 @@
       <c r="J118" s="2" t="inlineStr"/>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#054；位置：L027-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#054；位置：L027-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L118" s="2" t="inlineStr">
@@ -10951,7 +11207,7 @@
       <c r="J119" s="4" t="inlineStr"/>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#055；位置：L028-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#055；位置：L028-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L119" s="4" t="inlineStr">
@@ -11039,7 +11295,7 @@
       <c r="J120" s="2" t="inlineStr"/>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#056；位置：L028-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#056；位置：L028-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L120" s="2" t="inlineStr">
@@ -11127,7 +11383,7 @@
       <c r="J121" s="4" t="inlineStr"/>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#057；位置：L029-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#057；位置：L029-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L121" s="4" t="inlineStr">
@@ -11215,7 +11471,7 @@
       <c r="J122" s="2" t="inlineStr"/>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#058；位置：L029-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#058；位置：L029-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L122" s="2" t="inlineStr">
@@ -11303,7 +11559,7 @@
       <c r="J123" s="4" t="inlineStr"/>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#059；位置：L030-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#059；位置：L030-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L123" s="4" t="inlineStr">
@@ -11391,7 +11647,7 @@
       <c r="J124" s="2" t="inlineStr"/>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#060；位置：L030-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#060；位置：L030-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L124" s="2" t="inlineStr">
@@ -11479,7 +11735,7 @@
       <c r="J125" s="4" t="inlineStr"/>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#061；位置：L031-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#061；位置：L031-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L125" s="4" t="inlineStr">
@@ -11567,7 +11823,7 @@
       <c r="J126" s="2" t="inlineStr"/>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#062；位置：L031-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#062；位置：L031-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L126" s="2" t="inlineStr">
@@ -11655,7 +11911,7 @@
       <c r="J127" s="4" t="inlineStr"/>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#063；位置：L032-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#063；位置：L032-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L127" s="4" t="inlineStr">
@@ -11743,7 +11999,7 @@
       <c r="J128" s="2" t="inlineStr"/>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#064；位置：L032-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#064；位置：L032-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L128" s="2" t="inlineStr">
@@ -11808,7 +12064,7 @@
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L001-B001-W</t>
+          <t>1G-GGRQ-GQ-L001-F024-W</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
@@ -11831,7 +12087,7 @@
       <c r="J129" s="4" t="inlineStr"/>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#001；位置：L001-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#001；位置：L001-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L129" s="4" t="inlineStr">
@@ -11896,7 +12152,7 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-B001-W</t>
+          <t>1G-GGRQ-GQ-L002-F024-W</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -11919,7 +12175,7 @@
       <c r="J130" s="2" t="inlineStr"/>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#002；位置：L002-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#002；位置：L002-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L130" s="2" t="inlineStr">
@@ -11984,7 +12240,7 @@
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L003-B001-W</t>
+          <t>1G-GGRQ-GQ-L003-F024-W</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
@@ -12007,7 +12263,7 @@
       <c r="J131" s="4" t="inlineStr"/>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#003；位置：L003-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#003；位置：L003-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L131" s="4" t="inlineStr">
@@ -12072,7 +12328,7 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L004-B001-W</t>
+          <t>1G-GGRQ-GQ-L004-F024-W</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -12095,7 +12351,7 @@
       <c r="J132" s="2" t="inlineStr"/>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#004；位置：L004-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#004；位置：L004-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L132" s="2" t="inlineStr">
@@ -12160,7 +12416,7 @@
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L005-B001-W</t>
+          <t>1G-GGRQ-GQ-L005-F024-W</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
@@ -12183,7 +12439,7 @@
       <c r="J133" s="4" t="inlineStr"/>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#005；位置：L005-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#005；位置：L005-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L133" s="4" t="inlineStr">
@@ -12248,7 +12504,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L006-B001-W</t>
+          <t>1G-GGRQ-GQ-L006-F024-W</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -12271,7 +12527,7 @@
       <c r="J134" s="2" t="inlineStr"/>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#006；位置：L006-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#006；位置：L006-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L134" s="2" t="inlineStr">
@@ -12336,7 +12592,7 @@
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L007-B001-W</t>
+          <t>1G-GGRQ-GQ-L007-F024-W</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr">
@@ -12359,7 +12615,7 @@
       <c r="J135" s="4" t="inlineStr"/>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#007；位置：L007-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#007；位置：L007-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L135" s="4" t="inlineStr">
@@ -12424,7 +12680,7 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L008-B001-W</t>
+          <t>1G-GGRQ-GQ-L008-F024-W</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -12447,7 +12703,7 @@
       <c r="J136" s="2" t="inlineStr"/>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#008；位置：L008-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#008；位置：L008-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L136" s="2" t="inlineStr">
@@ -12512,7 +12768,7 @@
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L009-B001-W</t>
+          <t>1G-GGRQ-GQ-L009-F024-W</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr">
@@ -12535,7 +12791,7 @@
       <c r="J137" s="4" t="inlineStr"/>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#009；位置：L009-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#009；位置：L009-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L137" s="4" t="inlineStr">
@@ -12600,7 +12856,7 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L010-B001-W</t>
+          <t>1G-GGRQ-GQ-L010-F024-W</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
@@ -12623,7 +12879,7 @@
       <c r="J138" s="2" t="inlineStr"/>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#010；位置：L010-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#010；位置：L010-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L138" s="2" t="inlineStr">
@@ -12688,7 +12944,7 @@
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L011-B001-W</t>
+          <t>1G-GGRQ-GQ-L011-F024-W</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr">
@@ -12711,7 +12967,7 @@
       <c r="J139" s="4" t="inlineStr"/>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#011；位置：L011-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#011；位置：L011-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L139" s="4" t="inlineStr">
@@ -12776,7 +13032,7 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L012-B001-W</t>
+          <t>1G-GGRQ-GQ-L012-F024-W</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -12799,7 +13055,7 @@
       <c r="J140" s="2" t="inlineStr"/>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#012；位置：L012-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#012；位置：L012-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L140" s="2" t="inlineStr">
@@ -12864,7 +13120,7 @@
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L013-B001-W</t>
+          <t>1G-GGRQ-GQ-L013-F024-W</t>
         </is>
       </c>
       <c r="E141" s="4" t="inlineStr">
@@ -12887,7 +13143,7 @@
       <c r="J141" s="4" t="inlineStr"/>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#013；位置：L013-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#013；位置：L013-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L141" s="4" t="inlineStr">
@@ -12952,7 +13208,7 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L014-B001-W</t>
+          <t>1G-GGRQ-GQ-L014-F024-W</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
@@ -12975,7 +13231,7 @@
       <c r="J142" s="2" t="inlineStr"/>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#014；位置：L014-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#014；位置：L014-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L142" s="2" t="inlineStr">
@@ -13040,7 +13296,7 @@
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L015-B001-W</t>
+          <t>1G-GGRQ-GQ-L015-F024-W</t>
         </is>
       </c>
       <c r="E143" s="4" t="inlineStr">
@@ -13063,7 +13319,7 @@
       <c r="J143" s="4" t="inlineStr"/>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#015；位置：L015-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#015；位置：L015-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L143" s="4" t="inlineStr">
@@ -13128,7 +13384,7 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L016-B001-W</t>
+          <t>1G-GGRQ-GQ-L016-F024-W</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -13151,7 +13407,7 @@
       <c r="J144" s="2" t="inlineStr"/>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#016；位置：L016-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#016；位置：L016-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L144" s="2" t="inlineStr">
@@ -13216,7 +13472,7 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L017-B001-W</t>
+          <t>1G-GGRQ-GQ-L017-F024-W</t>
         </is>
       </c>
       <c r="E145" s="4" t="inlineStr">
@@ -13239,7 +13495,7 @@
       <c r="J145" s="4" t="inlineStr"/>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#017；位置：L017-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#017；位置：L017-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L145" s="4" t="inlineStr">
@@ -13304,7 +13560,7 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L018-B001-W</t>
+          <t>1G-GGRQ-GQ-L018-F024-W</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -13327,7 +13583,7 @@
       <c r="J146" s="2" t="inlineStr"/>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#018；位置：L018-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#018；位置：L018-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L146" s="2" t="inlineStr">
@@ -13392,7 +13648,7 @@
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L019-B001-W</t>
+          <t>1G-GGRQ-GQ-L019-F024-W</t>
         </is>
       </c>
       <c r="E147" s="4" t="inlineStr">
@@ -13415,7 +13671,7 @@
       <c r="J147" s="4" t="inlineStr"/>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#019；位置：L019-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#019；位置：L019-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L147" s="4" t="inlineStr">
@@ -13480,7 +13736,7 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L020-B001-W</t>
+          <t>1G-GGRQ-GQ-L020-F024-W</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
@@ -13503,7 +13759,7 @@
       <c r="J148" s="2" t="inlineStr"/>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#020；位置：L020-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#020；位置：L020-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L148" s="2" t="inlineStr">
@@ -13568,7 +13824,7 @@
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L021-B001-W</t>
+          <t>1G-GGRQ-GQ-L021-F024-W</t>
         </is>
       </c>
       <c r="E149" s="4" t="inlineStr">
@@ -13591,7 +13847,7 @@
       <c r="J149" s="4" t="inlineStr"/>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#021；位置：L021-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#021；位置：L021-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L149" s="4" t="inlineStr">
@@ -13656,7 +13912,7 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L022-B001-W</t>
+          <t>1G-GGRQ-GQ-L022-F024-W</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
@@ -13679,7 +13935,7 @@
       <c r="J150" s="2" t="inlineStr"/>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#022；位置：L022-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#022；位置：L022-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L150" s="2" t="inlineStr">
@@ -13744,7 +14000,7 @@
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L023-B001-W</t>
+          <t>1G-GGRQ-GQ-L023-F024-W</t>
         </is>
       </c>
       <c r="E151" s="4" t="inlineStr">
@@ -13767,7 +14023,7 @@
       <c r="J151" s="4" t="inlineStr"/>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#023；位置：L023-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#023；位置：L023-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L151" s="4" t="inlineStr">
@@ -13832,7 +14088,7 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L024-B001-W</t>
+          <t>1G-GGRQ-GQ-L024-F024-W</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
@@ -13855,7 +14111,7 @@
       <c r="J152" s="2" t="inlineStr"/>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#024；位置：L024-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#024；位置：L024-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L152" s="2" t="inlineStr">
@@ -13920,7 +14176,7 @@
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L025-B001-W</t>
+          <t>1G-GGRQ-GQ-L025-F024-W</t>
         </is>
       </c>
       <c r="E153" s="4" t="inlineStr">
@@ -13943,7 +14199,7 @@
       <c r="J153" s="4" t="inlineStr"/>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#025；位置：L025-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#025；位置：L025-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L153" s="4" t="inlineStr">
@@ -14008,7 +14264,7 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L026-B001-W</t>
+          <t>1G-GGRQ-GQ-L026-F024-W</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
@@ -14031,7 +14287,7 @@
       <c r="J154" s="2" t="inlineStr"/>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#026；位置：L026-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#026；位置：L026-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L154" s="2" t="inlineStr">
@@ -14096,7 +14352,7 @@
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L027-B001-W</t>
+          <t>1G-GGRQ-GQ-L027-F024-W</t>
         </is>
       </c>
       <c r="E155" s="4" t="inlineStr">
@@ -14119,7 +14375,7 @@
       <c r="J155" s="4" t="inlineStr"/>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#027；位置：L027-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#027；位置：L027-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L155" s="4" t="inlineStr">
@@ -14184,7 +14440,7 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L028-B001-W</t>
+          <t>1G-GGRQ-GQ-L028-F024-W</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
@@ -14207,7 +14463,7 @@
       <c r="J156" s="2" t="inlineStr"/>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#028；位置：L028-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#028；位置：L028-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L156" s="2" t="inlineStr">
@@ -14272,7 +14528,7 @@
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L029-B001-W</t>
+          <t>1G-GGRQ-GQ-L029-F024-W</t>
         </is>
       </c>
       <c r="E157" s="4" t="inlineStr">
@@ -14295,7 +14551,7 @@
       <c r="J157" s="4" t="inlineStr"/>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#029；位置：L029-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#029；位置：L029-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L157" s="4" t="inlineStr">
@@ -14360,7 +14616,7 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L030-B001-W</t>
+          <t>1G-GGRQ-GQ-L030-F024-W</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
@@ -14383,7 +14639,7 @@
       <c r="J158" s="2" t="inlineStr"/>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#030；位置：L030-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#030；位置：L030-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L158" s="2" t="inlineStr">
@@ -14448,7 +14704,7 @@
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-B001-W</t>
+          <t>1G-GGRQ-GQ-L031-F024-W</t>
         </is>
       </c>
       <c r="E159" s="4" t="inlineStr">
@@ -14471,7 +14727,7 @@
       <c r="J159" s="4" t="inlineStr"/>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#031；位置：L031-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#031；位置：L031-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L159" s="4" t="inlineStr">
@@ -14536,7 +14792,7 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L032-B001-W</t>
+          <t>1G-GGRQ-GQ-L032-F024-W</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
@@ -14559,7 +14815,7 @@
       <c r="J160" s="2" t="inlineStr"/>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#032；位置：L032-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#032；位置：L032-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L160" s="2" t="inlineStr">

--- a/data-cleaning/verified/导入_2026年1号机C修.xlsx
+++ b/data-cleaning/verified/导入_2026年1号机C修.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'导入数据'!$A$1:$V$160</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'导入数据'!$A$1:$V$161</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'导入数据'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:V160"/>
+  <dimension ref="A1:V161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -600,7 +600,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="107" customHeight="1">
+    <row r="2" ht="126" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -611,7 +611,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -639,7 +639,7 @@
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#001；位置：L002-F004；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F004=炉后第21弯头→304H</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#001；位置：L002-F004；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F004=炉后第21弯头→SA-213TP304H</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T2" s="2" t="inlineStr">
@@ -692,7 +692,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="107" customHeight="1">
+    <row r="3" ht="126" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -703,7 +703,7 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -731,7 +731,7 @@
       <c r="J3" s="4" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#002；位置：L002-F005；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F005=炉后第20弯头→T91</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#002；位置：L002-F005；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F005=炉后第20弯头→T91</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="S3" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T3" s="4" t="inlineStr">
@@ -784,7 +784,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="107" customHeight="1">
+    <row r="4" ht="126" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -795,7 +795,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#003；位置：L002-F006；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F006=炉后第19弯头→T91</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#003；位置：L002-F006；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F006=炉后第19弯头→T91</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -876,7 +876,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="107" customHeight="1">
+    <row r="5" ht="126" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -887,7 +887,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -915,7 +915,7 @@
       <c r="J5" s="4" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#004；位置：L002-F007；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F007=炉后第18弯头→T91</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#004；位置：L002-F007；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F007=炉后第18弯头→T91</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="S5" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T5" s="4" t="inlineStr">
@@ -968,7 +968,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="107" customHeight="1">
+    <row r="6" ht="126" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -979,7 +979,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
@@ -1007,7 +1007,7 @@
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#005；位置：L002-F008；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F008=炉后第17弯头→12CrMoVG</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#005；位置：L002-F008；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F008=炉后第17弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
@@ -1060,7 +1060,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="107" customHeight="1">
+    <row r="7" ht="126" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr"/>
@@ -1099,7 +1099,7 @@
       <c r="J7" s="4" t="inlineStr"/>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#006；位置：L002-F009；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F009=炉后第16弯头→12CrMoVG</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#006；位置：L002-F009；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F009=炉后第16弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T7" s="4" t="inlineStr">
@@ -1152,7 +1152,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="107" customHeight="1">
+    <row r="8" ht="126" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
@@ -1191,7 +1191,7 @@
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#007；位置：L002-F010；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F010=炉后第15弯头→12CrMoVG</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#007；位置：L002-F010；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F010=炉后第15弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="107" customHeight="1">
+    <row r="9" ht="126" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr"/>
@@ -1283,7 +1283,7 @@
       <c r="J9" s="4" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#008；位置：L002-F014；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F014=炉后第11弯头→12CrMoVG</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#008；位置：L002-F014；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F014=炉后第11弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T9" s="4" t="inlineStr">
@@ -1336,7 +1336,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="107" customHeight="1">
+    <row r="10" ht="126" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
@@ -1375,7 +1375,7 @@
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#009；位置：L002-F015；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F015=炉后第10弯头→12CrMoVG</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#009；位置：L002-F015；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F015=炉后第10弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -1428,7 +1428,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="107" customHeight="1">
+    <row r="11" ht="126" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr"/>
@@ -1467,7 +1467,7 @@
       <c r="J11" s="4" t="inlineStr"/>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#010；位置：L002-F016；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F016=炉后第9弯头→12CrMoVG</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#010；位置：L002-F016；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F016=炉后第9弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T11" s="4" t="inlineStr">
@@ -1520,7 +1520,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="107" customHeight="1">
+    <row r="12" ht="126" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
@@ -1559,7 +1559,7 @@
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#011；位置：L002-F017；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F017=炉后第8弯头→12CrMoVG</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#011；位置：L002-F017；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F017=炉后第8弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="107" customHeight="1">
+    <row r="13" ht="126" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -1651,7 +1651,7 @@
       <c r="J13" s="4" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#012；位置：L002-F018；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F018=炉后第7弯头→T91</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#012；位置：L002-F018；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F018=炉后第7弯头→T91</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T13" s="4" t="inlineStr">
@@ -1704,7 +1704,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="107" customHeight="1">
+    <row r="14" ht="126" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1715,7 +1715,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1743,7 +1743,7 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#013；位置：L002-F019；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F019=炉后第6弯头→T91</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#013；位置：L002-F019；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F019=炉后第6弯头→T91</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1796,7 +1796,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="107" customHeight="1">
+    <row r="15" ht="126" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -1835,7 +1835,7 @@
       <c r="J15" s="4" t="inlineStr"/>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#014；位置：L002-F020；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F020=炉后第5弯头→T91</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#014；位置：L002-F020；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F020=炉后第5弯头→T91</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T15" s="4" t="inlineStr">
@@ -1888,7 +1888,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="107" customHeight="1">
+    <row r="16" ht="126" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1927,7 +1927,7 @@
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#015；位置：L002-F021；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F021=炉后第4弯头→304H</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#015；位置：L002-F021；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F021=炉后第4弯头→SA-213TP304H</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -1980,7 +1980,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="107" customHeight="1">
+    <row r="17" ht="126" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -2019,7 +2019,7 @@
       <c r="J17" s="4" t="inlineStr"/>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R4#016；位置：L002-F022；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F022=炉后第3弯头→304H</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#016；位置：L002-F022；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F022=炉后第3弯头→SA-213TP304H</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T17" s="4" t="inlineStr">
@@ -2072,7 +2072,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="107" customHeight="1">
+    <row r="18" ht="126" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2111,7 +2111,7 @@
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#001；位置：L031-F004；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F004=炉后第21弯头→304H</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#001；位置：L031-F004；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F004=炉后第21弯头→SA-213TP304H</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
@@ -2164,7 +2164,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="107" customHeight="1">
+    <row r="19" ht="126" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2175,7 +2175,7 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -2203,7 +2203,7 @@
       <c r="J19" s="4" t="inlineStr"/>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#002；位置：L031-F005；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F005=炉后第20弯头→T91</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#002；位置：L031-F005；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F005=炉后第20弯头→T91</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T19" s="4" t="inlineStr">
@@ -2256,7 +2256,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="107" customHeight="1">
+    <row r="20" ht="126" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -2295,7 +2295,7 @@
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#003；位置：L031-F006；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F006=炉后第19弯头→T91</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#003；位置：L031-F006；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F006=炉后第19弯头→T91</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2348,7 +2348,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="107" customHeight="1">
+    <row r="21" ht="126" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -2387,7 +2387,7 @@
       <c r="J21" s="4" t="inlineStr"/>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#004；位置：L031-F007；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F007=炉后第18弯头→T91</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#004；位置：L031-F007；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F007=炉后第18弯头→T91</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T21" s="4" t="inlineStr">
@@ -2440,7 +2440,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="107" customHeight="1">
+    <row r="22" ht="126" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
@@ -2479,7 +2479,7 @@
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#005；位置：L031-F008；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F008=炉后第17弯头→12CrMoVG</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#005；位置：L031-F008；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F008=炉后第17弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2513,7 +2513,7 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
@@ -2532,7 +2532,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="107" customHeight="1">
+    <row r="23" ht="126" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -2558,7 +2558,7 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr"/>
@@ -2571,7 +2571,7 @@
       <c r="J23" s="4" t="inlineStr"/>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#006；位置：L031-F009；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F009=炉后第16弯头→12CrMoVG</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#006；位置：L031-F009；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F009=炉后第16弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T23" s="4" t="inlineStr">
@@ -2624,7 +2624,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="107" customHeight="1">
+    <row r="24" ht="126" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
@@ -2663,7 +2663,7 @@
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#007；位置：L031-F010；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F010=炉后第15弯头→12CrMoVG</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#007；位置：L031-F010；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F010=炉后第15弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
@@ -2716,7 +2716,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="107" customHeight="1">
+    <row r="25" ht="126" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2727,7 +2727,7 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr"/>
@@ -2755,7 +2755,7 @@
       <c r="J25" s="4" t="inlineStr"/>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#008；位置：L031-F014；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F014=炉后第11弯头→12CrMoVG</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#008；位置：L031-F014；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F014=炉后第11弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
@@ -2789,7 +2789,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T25" s="4" t="inlineStr">
@@ -2808,7 +2808,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="107" customHeight="1">
+    <row r="26" ht="126" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
@@ -2847,7 +2847,7 @@
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#009；位置：L031-F015；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F015=炉后第10弯头→12CrMoVG</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#009；位置：L031-F015；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F015=炉后第10弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -2900,7 +2900,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="107" customHeight="1">
+    <row r="27" ht="126" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr"/>
@@ -2939,7 +2939,7 @@
       <c r="J27" s="4" t="inlineStr"/>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#010；位置：L031-F016；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F016=炉后第9弯头→12CrMoVG</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#010；位置：L031-F016；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F016=炉后第9弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T27" s="4" t="inlineStr">
@@ -2992,7 +2992,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="107" customHeight="1">
+    <row r="28" ht="126" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>12CrMoVG</t>
+          <t>12Cr1MoVG</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
@@ -3031,7 +3031,7 @@
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#011；位置：L031-F017；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F017=炉后第8弯头→12CrMoVG</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#011；位置：L031-F017；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F017=炉后第8弯头→12Cr1MoVG</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -3065,7 +3065,7 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
@@ -3084,7 +3084,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="107" customHeight="1">
+    <row r="29" ht="126" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3095,7 +3095,7 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -3123,7 +3123,7 @@
       <c r="J29" s="4" t="inlineStr"/>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#012；位置：L031-F018；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F018=炉后第7弯头→T91</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#012；位置：L031-F018；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F018=炉后第7弯头→T91</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T29" s="4" t="inlineStr">
@@ -3176,7 +3176,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="107" customHeight="1">
+    <row r="30" ht="126" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3187,7 +3187,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3215,7 +3215,7 @@
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#013；位置：L031-F019；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F019=炉后第6弯头→T91</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#013；位置：L031-F019；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F019=炉后第6弯头→T91</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -3249,7 +3249,7 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
@@ -3268,7 +3268,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="107" customHeight="1">
+    <row r="31" ht="126" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -3307,7 +3307,7 @@
       <c r="J31" s="4" t="inlineStr"/>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#014；位置：L031-F020；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F020=炉后第5弯头→T91</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#014；位置：L031-F020；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F020=炉后第5弯头→T91</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T31" s="4" t="inlineStr">
@@ -3360,7 +3360,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="107" customHeight="1">
+    <row r="32" ht="126" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -3399,7 +3399,7 @@
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#015；位置：L031-F021；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F021=炉后第4弯头→304H</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#015；位置：L031-F021；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F021=炉后第4弯头→SA-213TP304H</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
@@ -3452,7 +3452,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="107" customHeight="1">
+    <row r="33" ht="126" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -3491,7 +3491,7 @@
       <c r="J33" s="4" t="inlineStr"/>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R5#016；位置：L031-F022；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F022=炉后第3弯头→304H</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#016；位置：L031-F022；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F022=炉后第3弯头→SA-213TP304H</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T33" s="4" t="inlineStr">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -3583,7 +3583,7 @@
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R6#001；位置：L001-F001；源位置：1号炉炉左至炉右第1屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R6#001；位置：L001-F001；源位置：1号炉炉左至炉右第1屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -3617,7 +3617,7 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
@@ -3647,7 +3647,7 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -3675,7 +3675,7 @@
       <c r="J35" s="4" t="inlineStr"/>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R7#001；位置：L002-F001；源位置：1号炉炉左至炉右第2屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R7#001；位置：L002-F001；源位置：1号炉炉左至炉右第2屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
@@ -3709,7 +3709,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T35" s="4" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -3767,7 +3767,7 @@
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R8#001；位置：L003-F001；源位置：1号炉炉左至炉右第3屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R8#001；位置：L003-F001；源位置：1号炉炉左至炉右第3屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -3859,7 +3859,7 @@
       <c r="J37" s="4" t="inlineStr"/>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R9#001；位置：L004-F001；源位置：1号炉炉左至炉右第4屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R9#001；位置：L004-F001；源位置：1号炉炉左至炉右第4屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T37" s="4" t="inlineStr">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -3951,7 +3951,7 @@
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R10#001；位置：L005-F001；源位置：1号炉炉左至炉右第5屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R10#001；位置：L005-F001；源位置：1号炉炉左至炉右第5屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -4043,7 +4043,7 @@
       <c r="J39" s="4" t="inlineStr"/>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R11#001；位置：L006-F001；源位置：1号炉炉左至炉右第6屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R11#001；位置：L006-F001；源位置：1号炉炉左至炉右第6屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T39" s="4" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -4135,7 +4135,7 @@
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R12#001；位置：L007-F001；源位置：1号炉炉左至炉右第7屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R12#001；位置：L007-F001；源位置：1号炉炉左至炉右第7屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -4169,7 +4169,7 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -4227,7 +4227,7 @@
       <c r="J41" s="4" t="inlineStr"/>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R13#001；位置：L008-F001；源位置：1号炉炉左至炉右第8屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R13#001；位置：L008-F001；源位置：1号炉炉左至炉右第8屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T41" s="4" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -4319,7 +4319,7 @@
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R14#001；位置：L009-F001；源位置：1号炉炉左至炉右第9屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R14#001；位置：L009-F001；源位置：1号炉炉左至炉右第9屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -4353,7 +4353,7 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -4411,7 +4411,7 @@
       <c r="J43" s="4" t="inlineStr"/>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R15#001；位置：L010-F001；源位置：1号炉炉左至炉右第10屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R15#001；位置：L010-F001；源位置：1号炉炉左至炉右第10屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T43" s="4" t="inlineStr">
@@ -4475,7 +4475,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -4503,7 +4503,7 @@
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R16#001；位置：L011-F001；源位置：1号炉炉左至炉右第11屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R16#001；位置：L011-F001；源位置：1号炉炉左至炉右第11屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
@@ -4567,7 +4567,7 @@
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -4595,7 +4595,7 @@
       <c r="J45" s="4" t="inlineStr"/>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R17#001；位置：L012-F001；源位置：1号炉炉左至炉右第12屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R17#001；位置：L012-F001；源位置：1号炉炉左至炉右第12屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
         </is>
       </c>
       <c r="L45" s="4" t="inlineStr">
@@ -4629,7 +4629,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T45" s="4" t="inlineStr">
@@ -4659,7 +4659,7 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -4687,7 +4687,7 @@
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R18#001；位置：L013-F001；源位置：1号炉炉左至炉右第13屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R18#001；位置：L013-F001；源位置：1号炉炉左至炉右第13屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
@@ -4751,7 +4751,7 @@
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -4779,7 +4779,7 @@
       <c r="J47" s="4" t="inlineStr"/>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R19#001；位置：L014-F001；源位置：1号炉炉左至炉右第14屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R19#001；位置：L014-F001；源位置：1号炉炉左至炉右第14屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
         </is>
       </c>
       <c r="L47" s="4" t="inlineStr">
@@ -4813,7 +4813,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T47" s="4" t="inlineStr">
@@ -4843,7 +4843,7 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -4871,7 +4871,7 @@
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R20#001；位置：L015-F001；源位置：1号炉炉左至炉右第15屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R20#001；位置：L015-F001；源位置：1号炉炉左至炉右第15屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -4905,7 +4905,7 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
@@ -4935,7 +4935,7 @@
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -4963,7 +4963,7 @@
       <c r="J49" s="4" t="inlineStr"/>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R21#001；位置：L016-F001；源位置：1号炉炉左至炉右第16屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R21#001；位置：L016-F001；源位置：1号炉炉左至炉右第16屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
         </is>
       </c>
       <c r="L49" s="4" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T49" s="4" t="inlineStr">
@@ -5027,7 +5027,7 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -5055,7 +5055,7 @@
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R22#001；位置：L017-F001；源位置：1号炉炉左至炉右第17屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R22#001；位置：L017-F001；源位置：1号炉炉左至炉右第17屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -5147,7 +5147,7 @@
       <c r="J51" s="4" t="inlineStr"/>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R23#001；位置：L018-F001；源位置：1号炉炉左至炉右第18屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R23#001；位置：L018-F001；源位置：1号炉炉左至炉右第18屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
         </is>
       </c>
       <c r="L51" s="4" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T51" s="4" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -5239,7 +5239,7 @@
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R24#001；位置：L019-F001；源位置：1号炉炉左至炉右第19屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R24#001；位置：L019-F001；源位置：1号炉炉左至炉右第19屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
@@ -5273,7 +5273,7 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -5331,7 +5331,7 @@
       <c r="J53" s="4" t="inlineStr"/>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R25#001；位置：L020-F001；源位置：1号炉炉左至炉右第20屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R25#001；位置：L020-F001；源位置：1号炉炉左至炉右第20屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
         </is>
       </c>
       <c r="L53" s="4" t="inlineStr">
@@ -5365,7 +5365,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T53" s="4" t="inlineStr">
@@ -5395,7 +5395,7 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -5423,7 +5423,7 @@
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R26#001；位置：L021-F001；源位置：1号炉炉左至炉右第21屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R26#001；位置：L021-F001；源位置：1号炉炉左至炉右第21屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
@@ -5457,7 +5457,7 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -5515,7 +5515,7 @@
       <c r="J55" s="4" t="inlineStr"/>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R27#001；位置：L022-F001；源位置：1号炉炉左至炉右第22屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R27#001；位置：L022-F001；源位置：1号炉炉左至炉右第22屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
         </is>
       </c>
       <c r="L55" s="4" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T55" s="4" t="inlineStr">
@@ -5579,7 +5579,7 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -5607,7 +5607,7 @@
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R28#001；位置：L023-F001；源位置：1号炉炉左至炉右第23屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R28#001；位置：L023-F001；源位置：1号炉炉左至炉右第23屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -5699,7 +5699,7 @@
       <c r="J57" s="4" t="inlineStr"/>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R29#001；位置：L024-F001；源位置：1号炉炉左至炉右第24屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R29#001；位置：L024-F001；源位置：1号炉炉左至炉右第24屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
         </is>
       </c>
       <c r="L57" s="4" t="inlineStr">
@@ -5733,7 +5733,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T57" s="4" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R30#001；位置：L025-F001；源位置：1号炉炉左至炉右第25屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R30#001；位置：L025-F001；源位置：1号炉炉左至炉右第25屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
@@ -5825,7 +5825,7 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
@@ -5855,7 +5855,7 @@
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -5883,7 +5883,7 @@
       <c r="J59" s="4" t="inlineStr"/>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R31#001；位置：L026-F001；源位置：1号炉炉左至炉右第26屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R31#001；位置：L026-F001；源位置：1号炉炉左至炉右第26屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
         </is>
       </c>
       <c r="L59" s="4" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T59" s="4" t="inlineStr">
@@ -5936,7 +5936,7 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="69" customHeight="1">
+    <row r="60" ht="88" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5947,12 +5947,12 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L028-F001-W</t>
+          <t>1G-GGRQ-GQ-L027-F001-W</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -5975,7 +5975,7 @@
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R33#001；位置：L028-F001；源位置：1号炉炉左至炉右第28屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R32#001；位置：L027-F001；源位置：1号炉炉左至炉右第24屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格；用户确认源表第32行“第24屏”实为第27屏（原表笔误），编码按L027修正</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
@@ -5985,7 +5985,7 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R33#001</t>
+          <t>2026年1号机C修!R32#001</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -5994,7 +5994,7 @@
         </is>
       </c>
       <c r="O60" s="2" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P60" s="2" t="n">
         <v>1</v>
@@ -6009,7 +6009,7 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
@@ -6024,7 +6024,7 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L028-F001-W01</t>
+          <t>1G-GGRQ-GQ-L024-F001-W01</t>
         </is>
       </c>
     </row>
@@ -6039,12 +6039,12 @@
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L029-F001-W</t>
+          <t>1G-GGRQ-GQ-L028-F001-W</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
@@ -6067,7 +6067,7 @@
       <c r="J61" s="4" t="inlineStr"/>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R34#001；位置：L029-F001；源位置：1号炉炉左至炉右第29屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R33#001；位置：L028-F001；源位置：1号炉炉左至炉右第28屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
         </is>
       </c>
       <c r="L61" s="4" t="inlineStr">
@@ -6077,7 +6077,7 @@
       </c>
       <c r="M61" s="4" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R34#001</t>
+          <t>2026年1号机C修!R33#001</t>
         </is>
       </c>
       <c r="N61" s="4" t="inlineStr">
@@ -6086,7 +6086,7 @@
         </is>
       </c>
       <c r="O61" s="4" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P61" s="4" t="n">
         <v>1</v>
@@ -6101,7 +6101,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T61" s="4" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="V61" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L029-F001-W01</t>
+          <t>1G-GGRQ-GQ-L028-F001-W01</t>
         </is>
       </c>
     </row>
@@ -6131,12 +6131,12 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L030-F001-W</t>
+          <t>1G-GGRQ-GQ-L029-F001-W</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -6159,7 +6159,7 @@
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R35#001；位置：L030-F001；源位置：1号炉炉左至炉右第30屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R34#001；位置：L029-F001；源位置：1号炉炉左至炉右第29屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R35#001</t>
+          <t>2026年1号机C修!R34#001</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -6178,7 +6178,7 @@
         </is>
       </c>
       <c r="O62" s="2" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P62" s="2" t="n">
         <v>1</v>
@@ -6193,7 +6193,7 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
@@ -6208,7 +6208,7 @@
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L030-F001-W01</t>
+          <t>1G-GGRQ-GQ-L029-F001-W01</t>
         </is>
       </c>
     </row>
@@ -6223,12 +6223,12 @@
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F001-W</t>
+          <t>1G-GGRQ-GQ-L030-F001-W</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
@@ -6251,7 +6251,7 @@
       <c r="J63" s="4" t="inlineStr"/>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R36#001；位置：L031-F001；源位置：1号炉炉左至炉右第31屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R35#001；位置：L030-F001；源位置：1号炉炉左至炉右第30屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
         </is>
       </c>
       <c r="L63" s="4" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="M63" s="4" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R36#001</t>
+          <t>2026年1号机C修!R35#001</t>
         </is>
       </c>
       <c r="N63" s="4" t="inlineStr">
@@ -6270,7 +6270,7 @@
         </is>
       </c>
       <c r="O63" s="4" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P63" s="4" t="n">
         <v>1</v>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T63" s="4" t="inlineStr">
@@ -6300,7 +6300,7 @@
       </c>
       <c r="V63" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F001-W01</t>
+          <t>1G-GGRQ-GQ-L030-F001-W01</t>
         </is>
       </c>
     </row>
@@ -6315,12 +6315,12 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L032-F001-W</t>
+          <t>1G-GGRQ-GQ-L031-F001-W</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -6343,7 +6343,7 @@
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R37#001；位置：L032-F001；源位置：1号炉炉左至炉右第32屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R36#001；位置：L031-F001；源位置：1号炉炉左至炉右第31屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R37#001</t>
+          <t>2026年1号机C修!R36#001</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -6362,7 +6362,7 @@
         </is>
       </c>
       <c r="O64" s="2" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P64" s="2" t="n">
         <v>1</v>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
@@ -6392,11 +6392,11 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L032-F001-W01</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="107" customHeight="1">
+          <t>1G-GGRQ-GQ-L031-F001-W01</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="69" customHeight="1">
       <c r="A65" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6407,12 +6407,12 @@
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L001-F002-W</t>
+          <t>1G-GGRQ-GQ-L032-F001-W</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr"/>
@@ -6435,7 +6435,7 @@
       <c r="J65" s="4" t="inlineStr"/>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#001；位置：L001-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R37#001；位置：L032-F001；源位置：1号炉炉左至炉右第32屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
@@ -6445,7 +6445,7 @@
       </c>
       <c r="M65" s="4" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#001</t>
+          <t>2026年1号机C修!R37#001</t>
         </is>
       </c>
       <c r="N65" s="4" t="inlineStr">
@@ -6454,7 +6454,7 @@
         </is>
       </c>
       <c r="O65" s="4" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P65" s="4" t="n">
         <v>1</v>
@@ -6464,12 +6464,12 @@
       </c>
       <c r="R65" s="4" t="inlineStr">
         <is>
-          <t>汇总展开</t>
+          <t>原始编码</t>
         </is>
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T65" s="4" t="inlineStr">
@@ -6482,9 +6482,13 @@
           <t>原文合格</t>
         </is>
       </c>
-      <c r="V65" s="4" t="inlineStr"/>
-    </row>
-    <row r="66" ht="107" customHeight="1">
+      <c r="V65" s="4" t="inlineStr">
+        <is>
+          <t>1G-GGRQ-GQ-L032-F001-W01</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="88" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6495,12 +6499,12 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L001-F003-W</t>
+          <t>1G-GGRQ-GQ-L001-F002-W</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -6510,7 +6514,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr"/>
@@ -6523,7 +6527,7 @@
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#002；位置：L001-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#001；位置：L001-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
@@ -6533,7 +6537,7 @@
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#002</t>
+          <t>2026年1号机C修!R38#001</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -6545,7 +6549,7 @@
         <v>38</v>
       </c>
       <c r="P66" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q66" s="2" t="n">
         <v>65</v>
@@ -6557,7 +6561,7 @@
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
@@ -6572,7 +6576,7 @@
       </c>
       <c r="V66" s="2" t="inlineStr"/>
     </row>
-    <row r="67" ht="107" customHeight="1">
+    <row r="67" ht="88" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6583,12 +6587,12 @@
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F002-W</t>
+          <t>1G-GGRQ-GQ-L001-F003-W</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
@@ -6598,7 +6602,7 @@
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr"/>
@@ -6611,7 +6615,7 @@
       <c r="J67" s="4" t="inlineStr"/>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#003；位置：L002-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#002；位置：L001-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L67" s="4" t="inlineStr">
@@ -6621,7 +6625,7 @@
       </c>
       <c r="M67" s="4" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#003</t>
+          <t>2026年1号机C修!R38#002</t>
         </is>
       </c>
       <c r="N67" s="4" t="inlineStr">
@@ -6633,7 +6637,7 @@
         <v>38</v>
       </c>
       <c r="P67" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q67" s="4" t="n">
         <v>66</v>
@@ -6645,7 +6649,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T67" s="4" t="inlineStr">
@@ -6660,7 +6664,7 @@
       </c>
       <c r="V67" s="4" t="inlineStr"/>
     </row>
-    <row r="68" ht="107" customHeight="1">
+    <row r="68" ht="88" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6671,12 +6675,12 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F003-W</t>
+          <t>1G-GGRQ-GQ-L002-F002-W</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -6686,7 +6690,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr"/>
@@ -6699,7 +6703,7 @@
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#004；位置：L002-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#003；位置：L002-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
@@ -6709,7 +6713,7 @@
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#004</t>
+          <t>2026年1号机C修!R38#003</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -6721,7 +6725,7 @@
         <v>38</v>
       </c>
       <c r="P68" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q68" s="2" t="n">
         <v>67</v>
@@ -6733,7 +6737,7 @@
       </c>
       <c r="S68" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T68" s="2" t="inlineStr">
@@ -6748,7 +6752,7 @@
       </c>
       <c r="V68" s="2" t="inlineStr"/>
     </row>
-    <row r="69" ht="107" customHeight="1">
+    <row r="69" ht="88" customHeight="1">
       <c r="A69" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6759,12 +6763,12 @@
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L003-F002-W</t>
+          <t>1G-GGRQ-GQ-L002-F003-W</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
@@ -6774,7 +6778,7 @@
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr"/>
@@ -6787,7 +6791,7 @@
       <c r="J69" s="4" t="inlineStr"/>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#005；位置：L003-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#004；位置：L002-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L69" s="4" t="inlineStr">
@@ -6797,7 +6801,7 @@
       </c>
       <c r="M69" s="4" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#005</t>
+          <t>2026年1号机C修!R38#004</t>
         </is>
       </c>
       <c r="N69" s="4" t="inlineStr">
@@ -6809,7 +6813,7 @@
         <v>38</v>
       </c>
       <c r="P69" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q69" s="4" t="n">
         <v>68</v>
@@ -6821,7 +6825,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T69" s="4" t="inlineStr">
@@ -6836,7 +6840,7 @@
       </c>
       <c r="V69" s="4" t="inlineStr"/>
     </row>
-    <row r="70" ht="107" customHeight="1">
+    <row r="70" ht="88" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6847,12 +6851,12 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L003-F003-W</t>
+          <t>1G-GGRQ-GQ-L003-F002-W</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -6862,7 +6866,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr"/>
@@ -6875,7 +6879,7 @@
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#006；位置：L003-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#005；位置：L003-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
@@ -6885,7 +6889,7 @@
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#006</t>
+          <t>2026年1号机C修!R38#005</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -6897,7 +6901,7 @@
         <v>38</v>
       </c>
       <c r="P70" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q70" s="2" t="n">
         <v>69</v>
@@ -6909,7 +6913,7 @@
       </c>
       <c r="S70" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T70" s="2" t="inlineStr">
@@ -6924,7 +6928,7 @@
       </c>
       <c r="V70" s="2" t="inlineStr"/>
     </row>
-    <row r="71" ht="107" customHeight="1">
+    <row r="71" ht="88" customHeight="1">
       <c r="A71" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6935,12 +6939,12 @@
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L004-F002-W</t>
+          <t>1G-GGRQ-GQ-L003-F003-W</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
@@ -6950,7 +6954,7 @@
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr"/>
@@ -6963,7 +6967,7 @@
       <c r="J71" s="4" t="inlineStr"/>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#007；位置：L004-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#006；位置：L003-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
@@ -6973,7 +6977,7 @@
       </c>
       <c r="M71" s="4" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#007</t>
+          <t>2026年1号机C修!R38#006</t>
         </is>
       </c>
       <c r="N71" s="4" t="inlineStr">
@@ -6985,7 +6989,7 @@
         <v>38</v>
       </c>
       <c r="P71" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q71" s="4" t="n">
         <v>70</v>
@@ -6997,7 +7001,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T71" s="4" t="inlineStr">
@@ -7012,7 +7016,7 @@
       </c>
       <c r="V71" s="4" t="inlineStr"/>
     </row>
-    <row r="72" ht="107" customHeight="1">
+    <row r="72" ht="88" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7023,12 +7027,12 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L004-F003-W</t>
+          <t>1G-GGRQ-GQ-L004-F002-W</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -7038,7 +7042,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr"/>
@@ -7051,7 +7055,7 @@
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#008；位置：L004-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：发现异物，割开检查为氧化皮；结果性质：异常观察；仅转录异常观察，未新增质量合格/不合格判定或处置闭环；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#007；位置：L004-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
@@ -7061,7 +7065,7 @@
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#008</t>
+          <t>2026年1号机C修!R38#007</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -7073,38 +7077,34 @@
         <v>38</v>
       </c>
       <c r="P72" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q72" s="2" t="n">
         <v>71</v>
       </c>
       <c r="R72" s="2" t="inlineStr">
         <is>
-          <t>原始编码</t>
+          <t>汇总展开</t>
         </is>
       </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>发现异物，割开检查为氧化皮</t>
+          <t>合格</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
         <is>
-          <t>异常观察</t>
-        </is>
-      </c>
-      <c r="V72" s="2" t="inlineStr">
-        <is>
-          <t>1G-GGRQ-GQ-L004-F003-W03（异物）</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="107" customHeight="1">
+          <t>原文合格</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73" ht="88" customHeight="1">
       <c r="A73" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7115,12 +7115,12 @@
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L005-F002-W</t>
+          <t>1G-GGRQ-GQ-L004-F003-W</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
@@ -7130,7 +7130,7 @@
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr"/>
@@ -7143,7 +7143,7 @@
       <c r="J73" s="4" t="inlineStr"/>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#009；位置：L005-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：发现异物，割开检查为氧化皮；结果性质：异常观察；仅转录异常观察，未新增质量合格/不合格判定或处置闭环；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#008；位置：L004-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：发现异物，割开检查为氧化皮；结果性质：异常观察；仅转录异常观察，未新增质量合格/不合格判定或处置闭环</t>
         </is>
       </c>
       <c r="L73" s="4" t="inlineStr">
@@ -7153,7 +7153,7 @@
       </c>
       <c r="M73" s="4" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#009</t>
+          <t>2026年1号机C修!R38#008</t>
         </is>
       </c>
       <c r="N73" s="4" t="inlineStr">
@@ -7165,7 +7165,7 @@
         <v>38</v>
       </c>
       <c r="P73" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q73" s="4" t="n">
         <v>72</v>
@@ -7177,7 +7177,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T73" s="4" t="inlineStr">
@@ -7192,11 +7192,11 @@
       </c>
       <c r="V73" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L005-F002-W02（异物）</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="107" customHeight="1">
+          <t>1G-GGRQ-GQ-L004-F003-W03（异物）</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="88" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7207,12 +7207,12 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L005-F003-W</t>
+          <t>1G-GGRQ-GQ-L005-F002-W</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -7222,7 +7222,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr"/>
@@ -7235,7 +7235,7 @@
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#010；位置：L005-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#009；位置：L005-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：发现异物，割开检查为氧化皮；结果性质：异常观察；仅转录异常观察，未新增质量合格/不合格判定或处置闭环</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
@@ -7245,7 +7245,7 @@
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#010</t>
+          <t>2026年1号机C修!R38#009</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -7257,34 +7257,38 @@
         <v>38</v>
       </c>
       <c r="P74" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q74" s="2" t="n">
         <v>73</v>
       </c>
       <c r="R74" s="2" t="inlineStr">
         <is>
-          <t>汇总展开</t>
+          <t>原始编码</t>
         </is>
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>合格</t>
+          <t>发现异物，割开检查为氧化皮</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
         <is>
-          <t>原文合格</t>
-        </is>
-      </c>
-      <c r="V74" s="2" t="inlineStr"/>
-    </row>
-    <row r="75" ht="107" customHeight="1">
+          <t>异常观察</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>1G-GGRQ-GQ-L005-F002-W02（异物）</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="88" customHeight="1">
       <c r="A75" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7295,12 +7299,12 @@
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L006-F002-W</t>
+          <t>1G-GGRQ-GQ-L005-F003-W</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
@@ -7310,7 +7314,7 @@
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr"/>
@@ -7323,7 +7327,7 @@
       <c r="J75" s="4" t="inlineStr"/>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#011；位置：L006-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#010；位置：L005-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L75" s="4" t="inlineStr">
@@ -7333,7 +7337,7 @@
       </c>
       <c r="M75" s="4" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#011</t>
+          <t>2026年1号机C修!R38#010</t>
         </is>
       </c>
       <c r="N75" s="4" t="inlineStr">
@@ -7345,7 +7349,7 @@
         <v>38</v>
       </c>
       <c r="P75" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q75" s="4" t="n">
         <v>74</v>
@@ -7357,7 +7361,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T75" s="4" t="inlineStr">
@@ -7372,7 +7376,7 @@
       </c>
       <c r="V75" s="4" t="inlineStr"/>
     </row>
-    <row r="76" ht="107" customHeight="1">
+    <row r="76" ht="88" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7383,12 +7387,12 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L006-F003-W</t>
+          <t>1G-GGRQ-GQ-L006-F002-W</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -7398,7 +7402,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr"/>
@@ -7411,7 +7415,7 @@
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#012；位置：L006-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#011；位置：L006-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
@@ -7421,7 +7425,7 @@
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#012</t>
+          <t>2026年1号机C修!R38#011</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -7433,7 +7437,7 @@
         <v>38</v>
       </c>
       <c r="P76" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q76" s="2" t="n">
         <v>75</v>
@@ -7445,7 +7449,7 @@
       </c>
       <c r="S76" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T76" s="2" t="inlineStr">
@@ -7460,7 +7464,7 @@
       </c>
       <c r="V76" s="2" t="inlineStr"/>
     </row>
-    <row r="77" ht="107" customHeight="1">
+    <row r="77" ht="88" customHeight="1">
       <c r="A77" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7471,12 +7475,12 @@
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L007-F002-W</t>
+          <t>1G-GGRQ-GQ-L006-F003-W</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
@@ -7486,7 +7490,7 @@
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr"/>
@@ -7499,7 +7503,7 @@
       <c r="J77" s="4" t="inlineStr"/>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#013；位置：L007-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#012；位置：L006-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L77" s="4" t="inlineStr">
@@ -7509,7 +7513,7 @@
       </c>
       <c r="M77" s="4" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#013</t>
+          <t>2026年1号机C修!R38#012</t>
         </is>
       </c>
       <c r="N77" s="4" t="inlineStr">
@@ -7521,7 +7525,7 @@
         <v>38</v>
       </c>
       <c r="P77" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q77" s="4" t="n">
         <v>76</v>
@@ -7533,7 +7537,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T77" s="4" t="inlineStr">
@@ -7548,7 +7552,7 @@
       </c>
       <c r="V77" s="4" t="inlineStr"/>
     </row>
-    <row r="78" ht="107" customHeight="1">
+    <row r="78" ht="88" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7559,12 +7563,12 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L007-F003-W</t>
+          <t>1G-GGRQ-GQ-L007-F002-W</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -7574,7 +7578,7 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr"/>
@@ -7587,7 +7591,7 @@
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#014；位置：L007-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#013；位置：L007-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
@@ -7597,7 +7601,7 @@
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#014</t>
+          <t>2026年1号机C修!R38#013</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -7609,7 +7613,7 @@
         <v>38</v>
       </c>
       <c r="P78" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q78" s="2" t="n">
         <v>77</v>
@@ -7621,7 +7625,7 @@
       </c>
       <c r="S78" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T78" s="2" t="inlineStr">
@@ -7636,7 +7640,7 @@
       </c>
       <c r="V78" s="2" t="inlineStr"/>
     </row>
-    <row r="79" ht="107" customHeight="1">
+    <row r="79" ht="88" customHeight="1">
       <c r="A79" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7647,12 +7651,12 @@
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L008-F002-W</t>
+          <t>1G-GGRQ-GQ-L007-F003-W</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
@@ -7662,7 +7666,7 @@
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr"/>
@@ -7675,7 +7679,7 @@
       <c r="J79" s="4" t="inlineStr"/>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#015；位置：L008-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#014；位置：L007-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L79" s="4" t="inlineStr">
@@ -7685,7 +7689,7 @@
       </c>
       <c r="M79" s="4" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#015</t>
+          <t>2026年1号机C修!R38#014</t>
         </is>
       </c>
       <c r="N79" s="4" t="inlineStr">
@@ -7697,7 +7701,7 @@
         <v>38</v>
       </c>
       <c r="P79" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Q79" s="4" t="n">
         <v>78</v>
@@ -7709,7 +7713,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T79" s="4" t="inlineStr">
@@ -7724,7 +7728,7 @@
       </c>
       <c r="V79" s="4" t="inlineStr"/>
     </row>
-    <row r="80" ht="107" customHeight="1">
+    <row r="80" ht="88" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7735,12 +7739,12 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L008-F003-W</t>
+          <t>1G-GGRQ-GQ-L008-F002-W</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -7750,7 +7754,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr"/>
@@ -7763,7 +7767,7 @@
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#016；位置：L008-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#015；位置：L008-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
@@ -7773,7 +7777,7 @@
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#016</t>
+          <t>2026年1号机C修!R38#015</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -7785,7 +7789,7 @@
         <v>38</v>
       </c>
       <c r="P80" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q80" s="2" t="n">
         <v>79</v>
@@ -7797,7 +7801,7 @@
       </c>
       <c r="S80" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T80" s="2" t="inlineStr">
@@ -7812,7 +7816,7 @@
       </c>
       <c r="V80" s="2" t="inlineStr"/>
     </row>
-    <row r="81" ht="107" customHeight="1">
+    <row r="81" ht="88" customHeight="1">
       <c r="A81" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7823,12 +7827,12 @@
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L009-F002-W</t>
+          <t>1G-GGRQ-GQ-L008-F003-W</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
@@ -7838,7 +7842,7 @@
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr"/>
@@ -7851,7 +7855,7 @@
       <c r="J81" s="4" t="inlineStr"/>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#017；位置：L009-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#016；位置：L008-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L81" s="4" t="inlineStr">
@@ -7861,7 +7865,7 @@
       </c>
       <c r="M81" s="4" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#017</t>
+          <t>2026年1号机C修!R38#016</t>
         </is>
       </c>
       <c r="N81" s="4" t="inlineStr">
@@ -7873,7 +7877,7 @@
         <v>38</v>
       </c>
       <c r="P81" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q81" s="4" t="n">
         <v>80</v>
@@ -7885,7 +7889,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T81" s="4" t="inlineStr">
@@ -7900,7 +7904,7 @@
       </c>
       <c r="V81" s="4" t="inlineStr"/>
     </row>
-    <row r="82" ht="107" customHeight="1">
+    <row r="82" ht="88" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7911,12 +7915,12 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L009-F003-W</t>
+          <t>1G-GGRQ-GQ-L009-F002-W</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -7926,7 +7930,7 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr"/>
@@ -7939,7 +7943,7 @@
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#018；位置：L009-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#017；位置：L009-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
@@ -7949,7 +7953,7 @@
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#018</t>
+          <t>2026年1号机C修!R38#017</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -7961,7 +7965,7 @@
         <v>38</v>
       </c>
       <c r="P82" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q82" s="2" t="n">
         <v>81</v>
@@ -7973,7 +7977,7 @@
       </c>
       <c r="S82" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T82" s="2" t="inlineStr">
@@ -7988,7 +7992,7 @@
       </c>
       <c r="V82" s="2" t="inlineStr"/>
     </row>
-    <row r="83" ht="107" customHeight="1">
+    <row r="83" ht="88" customHeight="1">
       <c r="A83" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7999,12 +8003,12 @@
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L010-F002-W</t>
+          <t>1G-GGRQ-GQ-L009-F003-W</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
@@ -8014,7 +8018,7 @@
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr"/>
@@ -8027,7 +8031,7 @@
       <c r="J83" s="4" t="inlineStr"/>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#019；位置：L010-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：发现异物，割开检查为氧化皮；结果性质：异常观察；仅转录异常观察，未新增质量合格/不合格判定或处置闭环；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#018；位置：L009-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L83" s="4" t="inlineStr">
@@ -8037,7 +8041,7 @@
       </c>
       <c r="M83" s="4" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#019</t>
+          <t>2026年1号机C修!R38#018</t>
         </is>
       </c>
       <c r="N83" s="4" t="inlineStr">
@@ -8049,38 +8053,34 @@
         <v>38</v>
       </c>
       <c r="P83" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q83" s="4" t="n">
         <v>82</v>
       </c>
       <c r="R83" s="4" t="inlineStr">
         <is>
-          <t>原始编码</t>
+          <t>汇总展开</t>
         </is>
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T83" s="4" t="inlineStr">
         <is>
-          <t>发现异物，割开检查为氧化皮</t>
+          <t>合格</t>
         </is>
       </c>
       <c r="U83" s="4" t="inlineStr">
         <is>
-          <t>异常观察</t>
-        </is>
-      </c>
-      <c r="V83" s="4" t="inlineStr">
-        <is>
-          <t>1G-GGRQ-GQ-L010-F002-W04（异物）</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="107" customHeight="1">
+          <t>原文合格</t>
+        </is>
+      </c>
+      <c r="V83" s="4" t="inlineStr"/>
+    </row>
+    <row r="84" ht="88" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8091,12 +8091,12 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L010-F003-W</t>
+          <t>1G-GGRQ-GQ-L010-F002-W</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr"/>
@@ -8119,7 +8119,7 @@
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#020；位置：L010-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#019；位置：L010-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：发现异物，割开检查为氧化皮；结果性质：异常观察；仅转录异常观察，未新增质量合格/不合格判定或处置闭环</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
@@ -8129,7 +8129,7 @@
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#020</t>
+          <t>2026年1号机C修!R38#019</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -8141,34 +8141,38 @@
         <v>38</v>
       </c>
       <c r="P84" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q84" s="2" t="n">
         <v>83</v>
       </c>
       <c r="R84" s="2" t="inlineStr">
         <is>
-          <t>汇总展开</t>
+          <t>原始编码</t>
         </is>
       </c>
       <c r="S84" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T84" s="2" t="inlineStr">
         <is>
-          <t>合格</t>
+          <t>发现异物，割开检查为氧化皮</t>
         </is>
       </c>
       <c r="U84" s="2" t="inlineStr">
         <is>
-          <t>原文合格</t>
-        </is>
-      </c>
-      <c r="V84" s="2" t="inlineStr"/>
-    </row>
-    <row r="85" ht="107" customHeight="1">
+          <t>异常观察</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>1G-GGRQ-GQ-L010-F002-W04（异物）</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="88" customHeight="1">
       <c r="A85" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8179,12 +8183,12 @@
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L011-F002-W</t>
+          <t>1G-GGRQ-GQ-L010-F003-W</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
@@ -8194,7 +8198,7 @@
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr"/>
@@ -8207,7 +8211,7 @@
       <c r="J85" s="4" t="inlineStr"/>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#021；位置：L011-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#020；位置：L010-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L85" s="4" t="inlineStr">
@@ -8217,7 +8221,7 @@
       </c>
       <c r="M85" s="4" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#021</t>
+          <t>2026年1号机C修!R38#020</t>
         </is>
       </c>
       <c r="N85" s="4" t="inlineStr">
@@ -8229,7 +8233,7 @@
         <v>38</v>
       </c>
       <c r="P85" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q85" s="4" t="n">
         <v>84</v>
@@ -8241,7 +8245,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T85" s="4" t="inlineStr">
@@ -8256,7 +8260,7 @@
       </c>
       <c r="V85" s="4" t="inlineStr"/>
     </row>
-    <row r="86" ht="107" customHeight="1">
+    <row r="86" ht="88" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8267,12 +8271,12 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L011-F003-W</t>
+          <t>1G-GGRQ-GQ-L011-F002-W</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -8282,7 +8286,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr"/>
@@ -8295,7 +8299,7 @@
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#022；位置：L011-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#021；位置：L011-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
@@ -8305,7 +8309,7 @@
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#022</t>
+          <t>2026年1号机C修!R38#021</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -8317,7 +8321,7 @@
         <v>38</v>
       </c>
       <c r="P86" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q86" s="2" t="n">
         <v>85</v>
@@ -8329,7 +8333,7 @@
       </c>
       <c r="S86" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T86" s="2" t="inlineStr">
@@ -8344,7 +8348,7 @@
       </c>
       <c r="V86" s="2" t="inlineStr"/>
     </row>
-    <row r="87" ht="107" customHeight="1">
+    <row r="87" ht="88" customHeight="1">
       <c r="A87" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8355,12 +8359,12 @@
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L012-F002-W</t>
+          <t>1G-GGRQ-GQ-L011-F003-W</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
@@ -8370,7 +8374,7 @@
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr"/>
@@ -8383,7 +8387,7 @@
       <c r="J87" s="4" t="inlineStr"/>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#023；位置：L012-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#022；位置：L011-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L87" s="4" t="inlineStr">
@@ -8393,7 +8397,7 @@
       </c>
       <c r="M87" s="4" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#023</t>
+          <t>2026年1号机C修!R38#022</t>
         </is>
       </c>
       <c r="N87" s="4" t="inlineStr">
@@ -8405,7 +8409,7 @@
         <v>38</v>
       </c>
       <c r="P87" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q87" s="4" t="n">
         <v>86</v>
@@ -8417,7 +8421,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T87" s="4" t="inlineStr">
@@ -8432,7 +8436,7 @@
       </c>
       <c r="V87" s="4" t="inlineStr"/>
     </row>
-    <row r="88" ht="107" customHeight="1">
+    <row r="88" ht="88" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8443,12 +8447,12 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L012-F003-W</t>
+          <t>1G-GGRQ-GQ-L012-F002-W</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -8458,7 +8462,7 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr"/>
@@ -8471,7 +8475,7 @@
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#024；位置：L012-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#023；位置：L012-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
@@ -8481,7 +8485,7 @@
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#024</t>
+          <t>2026年1号机C修!R38#023</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -8493,7 +8497,7 @@
         <v>38</v>
       </c>
       <c r="P88" s="2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q88" s="2" t="n">
         <v>87</v>
@@ -8505,7 +8509,7 @@
       </c>
       <c r="S88" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T88" s="2" t="inlineStr">
@@ -8520,7 +8524,7 @@
       </c>
       <c r="V88" s="2" t="inlineStr"/>
     </row>
-    <row r="89" ht="107" customHeight="1">
+    <row r="89" ht="88" customHeight="1">
       <c r="A89" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8531,12 +8535,12 @@
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L013-F002-W</t>
+          <t>1G-GGRQ-GQ-L012-F003-W</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
@@ -8546,7 +8550,7 @@
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr"/>
@@ -8559,7 +8563,7 @@
       <c r="J89" s="4" t="inlineStr"/>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#025；位置：L013-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：发现异物，割开检查为氧化皮；结果性质：异常观察；仅转录异常观察，未新增质量合格/不合格判定或处置闭环；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#024；位置：L012-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L89" s="4" t="inlineStr">
@@ -8569,7 +8573,7 @@
       </c>
       <c r="M89" s="4" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#025</t>
+          <t>2026年1号机C修!R38#024</t>
         </is>
       </c>
       <c r="N89" s="4" t="inlineStr">
@@ -8581,38 +8585,34 @@
         <v>38</v>
       </c>
       <c r="P89" s="4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q89" s="4" t="n">
         <v>88</v>
       </c>
       <c r="R89" s="4" t="inlineStr">
         <is>
-          <t>原始编码</t>
+          <t>汇总展开</t>
         </is>
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T89" s="4" t="inlineStr">
         <is>
-          <t>发现异物，割开检查为氧化皮</t>
+          <t>合格</t>
         </is>
       </c>
       <c r="U89" s="4" t="inlineStr">
         <is>
-          <t>异常观察</t>
-        </is>
-      </c>
-      <c r="V89" s="4" t="inlineStr">
-        <is>
-          <t>1G-GGRQ-GQ-L013-F002-W01（异物）</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="107" customHeight="1">
+          <t>原文合格</t>
+        </is>
+      </c>
+      <c r="V89" s="4" t="inlineStr"/>
+    </row>
+    <row r="90" ht="88" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L013-F003-W</t>
+          <t>1G-GGRQ-GQ-L013-F002-W</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr"/>
@@ -8651,7 +8651,7 @@
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#026；位置：L013-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#025；位置：L013-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：发现异物，割开检查为氧化皮；结果性质：异常观察；仅转录异常观察，未新增质量合格/不合格判定或处置闭环</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
@@ -8661,7 +8661,7 @@
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#026</t>
+          <t>2026年1号机C修!R38#025</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -8673,34 +8673,38 @@
         <v>38</v>
       </c>
       <c r="P90" s="2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q90" s="2" t="n">
         <v>89</v>
       </c>
       <c r="R90" s="2" t="inlineStr">
         <is>
-          <t>汇总展开</t>
+          <t>原始编码</t>
         </is>
       </c>
       <c r="S90" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T90" s="2" t="inlineStr">
         <is>
-          <t>合格</t>
+          <t>发现异物，割开检查为氧化皮</t>
         </is>
       </c>
       <c r="U90" s="2" t="inlineStr">
         <is>
-          <t>原文合格</t>
-        </is>
-      </c>
-      <c r="V90" s="2" t="inlineStr"/>
-    </row>
-    <row r="91" ht="107" customHeight="1">
+          <t>异常观察</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>1G-GGRQ-GQ-L013-F002-W01（异物）</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="88" customHeight="1">
       <c r="A91" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8711,12 +8715,12 @@
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L014-F002-W</t>
+          <t>1G-GGRQ-GQ-L013-F003-W</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
@@ -8726,7 +8730,7 @@
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr"/>
@@ -8739,7 +8743,7 @@
       <c r="J91" s="4" t="inlineStr"/>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#027；位置：L014-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#026；位置：L013-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L91" s="4" t="inlineStr">
@@ -8749,7 +8753,7 @@
       </c>
       <c r="M91" s="4" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#027</t>
+          <t>2026年1号机C修!R38#026</t>
         </is>
       </c>
       <c r="N91" s="4" t="inlineStr">
@@ -8761,7 +8765,7 @@
         <v>38</v>
       </c>
       <c r="P91" s="4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q91" s="4" t="n">
         <v>90</v>
@@ -8773,7 +8777,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T91" s="4" t="inlineStr">
@@ -8788,7 +8792,7 @@
       </c>
       <c r="V91" s="4" t="inlineStr"/>
     </row>
-    <row r="92" ht="107" customHeight="1">
+    <row r="92" ht="88" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8799,12 +8803,12 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L014-F003-W</t>
+          <t>1G-GGRQ-GQ-L014-F002-W</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -8814,7 +8818,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr"/>
@@ -8827,7 +8831,7 @@
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#028；位置：L014-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#027；位置：L014-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
@@ -8837,7 +8841,7 @@
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#028</t>
+          <t>2026年1号机C修!R38#027</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -8849,7 +8853,7 @@
         <v>38</v>
       </c>
       <c r="P92" s="2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Q92" s="2" t="n">
         <v>91</v>
@@ -8861,7 +8865,7 @@
       </c>
       <c r="S92" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T92" s="2" t="inlineStr">
@@ -8876,7 +8880,7 @@
       </c>
       <c r="V92" s="2" t="inlineStr"/>
     </row>
-    <row r="93" ht="107" customHeight="1">
+    <row r="93" ht="88" customHeight="1">
       <c r="A93" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8887,12 +8891,12 @@
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L015-F002-W</t>
+          <t>1G-GGRQ-GQ-L014-F003-W</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
@@ -8902,7 +8906,7 @@
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr"/>
@@ -8915,7 +8919,7 @@
       <c r="J93" s="4" t="inlineStr"/>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#029；位置：L015-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#028；位置：L014-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L93" s="4" t="inlineStr">
@@ -8925,7 +8929,7 @@
       </c>
       <c r="M93" s="4" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#029</t>
+          <t>2026年1号机C修!R38#028</t>
         </is>
       </c>
       <c r="N93" s="4" t="inlineStr">
@@ -8937,7 +8941,7 @@
         <v>38</v>
       </c>
       <c r="P93" s="4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Q93" s="4" t="n">
         <v>92</v>
@@ -8949,7 +8953,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T93" s="4" t="inlineStr">
@@ -8964,7 +8968,7 @@
       </c>
       <c r="V93" s="4" t="inlineStr"/>
     </row>
-    <row r="94" ht="107" customHeight="1">
+    <row r="94" ht="88" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8975,12 +8979,12 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L015-F003-W</t>
+          <t>1G-GGRQ-GQ-L015-F002-W</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -8990,7 +8994,7 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr"/>
@@ -9003,7 +9007,7 @@
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#030；位置：L015-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#029；位置：L015-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
@@ -9013,7 +9017,7 @@
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#030</t>
+          <t>2026年1号机C修!R38#029</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -9025,7 +9029,7 @@
         <v>38</v>
       </c>
       <c r="P94" s="2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q94" s="2" t="n">
         <v>93</v>
@@ -9037,7 +9041,7 @@
       </c>
       <c r="S94" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T94" s="2" t="inlineStr">
@@ -9052,7 +9056,7 @@
       </c>
       <c r="V94" s="2" t="inlineStr"/>
     </row>
-    <row r="95" ht="107" customHeight="1">
+    <row r="95" ht="88" customHeight="1">
       <c r="A95" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9063,12 +9067,12 @@
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L016-F002-W</t>
+          <t>1G-GGRQ-GQ-L015-F003-W</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
@@ -9078,7 +9082,7 @@
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr"/>
@@ -9091,7 +9095,7 @@
       <c r="J95" s="4" t="inlineStr"/>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#031；位置：L016-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#030；位置：L015-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L95" s="4" t="inlineStr">
@@ -9101,7 +9105,7 @@
       </c>
       <c r="M95" s="4" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#031</t>
+          <t>2026年1号机C修!R38#030</t>
         </is>
       </c>
       <c r="N95" s="4" t="inlineStr">
@@ -9113,7 +9117,7 @@
         <v>38</v>
       </c>
       <c r="P95" s="4" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q95" s="4" t="n">
         <v>94</v>
@@ -9125,7 +9129,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T95" s="4" t="inlineStr">
@@ -9140,7 +9144,7 @@
       </c>
       <c r="V95" s="4" t="inlineStr"/>
     </row>
-    <row r="96" ht="107" customHeight="1">
+    <row r="96" ht="88" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9151,12 +9155,12 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L016-F003-W</t>
+          <t>1G-GGRQ-GQ-L016-F002-W</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -9166,7 +9170,7 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr"/>
@@ -9179,7 +9183,7 @@
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#032；位置：L016-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#031；位置：L016-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
@@ -9189,7 +9193,7 @@
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#032</t>
+          <t>2026年1号机C修!R38#031</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -9201,7 +9205,7 @@
         <v>38</v>
       </c>
       <c r="P96" s="2" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Q96" s="2" t="n">
         <v>95</v>
@@ -9213,7 +9217,7 @@
       </c>
       <c r="S96" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T96" s="2" t="inlineStr">
@@ -9228,7 +9232,7 @@
       </c>
       <c r="V96" s="2" t="inlineStr"/>
     </row>
-    <row r="97" ht="107" customHeight="1">
+    <row r="97" ht="88" customHeight="1">
       <c r="A97" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9239,12 +9243,12 @@
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L017-F002-W</t>
+          <t>1G-GGRQ-GQ-L016-F003-W</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
@@ -9254,7 +9258,7 @@
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr"/>
@@ -9267,7 +9271,7 @@
       <c r="J97" s="4" t="inlineStr"/>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#033；位置：L017-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#032；位置：L016-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L97" s="4" t="inlineStr">
@@ -9277,7 +9281,7 @@
       </c>
       <c r="M97" s="4" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#033</t>
+          <t>2026年1号机C修!R38#032</t>
         </is>
       </c>
       <c r="N97" s="4" t="inlineStr">
@@ -9289,7 +9293,7 @@
         <v>38</v>
       </c>
       <c r="P97" s="4" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q97" s="4" t="n">
         <v>96</v>
@@ -9301,7 +9305,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T97" s="4" t="inlineStr">
@@ -9316,7 +9320,7 @@
       </c>
       <c r="V97" s="4" t="inlineStr"/>
     </row>
-    <row r="98" ht="107" customHeight="1">
+    <row r="98" ht="88" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9327,12 +9331,12 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L017-F003-W</t>
+          <t>1G-GGRQ-GQ-L017-F002-W</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -9342,7 +9346,7 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr"/>
@@ -9355,7 +9359,7 @@
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#034；位置：L017-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#033；位置：L017-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
@@ -9365,7 +9369,7 @@
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#034</t>
+          <t>2026年1号机C修!R38#033</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -9377,7 +9381,7 @@
         <v>38</v>
       </c>
       <c r="P98" s="2" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q98" s="2" t="n">
         <v>97</v>
@@ -9389,7 +9393,7 @@
       </c>
       <c r="S98" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T98" s="2" t="inlineStr">
@@ -9404,7 +9408,7 @@
       </c>
       <c r="V98" s="2" t="inlineStr"/>
     </row>
-    <row r="99" ht="107" customHeight="1">
+    <row r="99" ht="88" customHeight="1">
       <c r="A99" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9415,12 +9419,12 @@
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L018-F002-W</t>
+          <t>1G-GGRQ-GQ-L017-F003-W</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
@@ -9430,7 +9434,7 @@
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr"/>
@@ -9443,7 +9447,7 @@
       <c r="J99" s="4" t="inlineStr"/>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#035；位置：L018-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#034；位置：L017-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L99" s="4" t="inlineStr">
@@ -9453,7 +9457,7 @@
       </c>
       <c r="M99" s="4" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#035</t>
+          <t>2026年1号机C修!R38#034</t>
         </is>
       </c>
       <c r="N99" s="4" t="inlineStr">
@@ -9465,7 +9469,7 @@
         <v>38</v>
       </c>
       <c r="P99" s="4" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q99" s="4" t="n">
         <v>98</v>
@@ -9477,7 +9481,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T99" s="4" t="inlineStr">
@@ -9492,7 +9496,7 @@
       </c>
       <c r="V99" s="4" t="inlineStr"/>
     </row>
-    <row r="100" ht="107" customHeight="1">
+    <row r="100" ht="88" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9503,12 +9507,12 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L018-F003-W</t>
+          <t>1G-GGRQ-GQ-L018-F002-W</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -9518,7 +9522,7 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr"/>
@@ -9531,7 +9535,7 @@
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#036；位置：L018-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#035；位置：L018-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
@@ -9541,7 +9545,7 @@
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#036</t>
+          <t>2026年1号机C修!R38#035</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -9553,7 +9557,7 @@
         <v>38</v>
       </c>
       <c r="P100" s="2" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q100" s="2" t="n">
         <v>99</v>
@@ -9565,7 +9569,7 @@
       </c>
       <c r="S100" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T100" s="2" t="inlineStr">
@@ -9580,7 +9584,7 @@
       </c>
       <c r="V100" s="2" t="inlineStr"/>
     </row>
-    <row r="101" ht="107" customHeight="1">
+    <row r="101" ht="88" customHeight="1">
       <c r="A101" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9591,12 +9595,12 @@
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L019-F002-W</t>
+          <t>1G-GGRQ-GQ-L018-F003-W</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
@@ -9606,7 +9610,7 @@
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G101" s="4" t="inlineStr"/>
@@ -9619,7 +9623,7 @@
       <c r="J101" s="4" t="inlineStr"/>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#037；位置：L019-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#036；位置：L018-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L101" s="4" t="inlineStr">
@@ -9629,7 +9633,7 @@
       </c>
       <c r="M101" s="4" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#037</t>
+          <t>2026年1号机C修!R38#036</t>
         </is>
       </c>
       <c r="N101" s="4" t="inlineStr">
@@ -9641,7 +9645,7 @@
         <v>38</v>
       </c>
       <c r="P101" s="4" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q101" s="4" t="n">
         <v>100</v>
@@ -9653,7 +9657,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T101" s="4" t="inlineStr">
@@ -9668,7 +9672,7 @@
       </c>
       <c r="V101" s="4" t="inlineStr"/>
     </row>
-    <row r="102" ht="107" customHeight="1">
+    <row r="102" ht="88" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9679,12 +9683,12 @@
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L019-F003-W</t>
+          <t>1G-GGRQ-GQ-L019-F002-W</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -9694,7 +9698,7 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr"/>
@@ -9707,7 +9711,7 @@
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#038；位置：L019-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#037；位置：L019-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
@@ -9717,7 +9721,7 @@
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#038</t>
+          <t>2026年1号机C修!R38#037</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -9729,7 +9733,7 @@
         <v>38</v>
       </c>
       <c r="P102" s="2" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Q102" s="2" t="n">
         <v>101</v>
@@ -9741,7 +9745,7 @@
       </c>
       <c r="S102" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T102" s="2" t="inlineStr">
@@ -9756,7 +9760,7 @@
       </c>
       <c r="V102" s="2" t="inlineStr"/>
     </row>
-    <row r="103" ht="107" customHeight="1">
+    <row r="103" ht="88" customHeight="1">
       <c r="A103" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9767,12 +9771,12 @@
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L020-F002-W</t>
+          <t>1G-GGRQ-GQ-L019-F003-W</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
@@ -9782,7 +9786,7 @@
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G103" s="4" t="inlineStr"/>
@@ -9795,7 +9799,7 @@
       <c r="J103" s="4" t="inlineStr"/>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#039；位置：L020-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#038；位置：L019-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L103" s="4" t="inlineStr">
@@ -9805,7 +9809,7 @@
       </c>
       <c r="M103" s="4" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#039</t>
+          <t>2026年1号机C修!R38#038</t>
         </is>
       </c>
       <c r="N103" s="4" t="inlineStr">
@@ -9817,7 +9821,7 @@
         <v>38</v>
       </c>
       <c r="P103" s="4" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q103" s="4" t="n">
         <v>102</v>
@@ -9829,7 +9833,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T103" s="4" t="inlineStr">
@@ -9844,7 +9848,7 @@
       </c>
       <c r="V103" s="4" t="inlineStr"/>
     </row>
-    <row r="104" ht="107" customHeight="1">
+    <row r="104" ht="88" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9855,12 +9859,12 @@
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L020-F003-W</t>
+          <t>1G-GGRQ-GQ-L020-F002-W</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -9870,7 +9874,7 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr"/>
@@ -9883,7 +9887,7 @@
       <c r="J104" s="2" t="inlineStr"/>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#040；位置：L020-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#039；位置：L020-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
@@ -9893,7 +9897,7 @@
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#040</t>
+          <t>2026年1号机C修!R38#039</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -9905,7 +9909,7 @@
         <v>38</v>
       </c>
       <c r="P104" s="2" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Q104" s="2" t="n">
         <v>103</v>
@@ -9917,7 +9921,7 @@
       </c>
       <c r="S104" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T104" s="2" t="inlineStr">
@@ -9932,7 +9936,7 @@
       </c>
       <c r="V104" s="2" t="inlineStr"/>
     </row>
-    <row r="105" ht="107" customHeight="1">
+    <row r="105" ht="88" customHeight="1">
       <c r="A105" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9943,12 +9947,12 @@
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L021-F002-W</t>
+          <t>1G-GGRQ-GQ-L020-F003-W</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
@@ -9958,7 +9962,7 @@
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G105" s="4" t="inlineStr"/>
@@ -9971,7 +9975,7 @@
       <c r="J105" s="4" t="inlineStr"/>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#041；位置：L021-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#040；位置：L020-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L105" s="4" t="inlineStr">
@@ -9981,7 +9985,7 @@
       </c>
       <c r="M105" s="4" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#041</t>
+          <t>2026年1号机C修!R38#040</t>
         </is>
       </c>
       <c r="N105" s="4" t="inlineStr">
@@ -9993,7 +9997,7 @@
         <v>38</v>
       </c>
       <c r="P105" s="4" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q105" s="4" t="n">
         <v>104</v>
@@ -10005,7 +10009,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T105" s="4" t="inlineStr">
@@ -10020,7 +10024,7 @@
       </c>
       <c r="V105" s="4" t="inlineStr"/>
     </row>
-    <row r="106" ht="107" customHeight="1">
+    <row r="106" ht="88" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10031,12 +10035,12 @@
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L021-F003-W</t>
+          <t>1G-GGRQ-GQ-L021-F002-W</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -10046,7 +10050,7 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr"/>
@@ -10059,7 +10063,7 @@
       <c r="J106" s="2" t="inlineStr"/>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#042；位置：L021-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#041；位置：L021-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L106" s="2" t="inlineStr">
@@ -10069,7 +10073,7 @@
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#042</t>
+          <t>2026年1号机C修!R38#041</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
@@ -10081,7 +10085,7 @@
         <v>38</v>
       </c>
       <c r="P106" s="2" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q106" s="2" t="n">
         <v>105</v>
@@ -10093,7 +10097,7 @@
       </c>
       <c r="S106" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T106" s="2" t="inlineStr">
@@ -10108,7 +10112,7 @@
       </c>
       <c r="V106" s="2" t="inlineStr"/>
     </row>
-    <row r="107" ht="107" customHeight="1">
+    <row r="107" ht="88" customHeight="1">
       <c r="A107" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10119,12 +10123,12 @@
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L022-F002-W</t>
+          <t>1G-GGRQ-GQ-L021-F003-W</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
@@ -10134,7 +10138,7 @@
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G107" s="4" t="inlineStr"/>
@@ -10147,7 +10151,7 @@
       <c r="J107" s="4" t="inlineStr"/>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#043；位置：L022-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#042；位置：L021-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L107" s="4" t="inlineStr">
@@ -10157,7 +10161,7 @@
       </c>
       <c r="M107" s="4" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#043</t>
+          <t>2026年1号机C修!R38#042</t>
         </is>
       </c>
       <c r="N107" s="4" t="inlineStr">
@@ -10169,7 +10173,7 @@
         <v>38</v>
       </c>
       <c r="P107" s="4" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Q107" s="4" t="n">
         <v>106</v>
@@ -10181,7 +10185,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T107" s="4" t="inlineStr">
@@ -10196,7 +10200,7 @@
       </c>
       <c r="V107" s="4" t="inlineStr"/>
     </row>
-    <row r="108" ht="107" customHeight="1">
+    <row r="108" ht="88" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10207,12 +10211,12 @@
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L022-F003-W</t>
+          <t>1G-GGRQ-GQ-L022-F002-W</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -10222,7 +10226,7 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr"/>
@@ -10235,7 +10239,7 @@
       <c r="J108" s="2" t="inlineStr"/>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#044；位置：L022-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#043；位置：L022-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L108" s="2" t="inlineStr">
@@ -10245,7 +10249,7 @@
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#044</t>
+          <t>2026年1号机C修!R38#043</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -10257,7 +10261,7 @@
         <v>38</v>
       </c>
       <c r="P108" s="2" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="Q108" s="2" t="n">
         <v>107</v>
@@ -10269,7 +10273,7 @@
       </c>
       <c r="S108" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T108" s="2" t="inlineStr">
@@ -10284,7 +10288,7 @@
       </c>
       <c r="V108" s="2" t="inlineStr"/>
     </row>
-    <row r="109" ht="107" customHeight="1">
+    <row r="109" ht="88" customHeight="1">
       <c r="A109" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10295,12 +10299,12 @@
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L023-F002-W</t>
+          <t>1G-GGRQ-GQ-L022-F003-W</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
@@ -10310,7 +10314,7 @@
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G109" s="4" t="inlineStr"/>
@@ -10323,7 +10327,7 @@
       <c r="J109" s="4" t="inlineStr"/>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#045；位置：L023-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#044；位置：L022-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L109" s="4" t="inlineStr">
@@ -10333,7 +10337,7 @@
       </c>
       <c r="M109" s="4" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#045</t>
+          <t>2026年1号机C修!R38#044</t>
         </is>
       </c>
       <c r="N109" s="4" t="inlineStr">
@@ -10345,7 +10349,7 @@
         <v>38</v>
       </c>
       <c r="P109" s="4" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q109" s="4" t="n">
         <v>108</v>
@@ -10357,7 +10361,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T109" s="4" t="inlineStr">
@@ -10372,7 +10376,7 @@
       </c>
       <c r="V109" s="4" t="inlineStr"/>
     </row>
-    <row r="110" ht="107" customHeight="1">
+    <row r="110" ht="88" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10383,12 +10387,12 @@
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L023-F003-W</t>
+          <t>1G-GGRQ-GQ-L023-F002-W</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -10398,7 +10402,7 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr"/>
@@ -10411,7 +10415,7 @@
       <c r="J110" s="2" t="inlineStr"/>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#046；位置：L023-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#045；位置：L023-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L110" s="2" t="inlineStr">
@@ -10421,7 +10425,7 @@
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#046</t>
+          <t>2026年1号机C修!R38#045</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
@@ -10433,7 +10437,7 @@
         <v>38</v>
       </c>
       <c r="P110" s="2" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q110" s="2" t="n">
         <v>109</v>
@@ -10445,7 +10449,7 @@
       </c>
       <c r="S110" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T110" s="2" t="inlineStr">
@@ -10460,7 +10464,7 @@
       </c>
       <c r="V110" s="2" t="inlineStr"/>
     </row>
-    <row r="111" ht="107" customHeight="1">
+    <row r="111" ht="88" customHeight="1">
       <c r="A111" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10471,12 +10475,12 @@
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L024-F002-W</t>
+          <t>1G-GGRQ-GQ-L023-F003-W</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
@@ -10486,7 +10490,7 @@
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G111" s="4" t="inlineStr"/>
@@ -10499,7 +10503,7 @@
       <c r="J111" s="4" t="inlineStr"/>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#047；位置：L024-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#046；位置：L023-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L111" s="4" t="inlineStr">
@@ -10509,7 +10513,7 @@
       </c>
       <c r="M111" s="4" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#047</t>
+          <t>2026年1号机C修!R38#046</t>
         </is>
       </c>
       <c r="N111" s="4" t="inlineStr">
@@ -10521,7 +10525,7 @@
         <v>38</v>
       </c>
       <c r="P111" s="4" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q111" s="4" t="n">
         <v>110</v>
@@ -10533,7 +10537,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T111" s="4" t="inlineStr">
@@ -10548,7 +10552,7 @@
       </c>
       <c r="V111" s="4" t="inlineStr"/>
     </row>
-    <row r="112" ht="107" customHeight="1">
+    <row r="112" ht="88" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10559,12 +10563,12 @@
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L024-F003-W</t>
+          <t>1G-GGRQ-GQ-L024-F002-W</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -10574,7 +10578,7 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr"/>
@@ -10587,7 +10591,7 @@
       <c r="J112" s="2" t="inlineStr"/>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#048；位置：L024-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#047；位置：L024-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L112" s="2" t="inlineStr">
@@ -10597,7 +10601,7 @@
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#048</t>
+          <t>2026年1号机C修!R38#047</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
@@ -10609,7 +10613,7 @@
         <v>38</v>
       </c>
       <c r="P112" s="2" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Q112" s="2" t="n">
         <v>111</v>
@@ -10621,7 +10625,7 @@
       </c>
       <c r="S112" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T112" s="2" t="inlineStr">
@@ -10636,7 +10640,7 @@
       </c>
       <c r="V112" s="2" t="inlineStr"/>
     </row>
-    <row r="113" ht="107" customHeight="1">
+    <row r="113" ht="88" customHeight="1">
       <c r="A113" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10647,12 +10651,12 @@
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L025-F002-W</t>
+          <t>1G-GGRQ-GQ-L024-F003-W</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
@@ -10662,7 +10666,7 @@
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G113" s="4" t="inlineStr"/>
@@ -10675,7 +10679,7 @@
       <c r="J113" s="4" t="inlineStr"/>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#049；位置：L025-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：发现异物，割开检查为氧化皮；结果性质：异常观察；仅转录异常观察，未新增质量合格/不合格判定或处置闭环；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#048；位置：L024-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L113" s="4" t="inlineStr">
@@ -10685,7 +10689,7 @@
       </c>
       <c r="M113" s="4" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#049</t>
+          <t>2026年1号机C修!R38#048</t>
         </is>
       </c>
       <c r="N113" s="4" t="inlineStr">
@@ -10697,38 +10701,34 @@
         <v>38</v>
       </c>
       <c r="P113" s="4" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q113" s="4" t="n">
         <v>112</v>
       </c>
       <c r="R113" s="4" t="inlineStr">
         <is>
-          <t>原始编码</t>
+          <t>汇总展开</t>
         </is>
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T113" s="4" t="inlineStr">
         <is>
-          <t>发现异物，割开检查为氧化皮</t>
+          <t>合格</t>
         </is>
       </c>
       <c r="U113" s="4" t="inlineStr">
         <is>
-          <t>异常观察</t>
-        </is>
-      </c>
-      <c r="V113" s="4" t="inlineStr">
-        <is>
-          <t>1G-GGRQ-GQ-L025-F002-W05（异物）</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="107" customHeight="1">
+          <t>原文合格</t>
+        </is>
+      </c>
+      <c r="V113" s="4" t="inlineStr"/>
+    </row>
+    <row r="114" ht="88" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10739,12 +10739,12 @@
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L025-F003-W</t>
+          <t>1G-GGRQ-GQ-L025-F002-W</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -10754,7 +10754,7 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr"/>
@@ -10767,7 +10767,7 @@
       <c r="J114" s="2" t="inlineStr"/>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#050；位置：L025-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#049；位置：L025-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：发现异物，割开检查为氧化皮；结果性质：异常观察；仅转录异常观察，未新增质量合格/不合格判定或处置闭环</t>
         </is>
       </c>
       <c r="L114" s="2" t="inlineStr">
@@ -10777,7 +10777,7 @@
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#050</t>
+          <t>2026年1号机C修!R38#049</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
@@ -10789,34 +10789,38 @@
         <v>38</v>
       </c>
       <c r="P114" s="2" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q114" s="2" t="n">
         <v>113</v>
       </c>
       <c r="R114" s="2" t="inlineStr">
         <is>
-          <t>汇总展开</t>
+          <t>原始编码</t>
         </is>
       </c>
       <c r="S114" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T114" s="2" t="inlineStr">
         <is>
-          <t>合格</t>
+          <t>发现异物，割开检查为氧化皮</t>
         </is>
       </c>
       <c r="U114" s="2" t="inlineStr">
         <is>
-          <t>原文合格</t>
-        </is>
-      </c>
-      <c r="V114" s="2" t="inlineStr"/>
-    </row>
-    <row r="115" ht="107" customHeight="1">
+          <t>异常观察</t>
+        </is>
+      </c>
+      <c r="V114" s="2" t="inlineStr">
+        <is>
+          <t>1G-GGRQ-GQ-L025-F002-W05（异物）</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="88" customHeight="1">
       <c r="A115" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10827,12 +10831,12 @@
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L026-F002-W</t>
+          <t>1G-GGRQ-GQ-L025-F003-W</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
@@ -10842,7 +10846,7 @@
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G115" s="4" t="inlineStr"/>
@@ -10855,7 +10859,7 @@
       <c r="J115" s="4" t="inlineStr"/>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#051；位置：L026-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#050；位置：L025-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L115" s="4" t="inlineStr">
@@ -10865,7 +10869,7 @@
       </c>
       <c r="M115" s="4" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#051</t>
+          <t>2026年1号机C修!R38#050</t>
         </is>
       </c>
       <c r="N115" s="4" t="inlineStr">
@@ -10877,7 +10881,7 @@
         <v>38</v>
       </c>
       <c r="P115" s="4" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Q115" s="4" t="n">
         <v>114</v>
@@ -10889,7 +10893,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T115" s="4" t="inlineStr">
@@ -10904,7 +10908,7 @@
       </c>
       <c r="V115" s="4" t="inlineStr"/>
     </row>
-    <row r="116" ht="107" customHeight="1">
+    <row r="116" ht="88" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10915,12 +10919,12 @@
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L026-F003-W</t>
+          <t>1G-GGRQ-GQ-L026-F002-W</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -10930,7 +10934,7 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr"/>
@@ -10943,7 +10947,7 @@
       <c r="J116" s="2" t="inlineStr"/>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#052；位置：L026-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#051；位置：L026-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L116" s="2" t="inlineStr">
@@ -10953,7 +10957,7 @@
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#052</t>
+          <t>2026年1号机C修!R38#051</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -10965,7 +10969,7 @@
         <v>38</v>
       </c>
       <c r="P116" s="2" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Q116" s="2" t="n">
         <v>115</v>
@@ -10977,7 +10981,7 @@
       </c>
       <c r="S116" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T116" s="2" t="inlineStr">
@@ -10992,7 +10996,7 @@
       </c>
       <c r="V116" s="2" t="inlineStr"/>
     </row>
-    <row r="117" ht="107" customHeight="1">
+    <row r="117" ht="88" customHeight="1">
       <c r="A117" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11003,12 +11007,12 @@
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L027-F002-W</t>
+          <t>1G-GGRQ-GQ-L026-F003-W</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
@@ -11018,7 +11022,7 @@
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G117" s="4" t="inlineStr"/>
@@ -11031,7 +11035,7 @@
       <c r="J117" s="4" t="inlineStr"/>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#053；位置：L027-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#052；位置：L026-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L117" s="4" t="inlineStr">
@@ -11041,7 +11045,7 @@
       </c>
       <c r="M117" s="4" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#053</t>
+          <t>2026年1号机C修!R38#052</t>
         </is>
       </c>
       <c r="N117" s="4" t="inlineStr">
@@ -11053,7 +11057,7 @@
         <v>38</v>
       </c>
       <c r="P117" s="4" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q117" s="4" t="n">
         <v>116</v>
@@ -11065,7 +11069,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T117" s="4" t="inlineStr">
@@ -11080,7 +11084,7 @@
       </c>
       <c r="V117" s="4" t="inlineStr"/>
     </row>
-    <row r="118" ht="107" customHeight="1">
+    <row r="118" ht="88" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11091,12 +11095,12 @@
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L027-F003-W</t>
+          <t>1G-GGRQ-GQ-L027-F002-W</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -11106,7 +11110,7 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr"/>
@@ -11119,7 +11123,7 @@
       <c r="J118" s="2" t="inlineStr"/>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#054；位置：L027-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#053；位置：L027-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L118" s="2" t="inlineStr">
@@ -11129,7 +11133,7 @@
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#054</t>
+          <t>2026年1号机C修!R38#053</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
@@ -11141,7 +11145,7 @@
         <v>38</v>
       </c>
       <c r="P118" s="2" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="Q118" s="2" t="n">
         <v>117</v>
@@ -11153,7 +11157,7 @@
       </c>
       <c r="S118" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T118" s="2" t="inlineStr">
@@ -11168,7 +11172,7 @@
       </c>
       <c r="V118" s="2" t="inlineStr"/>
     </row>
-    <row r="119" ht="107" customHeight="1">
+    <row r="119" ht="88" customHeight="1">
       <c r="A119" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11179,12 +11183,12 @@
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L028-F002-W</t>
+          <t>1G-GGRQ-GQ-L027-F003-W</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
@@ -11194,7 +11198,7 @@
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G119" s="4" t="inlineStr"/>
@@ -11207,7 +11211,7 @@
       <c r="J119" s="4" t="inlineStr"/>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#055；位置：L028-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#054；位置：L027-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L119" s="4" t="inlineStr">
@@ -11217,7 +11221,7 @@
       </c>
       <c r="M119" s="4" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#055</t>
+          <t>2026年1号机C修!R38#054</t>
         </is>
       </c>
       <c r="N119" s="4" t="inlineStr">
@@ -11229,7 +11233,7 @@
         <v>38</v>
       </c>
       <c r="P119" s="4" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="Q119" s="4" t="n">
         <v>118</v>
@@ -11241,7 +11245,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T119" s="4" t="inlineStr">
@@ -11256,7 +11260,7 @@
       </c>
       <c r="V119" s="4" t="inlineStr"/>
     </row>
-    <row r="120" ht="107" customHeight="1">
+    <row r="120" ht="88" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11267,12 +11271,12 @@
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L028-F003-W</t>
+          <t>1G-GGRQ-GQ-L028-F002-W</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -11282,7 +11286,7 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr"/>
@@ -11295,7 +11299,7 @@
       <c r="J120" s="2" t="inlineStr"/>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#056；位置：L028-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#055；位置：L028-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L120" s="2" t="inlineStr">
@@ -11305,7 +11309,7 @@
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#056</t>
+          <t>2026年1号机C修!R38#055</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -11317,7 +11321,7 @@
         <v>38</v>
       </c>
       <c r="P120" s="2" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Q120" s="2" t="n">
         <v>119</v>
@@ -11329,7 +11333,7 @@
       </c>
       <c r="S120" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T120" s="2" t="inlineStr">
@@ -11344,7 +11348,7 @@
       </c>
       <c r="V120" s="2" t="inlineStr"/>
     </row>
-    <row r="121" ht="107" customHeight="1">
+    <row r="121" ht="88" customHeight="1">
       <c r="A121" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11355,12 +11359,12 @@
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L029-F002-W</t>
+          <t>1G-GGRQ-GQ-L028-F003-W</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
@@ -11370,7 +11374,7 @@
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G121" s="4" t="inlineStr"/>
@@ -11383,7 +11387,7 @@
       <c r="J121" s="4" t="inlineStr"/>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#057；位置：L029-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#056；位置：L028-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L121" s="4" t="inlineStr">
@@ -11393,7 +11397,7 @@
       </c>
       <c r="M121" s="4" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#057</t>
+          <t>2026年1号机C修!R38#056</t>
         </is>
       </c>
       <c r="N121" s="4" t="inlineStr">
@@ -11405,7 +11409,7 @@
         <v>38</v>
       </c>
       <c r="P121" s="4" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Q121" s="4" t="n">
         <v>120</v>
@@ -11417,7 +11421,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T121" s="4" t="inlineStr">
@@ -11432,7 +11436,7 @@
       </c>
       <c r="V121" s="4" t="inlineStr"/>
     </row>
-    <row r="122" ht="107" customHeight="1">
+    <row r="122" ht="88" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11443,12 +11447,12 @@
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L029-F003-W</t>
+          <t>1G-GGRQ-GQ-L029-F002-W</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -11458,7 +11462,7 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr"/>
@@ -11471,7 +11475,7 @@
       <c r="J122" s="2" t="inlineStr"/>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#058；位置：L029-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#057；位置：L029-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L122" s="2" t="inlineStr">
@@ -11481,7 +11485,7 @@
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#058</t>
+          <t>2026年1号机C修!R38#057</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
@@ -11493,7 +11497,7 @@
         <v>38</v>
       </c>
       <c r="P122" s="2" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q122" s="2" t="n">
         <v>121</v>
@@ -11505,7 +11509,7 @@
       </c>
       <c r="S122" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T122" s="2" t="inlineStr">
@@ -11520,7 +11524,7 @@
       </c>
       <c r="V122" s="2" t="inlineStr"/>
     </row>
-    <row r="123" ht="107" customHeight="1">
+    <row r="123" ht="88" customHeight="1">
       <c r="A123" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11531,12 +11535,12 @@
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L030-F002-W</t>
+          <t>1G-GGRQ-GQ-L029-F003-W</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
@@ -11546,7 +11550,7 @@
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G123" s="4" t="inlineStr"/>
@@ -11559,7 +11563,7 @@
       <c r="J123" s="4" t="inlineStr"/>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#059；位置：L030-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#058；位置：L029-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L123" s="4" t="inlineStr">
@@ -11569,7 +11573,7 @@
       </c>
       <c r="M123" s="4" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#059</t>
+          <t>2026年1号机C修!R38#058</t>
         </is>
       </c>
       <c r="N123" s="4" t="inlineStr">
@@ -11581,7 +11585,7 @@
         <v>38</v>
       </c>
       <c r="P123" s="4" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Q123" s="4" t="n">
         <v>122</v>
@@ -11593,7 +11597,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T123" s="4" t="inlineStr">
@@ -11608,7 +11612,7 @@
       </c>
       <c r="V123" s="4" t="inlineStr"/>
     </row>
-    <row r="124" ht="107" customHeight="1">
+    <row r="124" ht="88" customHeight="1">
       <c r="A124" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11619,12 +11623,12 @@
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L030-F003-W</t>
+          <t>1G-GGRQ-GQ-L030-F002-W</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -11634,7 +11638,7 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr"/>
@@ -11647,7 +11651,7 @@
       <c r="J124" s="2" t="inlineStr"/>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#060；位置：L030-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#059；位置：L030-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L124" s="2" t="inlineStr">
@@ -11657,7 +11661,7 @@
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#060</t>
+          <t>2026年1号机C修!R38#059</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
@@ -11669,7 +11673,7 @@
         <v>38</v>
       </c>
       <c r="P124" s="2" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Q124" s="2" t="n">
         <v>123</v>
@@ -11681,7 +11685,7 @@
       </c>
       <c r="S124" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T124" s="2" t="inlineStr">
@@ -11696,7 +11700,7 @@
       </c>
       <c r="V124" s="2" t="inlineStr"/>
     </row>
-    <row r="125" ht="107" customHeight="1">
+    <row r="125" ht="88" customHeight="1">
       <c r="A125" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11707,12 +11711,12 @@
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F002-W</t>
+          <t>1G-GGRQ-GQ-L030-F003-W</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
@@ -11722,7 +11726,7 @@
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G125" s="4" t="inlineStr"/>
@@ -11735,7 +11739,7 @@
       <c r="J125" s="4" t="inlineStr"/>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#061；位置：L031-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#060；位置：L030-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L125" s="4" t="inlineStr">
@@ -11745,7 +11749,7 @@
       </c>
       <c r="M125" s="4" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#061</t>
+          <t>2026年1号机C修!R38#060</t>
         </is>
       </c>
       <c r="N125" s="4" t="inlineStr">
@@ -11757,7 +11761,7 @@
         <v>38</v>
       </c>
       <c r="P125" s="4" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q125" s="4" t="n">
         <v>124</v>
@@ -11769,7 +11773,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T125" s="4" t="inlineStr">
@@ -11784,7 +11788,7 @@
       </c>
       <c r="V125" s="4" t="inlineStr"/>
     </row>
-    <row r="126" ht="107" customHeight="1">
+    <row r="126" ht="88" customHeight="1">
       <c r="A126" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11795,12 +11799,12 @@
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F003-W</t>
+          <t>1G-GGRQ-GQ-L031-F002-W</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -11810,7 +11814,7 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr"/>
@@ -11823,7 +11827,7 @@
       <c r="J126" s="2" t="inlineStr"/>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#062；位置：L031-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#061；位置：L031-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L126" s="2" t="inlineStr">
@@ -11833,7 +11837,7 @@
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#062</t>
+          <t>2026年1号机C修!R38#061</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
@@ -11845,7 +11849,7 @@
         <v>38</v>
       </c>
       <c r="P126" s="2" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q126" s="2" t="n">
         <v>125</v>
@@ -11857,7 +11861,7 @@
       </c>
       <c r="S126" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T126" s="2" t="inlineStr">
@@ -11872,7 +11876,7 @@
       </c>
       <c r="V126" s="2" t="inlineStr"/>
     </row>
-    <row r="127" ht="107" customHeight="1">
+    <row r="127" ht="88" customHeight="1">
       <c r="A127" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11883,12 +11887,12 @@
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L032-F002-W</t>
+          <t>1G-GGRQ-GQ-L031-F003-W</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
@@ -11898,7 +11902,7 @@
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G127" s="4" t="inlineStr"/>
@@ -11911,7 +11915,7 @@
       <c r="J127" s="4" t="inlineStr"/>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#063；位置：L032-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#062；位置：L031-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L127" s="4" t="inlineStr">
@@ -11921,7 +11925,7 @@
       </c>
       <c r="M127" s="4" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#063</t>
+          <t>2026年1号机C修!R38#062</t>
         </is>
       </c>
       <c r="N127" s="4" t="inlineStr">
@@ -11933,7 +11937,7 @@
         <v>38</v>
       </c>
       <c r="P127" s="4" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q127" s="4" t="n">
         <v>126</v>
@@ -11945,7 +11949,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T127" s="4" t="inlineStr">
@@ -11960,7 +11964,7 @@
       </c>
       <c r="V127" s="4" t="inlineStr"/>
     </row>
-    <row r="128" ht="107" customHeight="1">
+    <row r="128" ht="88" customHeight="1">
       <c r="A128" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11971,12 +11975,12 @@
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L032-F003-W</t>
+          <t>1G-GGRQ-GQ-L032-F002-W</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -11986,7 +11990,7 @@
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr"/>
@@ -11999,7 +12003,7 @@
       <c r="J128" s="2" t="inlineStr"/>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#064；位置：L032-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#063；位置：L032-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L128" s="2" t="inlineStr">
@@ -12009,7 +12013,7 @@
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R38#064</t>
+          <t>2026年1号机C修!R38#063</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
@@ -12021,7 +12025,7 @@
         <v>38</v>
       </c>
       <c r="P128" s="2" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="Q128" s="2" t="n">
         <v>127</v>
@@ -12033,7 +12037,7 @@
       </c>
       <c r="S128" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T128" s="2" t="inlineStr">
@@ -12059,12 +12063,12 @@
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L001-F024-W</t>
+          <t>1G-GGRQ-GQ-L032-F003-W</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
@@ -12074,7 +12078,7 @@
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G129" s="4" t="inlineStr"/>
@@ -12087,7 +12091,7 @@
       <c r="J129" s="4" t="inlineStr"/>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#001；位置：L001-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#064；位置：L032-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L129" s="4" t="inlineStr">
@@ -12097,7 +12101,7 @@
       </c>
       <c r="M129" s="4" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R39#001</t>
+          <t>2026年1号机C修!R38#064</t>
         </is>
       </c>
       <c r="N129" s="4" t="inlineStr">
@@ -12106,10 +12110,10 @@
         </is>
       </c>
       <c r="O129" s="4" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P129" s="4" t="n">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="Q129" s="4" t="n">
         <v>128</v>
@@ -12121,7 +12125,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T129" s="4" t="inlineStr">
@@ -12136,7 +12140,7 @@
       </c>
       <c r="V129" s="4" t="inlineStr"/>
     </row>
-    <row r="130" ht="88" customHeight="1">
+    <row r="130" ht="107" customHeight="1">
       <c r="A130" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -12147,12 +12151,12 @@
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F024-W</t>
+          <t>1G-GGRQ-GQ-L001-F024-W</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -12162,7 +12166,7 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr"/>
@@ -12175,7 +12179,7 @@
       <c r="J130" s="2" t="inlineStr"/>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#002；位置：L002-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#001；位置：L001-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L130" s="2" t="inlineStr">
@@ -12185,7 +12189,7 @@
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R39#002</t>
+          <t>2026年1号机C修!R39#001</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
@@ -12197,7 +12201,7 @@
         <v>39</v>
       </c>
       <c r="P130" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q130" s="2" t="n">
         <v>129</v>
@@ -12209,7 +12213,7 @@
       </c>
       <c r="S130" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T130" s="2" t="inlineStr">
@@ -12224,7 +12228,7 @@
       </c>
       <c r="V130" s="2" t="inlineStr"/>
     </row>
-    <row r="131" ht="88" customHeight="1">
+    <row r="131" ht="107" customHeight="1">
       <c r="A131" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -12235,12 +12239,12 @@
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L003-F024-W</t>
+          <t>1G-GGRQ-GQ-L002-F024-W</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
@@ -12250,7 +12254,7 @@
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G131" s="4" t="inlineStr"/>
@@ -12263,7 +12267,7 @@
       <c r="J131" s="4" t="inlineStr"/>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#003；位置：L003-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#002；位置：L002-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L131" s="4" t="inlineStr">
@@ -12273,7 +12277,7 @@
       </c>
       <c r="M131" s="4" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R39#003</t>
+          <t>2026年1号机C修!R39#002</t>
         </is>
       </c>
       <c r="N131" s="4" t="inlineStr">
@@ -12285,7 +12289,7 @@
         <v>39</v>
       </c>
       <c r="P131" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q131" s="4" t="n">
         <v>130</v>
@@ -12297,7 +12301,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T131" s="4" t="inlineStr">
@@ -12312,7 +12316,7 @@
       </c>
       <c r="V131" s="4" t="inlineStr"/>
     </row>
-    <row r="132" ht="88" customHeight="1">
+    <row r="132" ht="107" customHeight="1">
       <c r="A132" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -12323,12 +12327,12 @@
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L004-F024-W</t>
+          <t>1G-GGRQ-GQ-L003-F024-W</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -12338,7 +12342,7 @@
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr"/>
@@ -12351,7 +12355,7 @@
       <c r="J132" s="2" t="inlineStr"/>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#004；位置：L004-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#003；位置：L003-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L132" s="2" t="inlineStr">
@@ -12361,7 +12365,7 @@
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R39#004</t>
+          <t>2026年1号机C修!R39#003</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
@@ -12373,7 +12377,7 @@
         <v>39</v>
       </c>
       <c r="P132" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q132" s="2" t="n">
         <v>131</v>
@@ -12385,7 +12389,7 @@
       </c>
       <c r="S132" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T132" s="2" t="inlineStr">
@@ -12400,7 +12404,7 @@
       </c>
       <c r="V132" s="2" t="inlineStr"/>
     </row>
-    <row r="133" ht="88" customHeight="1">
+    <row r="133" ht="107" customHeight="1">
       <c r="A133" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -12411,12 +12415,12 @@
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L005-F024-W</t>
+          <t>1G-GGRQ-GQ-L004-F024-W</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
@@ -12426,7 +12430,7 @@
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G133" s="4" t="inlineStr"/>
@@ -12439,7 +12443,7 @@
       <c r="J133" s="4" t="inlineStr"/>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#005；位置：L005-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#004；位置：L004-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L133" s="4" t="inlineStr">
@@ -12449,7 +12453,7 @@
       </c>
       <c r="M133" s="4" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R39#005</t>
+          <t>2026年1号机C修!R39#004</t>
         </is>
       </c>
       <c r="N133" s="4" t="inlineStr">
@@ -12461,7 +12465,7 @@
         <v>39</v>
       </c>
       <c r="P133" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q133" s="4" t="n">
         <v>132</v>
@@ -12473,7 +12477,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T133" s="4" t="inlineStr">
@@ -12488,7 +12492,7 @@
       </c>
       <c r="V133" s="4" t="inlineStr"/>
     </row>
-    <row r="134" ht="88" customHeight="1">
+    <row r="134" ht="107" customHeight="1">
       <c r="A134" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -12499,12 +12503,12 @@
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L006-F024-W</t>
+          <t>1G-GGRQ-GQ-L005-F024-W</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -12514,7 +12518,7 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr"/>
@@ -12527,7 +12531,7 @@
       <c r="J134" s="2" t="inlineStr"/>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#006；位置：L006-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#005；位置：L005-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L134" s="2" t="inlineStr">
@@ -12537,7 +12541,7 @@
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R39#006</t>
+          <t>2026年1号机C修!R39#005</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr">
@@ -12549,7 +12553,7 @@
         <v>39</v>
       </c>
       <c r="P134" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q134" s="2" t="n">
         <v>133</v>
@@ -12561,7 +12565,7 @@
       </c>
       <c r="S134" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T134" s="2" t="inlineStr">
@@ -12576,7 +12580,7 @@
       </c>
       <c r="V134" s="2" t="inlineStr"/>
     </row>
-    <row r="135" ht="88" customHeight="1">
+    <row r="135" ht="107" customHeight="1">
       <c r="A135" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -12587,12 +12591,12 @@
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L007-F024-W</t>
+          <t>1G-GGRQ-GQ-L006-F024-W</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr">
@@ -12602,7 +12606,7 @@
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G135" s="4" t="inlineStr"/>
@@ -12615,7 +12619,7 @@
       <c r="J135" s="4" t="inlineStr"/>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#007；位置：L007-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#006；位置：L006-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L135" s="4" t="inlineStr">
@@ -12625,7 +12629,7 @@
       </c>
       <c r="M135" s="4" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R39#007</t>
+          <t>2026年1号机C修!R39#006</t>
         </is>
       </c>
       <c r="N135" s="4" t="inlineStr">
@@ -12637,7 +12641,7 @@
         <v>39</v>
       </c>
       <c r="P135" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q135" s="4" t="n">
         <v>134</v>
@@ -12649,7 +12653,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T135" s="4" t="inlineStr">
@@ -12664,7 +12668,7 @@
       </c>
       <c r="V135" s="4" t="inlineStr"/>
     </row>
-    <row r="136" ht="88" customHeight="1">
+    <row r="136" ht="107" customHeight="1">
       <c r="A136" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -12675,12 +12679,12 @@
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L008-F024-W</t>
+          <t>1G-GGRQ-GQ-L007-F024-W</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -12690,7 +12694,7 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr"/>
@@ -12703,7 +12707,7 @@
       <c r="J136" s="2" t="inlineStr"/>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#008；位置：L008-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#007；位置：L007-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L136" s="2" t="inlineStr">
@@ -12713,7 +12717,7 @@
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R39#008</t>
+          <t>2026年1号机C修!R39#007</t>
         </is>
       </c>
       <c r="N136" s="2" t="inlineStr">
@@ -12725,7 +12729,7 @@
         <v>39</v>
       </c>
       <c r="P136" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q136" s="2" t="n">
         <v>135</v>
@@ -12737,7 +12741,7 @@
       </c>
       <c r="S136" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T136" s="2" t="inlineStr">
@@ -12752,7 +12756,7 @@
       </c>
       <c r="V136" s="2" t="inlineStr"/>
     </row>
-    <row r="137" ht="88" customHeight="1">
+    <row r="137" ht="107" customHeight="1">
       <c r="A137" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -12763,12 +12767,12 @@
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L009-F024-W</t>
+          <t>1G-GGRQ-GQ-L008-F024-W</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr">
@@ -12778,7 +12782,7 @@
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G137" s="4" t="inlineStr"/>
@@ -12791,7 +12795,7 @@
       <c r="J137" s="4" t="inlineStr"/>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#009；位置：L009-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#008；位置：L008-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L137" s="4" t="inlineStr">
@@ -12801,7 +12805,7 @@
       </c>
       <c r="M137" s="4" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R39#009</t>
+          <t>2026年1号机C修!R39#008</t>
         </is>
       </c>
       <c r="N137" s="4" t="inlineStr">
@@ -12813,7 +12817,7 @@
         <v>39</v>
       </c>
       <c r="P137" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q137" s="4" t="n">
         <v>136</v>
@@ -12825,7 +12829,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T137" s="4" t="inlineStr">
@@ -12840,7 +12844,7 @@
       </c>
       <c r="V137" s="4" t="inlineStr"/>
     </row>
-    <row r="138" ht="88" customHeight="1">
+    <row r="138" ht="107" customHeight="1">
       <c r="A138" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -12851,12 +12855,12 @@
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L010-F024-W</t>
+          <t>1G-GGRQ-GQ-L009-F024-W</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
@@ -12866,7 +12870,7 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr"/>
@@ -12879,7 +12883,7 @@
       <c r="J138" s="2" t="inlineStr"/>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#010；位置：L010-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#009；位置：L009-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L138" s="2" t="inlineStr">
@@ -12889,7 +12893,7 @@
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R39#010</t>
+          <t>2026年1号机C修!R39#009</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr">
@@ -12901,7 +12905,7 @@
         <v>39</v>
       </c>
       <c r="P138" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q138" s="2" t="n">
         <v>137</v>
@@ -12913,7 +12917,7 @@
       </c>
       <c r="S138" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T138" s="2" t="inlineStr">
@@ -12928,7 +12932,7 @@
       </c>
       <c r="V138" s="2" t="inlineStr"/>
     </row>
-    <row r="139" ht="88" customHeight="1">
+    <row r="139" ht="107" customHeight="1">
       <c r="A139" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -12939,12 +12943,12 @@
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L011-F024-W</t>
+          <t>1G-GGRQ-GQ-L010-F024-W</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr">
@@ -12954,7 +12958,7 @@
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G139" s="4" t="inlineStr"/>
@@ -12967,7 +12971,7 @@
       <c r="J139" s="4" t="inlineStr"/>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#011；位置：L011-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#010；位置：L010-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L139" s="4" t="inlineStr">
@@ -12977,7 +12981,7 @@
       </c>
       <c r="M139" s="4" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R39#011</t>
+          <t>2026年1号机C修!R39#010</t>
         </is>
       </c>
       <c r="N139" s="4" t="inlineStr">
@@ -12989,7 +12993,7 @@
         <v>39</v>
       </c>
       <c r="P139" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q139" s="4" t="n">
         <v>138</v>
@@ -13001,7 +13005,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T139" s="4" t="inlineStr">
@@ -13016,7 +13020,7 @@
       </c>
       <c r="V139" s="4" t="inlineStr"/>
     </row>
-    <row r="140" ht="88" customHeight="1">
+    <row r="140" ht="107" customHeight="1">
       <c r="A140" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -13027,12 +13031,12 @@
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L012-F024-W</t>
+          <t>1G-GGRQ-GQ-L011-F024-W</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -13042,7 +13046,7 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr"/>
@@ -13055,7 +13059,7 @@
       <c r="J140" s="2" t="inlineStr"/>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#012；位置：L012-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#011；位置：L011-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L140" s="2" t="inlineStr">
@@ -13065,7 +13069,7 @@
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R39#012</t>
+          <t>2026年1号机C修!R39#011</t>
         </is>
       </c>
       <c r="N140" s="2" t="inlineStr">
@@ -13077,7 +13081,7 @@
         <v>39</v>
       </c>
       <c r="P140" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q140" s="2" t="n">
         <v>139</v>
@@ -13089,7 +13093,7 @@
       </c>
       <c r="S140" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T140" s="2" t="inlineStr">
@@ -13104,7 +13108,7 @@
       </c>
       <c r="V140" s="2" t="inlineStr"/>
     </row>
-    <row r="141" ht="88" customHeight="1">
+    <row r="141" ht="107" customHeight="1">
       <c r="A141" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -13115,12 +13119,12 @@
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L013-F024-W</t>
+          <t>1G-GGRQ-GQ-L012-F024-W</t>
         </is>
       </c>
       <c r="E141" s="4" t="inlineStr">
@@ -13130,7 +13134,7 @@
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G141" s="4" t="inlineStr"/>
@@ -13143,7 +13147,7 @@
       <c r="J141" s="4" t="inlineStr"/>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#013；位置：L013-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#012；位置：L012-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L141" s="4" t="inlineStr">
@@ -13153,7 +13157,7 @@
       </c>
       <c r="M141" s="4" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R39#013</t>
+          <t>2026年1号机C修!R39#012</t>
         </is>
       </c>
       <c r="N141" s="4" t="inlineStr">
@@ -13165,7 +13169,7 @@
         <v>39</v>
       </c>
       <c r="P141" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q141" s="4" t="n">
         <v>140</v>
@@ -13177,7 +13181,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T141" s="4" t="inlineStr">
@@ -13192,7 +13196,7 @@
       </c>
       <c r="V141" s="4" t="inlineStr"/>
     </row>
-    <row r="142" ht="88" customHeight="1">
+    <row r="142" ht="107" customHeight="1">
       <c r="A142" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -13203,12 +13207,12 @@
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L014-F024-W</t>
+          <t>1G-GGRQ-GQ-L013-F024-W</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
@@ -13218,7 +13222,7 @@
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr"/>
@@ -13231,7 +13235,7 @@
       <c r="J142" s="2" t="inlineStr"/>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#014；位置：L014-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#013；位置：L013-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L142" s="2" t="inlineStr">
@@ -13241,7 +13245,7 @@
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R39#014</t>
+          <t>2026年1号机C修!R39#013</t>
         </is>
       </c>
       <c r="N142" s="2" t="inlineStr">
@@ -13253,7 +13257,7 @@
         <v>39</v>
       </c>
       <c r="P142" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q142" s="2" t="n">
         <v>141</v>
@@ -13265,7 +13269,7 @@
       </c>
       <c r="S142" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T142" s="2" t="inlineStr">
@@ -13280,7 +13284,7 @@
       </c>
       <c r="V142" s="2" t="inlineStr"/>
     </row>
-    <row r="143" ht="88" customHeight="1">
+    <row r="143" ht="107" customHeight="1">
       <c r="A143" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -13291,12 +13295,12 @@
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L015-F024-W</t>
+          <t>1G-GGRQ-GQ-L014-F024-W</t>
         </is>
       </c>
       <c r="E143" s="4" t="inlineStr">
@@ -13306,7 +13310,7 @@
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G143" s="4" t="inlineStr"/>
@@ -13319,7 +13323,7 @@
       <c r="J143" s="4" t="inlineStr"/>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#015；位置：L015-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#014；位置：L014-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L143" s="4" t="inlineStr">
@@ -13329,7 +13333,7 @@
       </c>
       <c r="M143" s="4" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R39#015</t>
+          <t>2026年1号机C修!R39#014</t>
         </is>
       </c>
       <c r="N143" s="4" t="inlineStr">
@@ -13341,7 +13345,7 @@
         <v>39</v>
       </c>
       <c r="P143" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Q143" s="4" t="n">
         <v>142</v>
@@ -13353,7 +13357,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T143" s="4" t="inlineStr">
@@ -13368,7 +13372,7 @@
       </c>
       <c r="V143" s="4" t="inlineStr"/>
     </row>
-    <row r="144" ht="88" customHeight="1">
+    <row r="144" ht="107" customHeight="1">
       <c r="A144" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -13379,12 +13383,12 @@
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L016-F024-W</t>
+          <t>1G-GGRQ-GQ-L015-F024-W</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -13394,7 +13398,7 @@
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr"/>
@@ -13407,7 +13411,7 @@
       <c r="J144" s="2" t="inlineStr"/>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#016；位置：L016-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#015；位置：L015-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L144" s="2" t="inlineStr">
@@ -13417,7 +13421,7 @@
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R39#016</t>
+          <t>2026年1号机C修!R39#015</t>
         </is>
       </c>
       <c r="N144" s="2" t="inlineStr">
@@ -13429,7 +13433,7 @@
         <v>39</v>
       </c>
       <c r="P144" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q144" s="2" t="n">
         <v>143</v>
@@ -13441,7 +13445,7 @@
       </c>
       <c r="S144" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T144" s="2" t="inlineStr">
@@ -13456,7 +13460,7 @@
       </c>
       <c r="V144" s="2" t="inlineStr"/>
     </row>
-    <row r="145" ht="88" customHeight="1">
+    <row r="145" ht="107" customHeight="1">
       <c r="A145" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -13467,12 +13471,12 @@
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L017-F024-W</t>
+          <t>1G-GGRQ-GQ-L016-F024-W</t>
         </is>
       </c>
       <c r="E145" s="4" t="inlineStr">
@@ -13482,7 +13486,7 @@
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G145" s="4" t="inlineStr"/>
@@ -13495,7 +13499,7 @@
       <c r="J145" s="4" t="inlineStr"/>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#017；位置：L017-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#016；位置：L016-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L145" s="4" t="inlineStr">
@@ -13505,7 +13509,7 @@
       </c>
       <c r="M145" s="4" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R39#017</t>
+          <t>2026年1号机C修!R39#016</t>
         </is>
       </c>
       <c r="N145" s="4" t="inlineStr">
@@ -13517,7 +13521,7 @@
         <v>39</v>
       </c>
       <c r="P145" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q145" s="4" t="n">
         <v>144</v>
@@ -13529,7 +13533,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T145" s="4" t="inlineStr">
@@ -13544,7 +13548,7 @@
       </c>
       <c r="V145" s="4" t="inlineStr"/>
     </row>
-    <row r="146" ht="88" customHeight="1">
+    <row r="146" ht="107" customHeight="1">
       <c r="A146" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -13555,12 +13559,12 @@
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L018-F024-W</t>
+          <t>1G-GGRQ-GQ-L017-F024-W</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -13570,7 +13574,7 @@
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr"/>
@@ -13583,7 +13587,7 @@
       <c r="J146" s="2" t="inlineStr"/>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#018；位置：L018-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#017；位置：L017-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L146" s="2" t="inlineStr">
@@ -13593,7 +13597,7 @@
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R39#018</t>
+          <t>2026年1号机C修!R39#017</t>
         </is>
       </c>
       <c r="N146" s="2" t="inlineStr">
@@ -13605,7 +13609,7 @@
         <v>39</v>
       </c>
       <c r="P146" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q146" s="2" t="n">
         <v>145</v>
@@ -13617,7 +13621,7 @@
       </c>
       <c r="S146" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T146" s="2" t="inlineStr">
@@ -13632,7 +13636,7 @@
       </c>
       <c r="V146" s="2" t="inlineStr"/>
     </row>
-    <row r="147" ht="88" customHeight="1">
+    <row r="147" ht="107" customHeight="1">
       <c r="A147" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -13643,12 +13647,12 @@
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L019-F024-W</t>
+          <t>1G-GGRQ-GQ-L018-F024-W</t>
         </is>
       </c>
       <c r="E147" s="4" t="inlineStr">
@@ -13658,7 +13662,7 @@
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G147" s="4" t="inlineStr"/>
@@ -13671,7 +13675,7 @@
       <c r="J147" s="4" t="inlineStr"/>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#019；位置：L019-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#018；位置：L018-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L147" s="4" t="inlineStr">
@@ -13681,7 +13685,7 @@
       </c>
       <c r="M147" s="4" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R39#019</t>
+          <t>2026年1号机C修!R39#018</t>
         </is>
       </c>
       <c r="N147" s="4" t="inlineStr">
@@ -13693,7 +13697,7 @@
         <v>39</v>
       </c>
       <c r="P147" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q147" s="4" t="n">
         <v>146</v>
@@ -13705,7 +13709,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T147" s="4" t="inlineStr">
@@ -13720,7 +13724,7 @@
       </c>
       <c r="V147" s="4" t="inlineStr"/>
     </row>
-    <row r="148" ht="88" customHeight="1">
+    <row r="148" ht="107" customHeight="1">
       <c r="A148" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -13731,12 +13735,12 @@
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L020-F024-W</t>
+          <t>1G-GGRQ-GQ-L019-F024-W</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
@@ -13746,7 +13750,7 @@
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr"/>
@@ -13759,7 +13763,7 @@
       <c r="J148" s="2" t="inlineStr"/>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#020；位置：L020-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#019；位置：L019-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L148" s="2" t="inlineStr">
@@ -13769,7 +13773,7 @@
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R39#020</t>
+          <t>2026年1号机C修!R39#019</t>
         </is>
       </c>
       <c r="N148" s="2" t="inlineStr">
@@ -13781,7 +13785,7 @@
         <v>39</v>
       </c>
       <c r="P148" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q148" s="2" t="n">
         <v>147</v>
@@ -13793,7 +13797,7 @@
       </c>
       <c r="S148" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T148" s="2" t="inlineStr">
@@ -13808,7 +13812,7 @@
       </c>
       <c r="V148" s="2" t="inlineStr"/>
     </row>
-    <row r="149" ht="88" customHeight="1">
+    <row r="149" ht="107" customHeight="1">
       <c r="A149" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -13819,12 +13823,12 @@
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L021-F024-W</t>
+          <t>1G-GGRQ-GQ-L020-F024-W</t>
         </is>
       </c>
       <c r="E149" s="4" t="inlineStr">
@@ -13834,7 +13838,7 @@
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G149" s="4" t="inlineStr"/>
@@ -13847,7 +13851,7 @@
       <c r="J149" s="4" t="inlineStr"/>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#021；位置：L021-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#020；位置：L020-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L149" s="4" t="inlineStr">
@@ -13857,7 +13861,7 @@
       </c>
       <c r="M149" s="4" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R39#021</t>
+          <t>2026年1号机C修!R39#020</t>
         </is>
       </c>
       <c r="N149" s="4" t="inlineStr">
@@ -13869,7 +13873,7 @@
         <v>39</v>
       </c>
       <c r="P149" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q149" s="4" t="n">
         <v>148</v>
@@ -13881,7 +13885,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T149" s="4" t="inlineStr">
@@ -13896,7 +13900,7 @@
       </c>
       <c r="V149" s="4" t="inlineStr"/>
     </row>
-    <row r="150" ht="88" customHeight="1">
+    <row r="150" ht="107" customHeight="1">
       <c r="A150" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -13907,12 +13911,12 @@
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L022-F024-W</t>
+          <t>1G-GGRQ-GQ-L021-F024-W</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
@@ -13922,7 +13926,7 @@
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr"/>
@@ -13935,7 +13939,7 @@
       <c r="J150" s="2" t="inlineStr"/>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#022；位置：L022-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#021；位置：L021-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L150" s="2" t="inlineStr">
@@ -13945,7 +13949,7 @@
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R39#022</t>
+          <t>2026年1号机C修!R39#021</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr">
@@ -13957,7 +13961,7 @@
         <v>39</v>
       </c>
       <c r="P150" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q150" s="2" t="n">
         <v>149</v>
@@ -13969,7 +13973,7 @@
       </c>
       <c r="S150" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T150" s="2" t="inlineStr">
@@ -13984,7 +13988,7 @@
       </c>
       <c r="V150" s="2" t="inlineStr"/>
     </row>
-    <row r="151" ht="88" customHeight="1">
+    <row r="151" ht="107" customHeight="1">
       <c r="A151" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -13995,12 +13999,12 @@
       </c>
       <c r="C151" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L023-F024-W</t>
+          <t>1G-GGRQ-GQ-L022-F024-W</t>
         </is>
       </c>
       <c r="E151" s="4" t="inlineStr">
@@ -14010,7 +14014,7 @@
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G151" s="4" t="inlineStr"/>
@@ -14023,7 +14027,7 @@
       <c r="J151" s="4" t="inlineStr"/>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#023；位置：L023-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#022；位置：L022-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L151" s="4" t="inlineStr">
@@ -14033,7 +14037,7 @@
       </c>
       <c r="M151" s="4" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R39#023</t>
+          <t>2026年1号机C修!R39#022</t>
         </is>
       </c>
       <c r="N151" s="4" t="inlineStr">
@@ -14045,7 +14049,7 @@
         <v>39</v>
       </c>
       <c r="P151" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q151" s="4" t="n">
         <v>150</v>
@@ -14057,7 +14061,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T151" s="4" t="inlineStr">
@@ -14072,7 +14076,7 @@
       </c>
       <c r="V151" s="4" t="inlineStr"/>
     </row>
-    <row r="152" ht="88" customHeight="1">
+    <row r="152" ht="107" customHeight="1">
       <c r="A152" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -14083,12 +14087,12 @@
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L024-F024-W</t>
+          <t>1G-GGRQ-GQ-L023-F024-W</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
@@ -14098,7 +14102,7 @@
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr"/>
@@ -14111,7 +14115,7 @@
       <c r="J152" s="2" t="inlineStr"/>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#024；位置：L024-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#023；位置：L023-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L152" s="2" t="inlineStr">
@@ -14121,7 +14125,7 @@
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R39#024</t>
+          <t>2026年1号机C修!R39#023</t>
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr">
@@ -14133,7 +14137,7 @@
         <v>39</v>
       </c>
       <c r="P152" s="2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q152" s="2" t="n">
         <v>151</v>
@@ -14145,7 +14149,7 @@
       </c>
       <c r="S152" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T152" s="2" t="inlineStr">
@@ -14160,7 +14164,7 @@
       </c>
       <c r="V152" s="2" t="inlineStr"/>
     </row>
-    <row r="153" ht="88" customHeight="1">
+    <row r="153" ht="107" customHeight="1">
       <c r="A153" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -14171,12 +14175,12 @@
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L025-F024-W</t>
+          <t>1G-GGRQ-GQ-L024-F024-W</t>
         </is>
       </c>
       <c r="E153" s="4" t="inlineStr">
@@ -14186,7 +14190,7 @@
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G153" s="4" t="inlineStr"/>
@@ -14199,7 +14203,7 @@
       <c r="J153" s="4" t="inlineStr"/>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#025；位置：L025-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#024；位置：L024-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L153" s="4" t="inlineStr">
@@ -14209,7 +14213,7 @@
       </c>
       <c r="M153" s="4" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R39#025</t>
+          <t>2026年1号机C修!R39#024</t>
         </is>
       </c>
       <c r="N153" s="4" t="inlineStr">
@@ -14221,7 +14225,7 @@
         <v>39</v>
       </c>
       <c r="P153" s="4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q153" s="4" t="n">
         <v>152</v>
@@ -14233,7 +14237,7 @@
       </c>
       <c r="S153" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T153" s="4" t="inlineStr">
@@ -14248,7 +14252,7 @@
       </c>
       <c r="V153" s="4" t="inlineStr"/>
     </row>
-    <row r="154" ht="88" customHeight="1">
+    <row r="154" ht="107" customHeight="1">
       <c r="A154" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -14259,12 +14263,12 @@
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L026-F024-W</t>
+          <t>1G-GGRQ-GQ-L025-F024-W</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
@@ -14274,7 +14278,7 @@
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr"/>
@@ -14287,7 +14291,7 @@
       <c r="J154" s="2" t="inlineStr"/>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#026；位置：L026-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#025；位置：L025-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L154" s="2" t="inlineStr">
@@ -14297,7 +14301,7 @@
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R39#026</t>
+          <t>2026年1号机C修!R39#025</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
@@ -14309,7 +14313,7 @@
         <v>39</v>
       </c>
       <c r="P154" s="2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q154" s="2" t="n">
         <v>153</v>
@@ -14321,7 +14325,7 @@
       </c>
       <c r="S154" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T154" s="2" t="inlineStr">
@@ -14336,7 +14340,7 @@
       </c>
       <c r="V154" s="2" t="inlineStr"/>
     </row>
-    <row r="155" ht="88" customHeight="1">
+    <row r="155" ht="107" customHeight="1">
       <c r="A155" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -14347,12 +14351,12 @@
       </c>
       <c r="C155" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L027-F024-W</t>
+          <t>1G-GGRQ-GQ-L026-F024-W</t>
         </is>
       </c>
       <c r="E155" s="4" t="inlineStr">
@@ -14362,7 +14366,7 @@
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G155" s="4" t="inlineStr"/>
@@ -14375,7 +14379,7 @@
       <c r="J155" s="4" t="inlineStr"/>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#027；位置：L027-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#026；位置：L026-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L155" s="4" t="inlineStr">
@@ -14385,7 +14389,7 @@
       </c>
       <c r="M155" s="4" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R39#027</t>
+          <t>2026年1号机C修!R39#026</t>
         </is>
       </c>
       <c r="N155" s="4" t="inlineStr">
@@ -14397,7 +14401,7 @@
         <v>39</v>
       </c>
       <c r="P155" s="4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q155" s="4" t="n">
         <v>154</v>
@@ -14409,7 +14413,7 @@
       </c>
       <c r="S155" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T155" s="4" t="inlineStr">
@@ -14424,7 +14428,7 @@
       </c>
       <c r="V155" s="4" t="inlineStr"/>
     </row>
-    <row r="156" ht="88" customHeight="1">
+    <row r="156" ht="107" customHeight="1">
       <c r="A156" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -14435,12 +14439,12 @@
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L028-F024-W</t>
+          <t>1G-GGRQ-GQ-L027-F024-W</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
@@ -14450,7 +14454,7 @@
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr"/>
@@ -14463,7 +14467,7 @@
       <c r="J156" s="2" t="inlineStr"/>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#028；位置：L028-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#027；位置：L027-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L156" s="2" t="inlineStr">
@@ -14473,7 +14477,7 @@
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R39#028</t>
+          <t>2026年1号机C修!R39#027</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
@@ -14485,7 +14489,7 @@
         <v>39</v>
       </c>
       <c r="P156" s="2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Q156" s="2" t="n">
         <v>155</v>
@@ -14497,7 +14501,7 @@
       </c>
       <c r="S156" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T156" s="2" t="inlineStr">
@@ -14512,7 +14516,7 @@
       </c>
       <c r="V156" s="2" t="inlineStr"/>
     </row>
-    <row r="157" ht="88" customHeight="1">
+    <row r="157" ht="107" customHeight="1">
       <c r="A157" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -14523,12 +14527,12 @@
       </c>
       <c r="C157" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L029-F024-W</t>
+          <t>1G-GGRQ-GQ-L028-F024-W</t>
         </is>
       </c>
       <c r="E157" s="4" t="inlineStr">
@@ -14538,7 +14542,7 @@
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G157" s="4" t="inlineStr"/>
@@ -14551,7 +14555,7 @@
       <c r="J157" s="4" t="inlineStr"/>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#029；位置：L029-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#028；位置：L028-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L157" s="4" t="inlineStr">
@@ -14561,7 +14565,7 @@
       </c>
       <c r="M157" s="4" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R39#029</t>
+          <t>2026年1号机C修!R39#028</t>
         </is>
       </c>
       <c r="N157" s="4" t="inlineStr">
@@ -14573,7 +14577,7 @@
         <v>39</v>
       </c>
       <c r="P157" s="4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Q157" s="4" t="n">
         <v>156</v>
@@ -14585,7 +14589,7 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T157" s="4" t="inlineStr">
@@ -14600,7 +14604,7 @@
       </c>
       <c r="V157" s="4" t="inlineStr"/>
     </row>
-    <row r="158" ht="88" customHeight="1">
+    <row r="158" ht="107" customHeight="1">
       <c r="A158" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -14611,12 +14615,12 @@
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L030-F024-W</t>
+          <t>1G-GGRQ-GQ-L029-F024-W</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
@@ -14626,7 +14630,7 @@
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr"/>
@@ -14639,7 +14643,7 @@
       <c r="J158" s="2" t="inlineStr"/>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#030；位置：L030-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#029；位置：L029-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L158" s="2" t="inlineStr">
@@ -14649,7 +14653,7 @@
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R39#030</t>
+          <t>2026年1号机C修!R39#029</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
@@ -14661,7 +14665,7 @@
         <v>39</v>
       </c>
       <c r="P158" s="2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q158" s="2" t="n">
         <v>157</v>
@@ -14673,7 +14677,7 @@
       </c>
       <c r="S158" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T158" s="2" t="inlineStr">
@@ -14688,7 +14692,7 @@
       </c>
       <c r="V158" s="2" t="inlineStr"/>
     </row>
-    <row r="159" ht="88" customHeight="1">
+    <row r="159" ht="107" customHeight="1">
       <c r="A159" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -14699,12 +14703,12 @@
       </c>
       <c r="C159" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F024-W</t>
+          <t>1G-GGRQ-GQ-L030-F024-W</t>
         </is>
       </c>
       <c r="E159" s="4" t="inlineStr">
@@ -14714,7 +14718,7 @@
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G159" s="4" t="inlineStr"/>
@@ -14727,7 +14731,7 @@
       <c r="J159" s="4" t="inlineStr"/>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#031；位置：L031-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#030；位置：L030-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L159" s="4" t="inlineStr">
@@ -14737,7 +14741,7 @@
       </c>
       <c r="M159" s="4" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R39#031</t>
+          <t>2026年1号机C修!R39#030</t>
         </is>
       </c>
       <c r="N159" s="4" t="inlineStr">
@@ -14749,7 +14753,7 @@
         <v>39</v>
       </c>
       <c r="P159" s="4" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q159" s="4" t="n">
         <v>158</v>
@@ -14761,7 +14765,7 @@
       </c>
       <c r="S159" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T159" s="4" t="inlineStr">
@@ -14776,7 +14780,7 @@
       </c>
       <c r="V159" s="4" t="inlineStr"/>
     </row>
-    <row r="160" ht="88" customHeight="1">
+    <row r="160" ht="107" customHeight="1">
       <c r="A160" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -14787,12 +14791,12 @@
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L032-F024-W</t>
+          <t>1G-GGRQ-GQ-L031-F024-W</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
@@ -14802,7 +14806,7 @@
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr"/>
@@ -14815,7 +14819,7 @@
       <c r="J160" s="2" t="inlineStr"/>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#032；位置：L032-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#031；位置：L031-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L160" s="2" t="inlineStr">
@@ -14825,7 +14829,7 @@
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>2026年1号机C修!R39#032</t>
+          <t>2026年1号机C修!R39#031</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
@@ -14837,7 +14841,7 @@
         <v>39</v>
       </c>
       <c r="P160" s="2" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Q160" s="2" t="n">
         <v>159</v>
@@ -14849,7 +14853,7 @@
       </c>
       <c r="S160" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T160" s="2" t="inlineStr">
@@ -14864,8 +14868,96 @@
       </c>
       <c r="V160" s="2" t="inlineStr"/>
     </row>
+    <row r="161" ht="107" customHeight="1">
+      <c r="A161" s="4" t="inlineStr">
+        <is>
+          <t>事件</t>
+        </is>
+      </c>
+      <c r="B161" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C161" s="5" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="D161" s="4" t="inlineStr">
+        <is>
+          <t>1G-GGRQ-GQ-L032-F024-W</t>
+        </is>
+      </c>
+      <c r="E161" s="4" t="inlineStr">
+        <is>
+          <t>Φ54×7.5</t>
+        </is>
+      </c>
+      <c r="F161" s="4" t="inlineStr">
+        <is>
+          <t>SA-213TP347H</t>
+        </is>
+      </c>
+      <c r="G161" s="4" t="inlineStr"/>
+      <c r="H161" s="4" t="inlineStr"/>
+      <c r="I161" s="4" t="inlineStr">
+        <is>
+          <t>无损检测</t>
+        </is>
+      </c>
+      <c r="J161" s="4" t="inlineStr"/>
+      <c r="K161" s="4" t="inlineStr">
+        <is>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#032；位置：L032-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+        </is>
+      </c>
+      <c r="L161" s="4" t="inlineStr">
+        <is>
+          <t>2026年1号机C修</t>
+        </is>
+      </c>
+      <c r="M161" s="4" t="inlineStr">
+        <is>
+          <t>2026年1号机C修!R39#032</t>
+        </is>
+      </c>
+      <c r="N161" s="4" t="inlineStr">
+        <is>
+          <t>2026年1号机C修</t>
+        </is>
+      </c>
+      <c r="O161" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="P161" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q161" s="4" t="n">
+        <v>160</v>
+      </c>
+      <c r="R161" s="4" t="inlineStr">
+        <is>
+          <t>汇总展开</t>
+        </is>
+      </c>
+      <c r="S161" s="4" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="T161" s="4" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+      <c r="U161" s="4" t="inlineStr">
+        <is>
+          <t>原文合格</t>
+        </is>
+      </c>
+      <c r="V161" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V160"/>
+  <autoFilter ref="A1:V161"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/data-cleaning/verified/导入_2026年1号机C修.xlsx
+++ b/data-cleaning/verified/导入_2026年1号机C修.xlsx
@@ -718,7 +718,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr"/>
@@ -731,7 +731,7 @@
       <c r="J3" s="4" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#002；位置：L002-F005；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F005=炉后第20弯头→T91</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#002；位置：L002-F005；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F005=炉后第20弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -810,7 +810,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
@@ -823,7 +823,7 @@
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#003；位置：L002-F006；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F006=炉后第19弯头→T91</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#003；位置：L002-F006；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F006=炉后第19弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr"/>
@@ -915,7 +915,7 @@
       <c r="J5" s="4" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#004；位置：L002-F007；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F007=炉后第18弯头→T91</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#004；位置：L002-F007；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F007=炉后第18弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr"/>
@@ -1651,7 +1651,7 @@
       <c r="J13" s="4" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#012；位置：L002-F018；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F018=炉后第7弯头→T91</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#012；位置：L002-F018；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F018=炉后第7弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
@@ -1743,7 +1743,7 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#013；位置：L002-F019；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F019=炉后第6弯头→T91</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#013；位置：L002-F019；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F019=炉后第6弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr"/>
@@ -1835,7 +1835,7 @@
       <c r="J15" s="4" t="inlineStr"/>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#014；位置：L002-F020；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F020=炉后第5弯头→T91</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#014；位置：L002-F020；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F020=炉后第5弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr"/>
@@ -2203,7 +2203,7 @@
       <c r="J19" s="4" t="inlineStr"/>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#002；位置：L031-F005；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F005=炉后第20弯头→T91</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#002；位置：L031-F005；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F005=炉后第20弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
@@ -2295,7 +2295,7 @@
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#003；位置：L031-F006；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F006=炉后第19弯头→T91</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#003；位置：L031-F006；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F006=炉后第19弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr"/>
@@ -2387,7 +2387,7 @@
       <c r="J21" s="4" t="inlineStr"/>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#004；位置：L031-F007；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F007=炉后第18弯头→T91</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#004；位置：L031-F007；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F007=炉后第18弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
@@ -3110,7 +3110,7 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr"/>
@@ -3123,7 +3123,7 @@
       <c r="J29" s="4" t="inlineStr"/>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#012；位置：L031-F018；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F018=炉后第7弯头→T91</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#012；位置：L031-F018；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F018=炉后第7弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
@@ -3215,7 +3215,7 @@
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#013；位置：L031-F019；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F019=炉后第6弯头→T91</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#013；位置：L031-F019；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F019=炉后第6弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>T91</t>
+          <t>SA-213T91</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr"/>
@@ -3307,7 +3307,7 @@
       <c r="J31" s="4" t="inlineStr"/>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#014；位置：L031-F020；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F020=炉后第5弯头→T91</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#014；位置：L031-F020；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按管位区带映射：F020=炉后第5弯头→SA-213T91</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
@@ -6488,7 +6488,7 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="88" customHeight="1">
+    <row r="66" ht="107" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6509,7 +6509,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -6527,7 +6527,7 @@
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#001；位置：L001-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#001；位置：L001-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="V66" s="2" t="inlineStr"/>
     </row>
-    <row r="67" ht="88" customHeight="1">
+    <row r="67" ht="107" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6597,7 +6597,7 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
@@ -6615,7 +6615,7 @@
       <c r="J67" s="4" t="inlineStr"/>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#002；位置：L001-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#002；位置：L001-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L67" s="4" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="V67" s="4" t="inlineStr"/>
     </row>
-    <row r="68" ht="88" customHeight="1">
+    <row r="68" ht="107" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6685,7 +6685,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -6703,7 +6703,7 @@
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#003；位置：L002-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#003；位置：L002-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
@@ -6752,7 +6752,7 @@
       </c>
       <c r="V68" s="2" t="inlineStr"/>
     </row>
-    <row r="69" ht="88" customHeight="1">
+    <row r="69" ht="107" customHeight="1">
       <c r="A69" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6773,7 +6773,7 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
@@ -6791,7 +6791,7 @@
       <c r="J69" s="4" t="inlineStr"/>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#004；位置：L002-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#004；位置：L002-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L69" s="4" t="inlineStr">
@@ -6840,7 +6840,7 @@
       </c>
       <c r="V69" s="4" t="inlineStr"/>
     </row>
-    <row r="70" ht="88" customHeight="1">
+    <row r="70" ht="107" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6861,7 +6861,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -6879,7 +6879,7 @@
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#005；位置：L003-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#005；位置：L003-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="V70" s="2" t="inlineStr"/>
     </row>
-    <row r="71" ht="88" customHeight="1">
+    <row r="71" ht="107" customHeight="1">
       <c r="A71" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6949,7 +6949,7 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
@@ -6967,7 +6967,7 @@
       <c r="J71" s="4" t="inlineStr"/>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#006；位置：L003-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#006；位置：L003-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="V71" s="4" t="inlineStr"/>
     </row>
-    <row r="72" ht="88" customHeight="1">
+    <row r="72" ht="107" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7037,7 +7037,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -7055,7 +7055,7 @@
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#007；位置：L004-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#007；位置：L004-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
@@ -7104,7 +7104,7 @@
       </c>
       <c r="V72" s="2" t="inlineStr"/>
     </row>
-    <row r="73" ht="88" customHeight="1">
+    <row r="73" ht="107" customHeight="1">
       <c r="A73" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7125,7 +7125,7 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
@@ -7143,7 +7143,7 @@
       <c r="J73" s="4" t="inlineStr"/>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#008；位置：L004-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：发现异物，割开检查为氧化皮；结果性质：异常观察；仅转录异常观察，未新增质量合格/不合格判定或处置闭环</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#008；位置：L004-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：发现异物，割开检查为氧化皮；结果性质：异常观察；仅转录异常观察，未新增质量合格/不合格判定或处置闭环；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L73" s="4" t="inlineStr">
@@ -7196,7 +7196,7 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="88" customHeight="1">
+    <row r="74" ht="107" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7217,7 +7217,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -7235,7 +7235,7 @@
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#009；位置：L005-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：发现异物，割开检查为氧化皮；结果性质：异常观察；仅转录异常观察，未新增质量合格/不合格判定或处置闭环</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#009；位置：L005-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：发现异物，割开检查为氧化皮；结果性质：异常观察；仅转录异常观察，未新增质量合格/不合格判定或处置闭环；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
@@ -7288,7 +7288,7 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="88" customHeight="1">
+    <row r="75" ht="107" customHeight="1">
       <c r="A75" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7309,7 +7309,7 @@
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
@@ -7327,7 +7327,7 @@
       <c r="J75" s="4" t="inlineStr"/>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#010；位置：L005-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#010；位置：L005-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L75" s="4" t="inlineStr">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="V75" s="4" t="inlineStr"/>
     </row>
-    <row r="76" ht="88" customHeight="1">
+    <row r="76" ht="107" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7397,7 +7397,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -7415,7 +7415,7 @@
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#011；位置：L006-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#011；位置：L006-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="V76" s="2" t="inlineStr"/>
     </row>
-    <row r="77" ht="88" customHeight="1">
+    <row r="77" ht="107" customHeight="1">
       <c r="A77" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7485,7 +7485,7 @@
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
@@ -7503,7 +7503,7 @@
       <c r="J77" s="4" t="inlineStr"/>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#012；位置：L006-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#012；位置：L006-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L77" s="4" t="inlineStr">
@@ -7552,7 +7552,7 @@
       </c>
       <c r="V77" s="4" t="inlineStr"/>
     </row>
-    <row r="78" ht="88" customHeight="1">
+    <row r="78" ht="107" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7573,7 +7573,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -7591,7 +7591,7 @@
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#013；位置：L007-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#013；位置：L007-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
@@ -7640,7 +7640,7 @@
       </c>
       <c r="V78" s="2" t="inlineStr"/>
     </row>
-    <row r="79" ht="88" customHeight="1">
+    <row r="79" ht="107" customHeight="1">
       <c r="A79" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7661,7 +7661,7 @@
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
@@ -7679,7 +7679,7 @@
       <c r="J79" s="4" t="inlineStr"/>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#014；位置：L007-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#014；位置：L007-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L79" s="4" t="inlineStr">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="V79" s="4" t="inlineStr"/>
     </row>
-    <row r="80" ht="88" customHeight="1">
+    <row r="80" ht="107" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7749,7 +7749,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -7767,7 +7767,7 @@
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#015；位置：L008-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#015；位置：L008-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
@@ -7816,7 +7816,7 @@
       </c>
       <c r="V80" s="2" t="inlineStr"/>
     </row>
-    <row r="81" ht="88" customHeight="1">
+    <row r="81" ht="107" customHeight="1">
       <c r="A81" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7837,7 +7837,7 @@
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
@@ -7855,7 +7855,7 @@
       <c r="J81" s="4" t="inlineStr"/>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#016；位置：L008-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#016；位置：L008-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L81" s="4" t="inlineStr">
@@ -7904,7 +7904,7 @@
       </c>
       <c r="V81" s="4" t="inlineStr"/>
     </row>
-    <row r="82" ht="88" customHeight="1">
+    <row r="82" ht="107" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7925,7 +7925,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -7943,7 +7943,7 @@
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#017；位置：L009-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#017；位置：L009-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
@@ -7992,7 +7992,7 @@
       </c>
       <c r="V82" s="2" t="inlineStr"/>
     </row>
-    <row r="83" ht="88" customHeight="1">
+    <row r="83" ht="107" customHeight="1">
       <c r="A83" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8013,7 +8013,7 @@
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
@@ -8031,7 +8031,7 @@
       <c r="J83" s="4" t="inlineStr"/>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#018；位置：L009-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#018；位置：L009-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L83" s="4" t="inlineStr">
@@ -8080,7 +8080,7 @@
       </c>
       <c r="V83" s="4" t="inlineStr"/>
     </row>
-    <row r="84" ht="88" customHeight="1">
+    <row r="84" ht="107" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8101,7 +8101,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -8119,7 +8119,7 @@
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#019；位置：L010-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：发现异物，割开检查为氧化皮；结果性质：异常观察；仅转录异常观察，未新增质量合格/不合格判定或处置闭环</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#019；位置：L010-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：发现异物，割开检查为氧化皮；结果性质：异常观察；仅转录异常观察，未新增质量合格/不合格判定或处置闭环；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
@@ -8172,7 +8172,7 @@
         </is>
       </c>
     </row>
-    <row r="85" ht="88" customHeight="1">
+    <row r="85" ht="107" customHeight="1">
       <c r="A85" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8193,7 +8193,7 @@
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
@@ -8211,7 +8211,7 @@
       <c r="J85" s="4" t="inlineStr"/>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#020；位置：L010-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#020；位置：L010-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L85" s="4" t="inlineStr">
@@ -8260,7 +8260,7 @@
       </c>
       <c r="V85" s="4" t="inlineStr"/>
     </row>
-    <row r="86" ht="88" customHeight="1">
+    <row r="86" ht="107" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8281,7 +8281,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -8299,7 +8299,7 @@
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#021；位置：L011-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#021；位置：L011-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
@@ -8348,7 +8348,7 @@
       </c>
       <c r="V86" s="2" t="inlineStr"/>
     </row>
-    <row r="87" ht="88" customHeight="1">
+    <row r="87" ht="107" customHeight="1">
       <c r="A87" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8369,7 +8369,7 @@
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
@@ -8387,7 +8387,7 @@
       <c r="J87" s="4" t="inlineStr"/>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#022；位置：L011-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#022；位置：L011-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L87" s="4" t="inlineStr">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="V87" s="4" t="inlineStr"/>
     </row>
-    <row r="88" ht="88" customHeight="1">
+    <row r="88" ht="107" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8457,7 +8457,7 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
@@ -8475,7 +8475,7 @@
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#023；位置：L012-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#023；位置：L012-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="V88" s="2" t="inlineStr"/>
     </row>
-    <row r="89" ht="88" customHeight="1">
+    <row r="89" ht="107" customHeight="1">
       <c r="A89" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8545,7 +8545,7 @@
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
@@ -8563,7 +8563,7 @@
       <c r="J89" s="4" t="inlineStr"/>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#024；位置：L012-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#024；位置：L012-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L89" s="4" t="inlineStr">
@@ -8612,7 +8612,7 @@
       </c>
       <c r="V89" s="4" t="inlineStr"/>
     </row>
-    <row r="90" ht="88" customHeight="1">
+    <row r="90" ht="107" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
@@ -8651,7 +8651,7 @@
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#025；位置：L013-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：发现异物，割开检查为氧化皮；结果性质：异常观察；仅转录异常观察，未新增质量合格/不合格判定或处置闭环</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#025；位置：L013-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：发现异物，割开检查为氧化皮；结果性质：异常观察；仅转录异常观察，未新增质量合格/不合格判定或处置闭环；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
@@ -8704,7 +8704,7 @@
         </is>
       </c>
     </row>
-    <row r="91" ht="88" customHeight="1">
+    <row r="91" ht="107" customHeight="1">
       <c r="A91" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8725,7 +8725,7 @@
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
@@ -8743,7 +8743,7 @@
       <c r="J91" s="4" t="inlineStr"/>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#026；位置：L013-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#026；位置：L013-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L91" s="4" t="inlineStr">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="V91" s="4" t="inlineStr"/>
     </row>
-    <row r="92" ht="88" customHeight="1">
+    <row r="92" ht="107" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8813,7 +8813,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -8831,7 +8831,7 @@
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#027；位置：L014-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#027；位置：L014-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
@@ -8880,7 +8880,7 @@
       </c>
       <c r="V92" s="2" t="inlineStr"/>
     </row>
-    <row r="93" ht="88" customHeight="1">
+    <row r="93" ht="107" customHeight="1">
       <c r="A93" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8901,7 +8901,7 @@
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
@@ -8919,7 +8919,7 @@
       <c r="J93" s="4" t="inlineStr"/>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#028；位置：L014-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#028；位置：L014-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L93" s="4" t="inlineStr">
@@ -8968,7 +8968,7 @@
       </c>
       <c r="V93" s="4" t="inlineStr"/>
     </row>
-    <row r="94" ht="88" customHeight="1">
+    <row r="94" ht="107" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8989,7 +8989,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -9007,7 +9007,7 @@
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#029；位置：L015-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#029；位置：L015-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
@@ -9056,7 +9056,7 @@
       </c>
       <c r="V94" s="2" t="inlineStr"/>
     </row>
-    <row r="95" ht="88" customHeight="1">
+    <row r="95" ht="107" customHeight="1">
       <c r="A95" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9077,7 +9077,7 @@
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
@@ -9095,7 +9095,7 @@
       <c r="J95" s="4" t="inlineStr"/>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#030；位置：L015-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#030；位置：L015-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L95" s="4" t="inlineStr">
@@ -9144,7 +9144,7 @@
       </c>
       <c r="V95" s="4" t="inlineStr"/>
     </row>
-    <row r="96" ht="88" customHeight="1">
+    <row r="96" ht="107" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9165,7 +9165,7 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -9183,7 +9183,7 @@
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#031；位置：L016-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#031；位置：L016-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
@@ -9232,7 +9232,7 @@
       </c>
       <c r="V96" s="2" t="inlineStr"/>
     </row>
-    <row r="97" ht="88" customHeight="1">
+    <row r="97" ht="107" customHeight="1">
       <c r="A97" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9253,7 +9253,7 @@
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
@@ -9271,7 +9271,7 @@
       <c r="J97" s="4" t="inlineStr"/>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#032；位置：L016-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#032；位置：L016-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L97" s="4" t="inlineStr">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="V97" s="4" t="inlineStr"/>
     </row>
-    <row r="98" ht="88" customHeight="1">
+    <row r="98" ht="107" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -9359,7 +9359,7 @@
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#033；位置：L017-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#033；位置：L017-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
@@ -9408,7 +9408,7 @@
       </c>
       <c r="V98" s="2" t="inlineStr"/>
     </row>
-    <row r="99" ht="88" customHeight="1">
+    <row r="99" ht="107" customHeight="1">
       <c r="A99" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
@@ -9447,7 +9447,7 @@
       <c r="J99" s="4" t="inlineStr"/>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#034；位置：L017-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#034；位置：L017-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L99" s="4" t="inlineStr">
@@ -9496,7 +9496,7 @@
       </c>
       <c r="V99" s="4" t="inlineStr"/>
     </row>
-    <row r="100" ht="88" customHeight="1">
+    <row r="100" ht="107" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9517,7 +9517,7 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
@@ -9535,7 +9535,7 @@
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#035；位置：L018-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#035；位置：L018-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
@@ -9584,7 +9584,7 @@
       </c>
       <c r="V100" s="2" t="inlineStr"/>
     </row>
-    <row r="101" ht="88" customHeight="1">
+    <row r="101" ht="107" customHeight="1">
       <c r="A101" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9605,7 +9605,7 @@
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
@@ -9623,7 +9623,7 @@
       <c r="J101" s="4" t="inlineStr"/>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#036；位置：L018-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#036；位置：L018-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L101" s="4" t="inlineStr">
@@ -9672,7 +9672,7 @@
       </c>
       <c r="V101" s="4" t="inlineStr"/>
     </row>
-    <row r="102" ht="88" customHeight="1">
+    <row r="102" ht="107" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9693,7 +9693,7 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
@@ -9711,7 +9711,7 @@
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#037；位置：L019-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#037；位置：L019-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="V102" s="2" t="inlineStr"/>
     </row>
-    <row r="103" ht="88" customHeight="1">
+    <row r="103" ht="107" customHeight="1">
       <c r="A103" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9781,7 +9781,7 @@
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
@@ -9799,7 +9799,7 @@
       <c r="J103" s="4" t="inlineStr"/>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#038；位置：L019-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#038；位置：L019-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L103" s="4" t="inlineStr">
@@ -9848,7 +9848,7 @@
       </c>
       <c r="V103" s="4" t="inlineStr"/>
     </row>
-    <row r="104" ht="88" customHeight="1">
+    <row r="104" ht="107" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
@@ -9887,7 +9887,7 @@
       <c r="J104" s="2" t="inlineStr"/>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#039；位置：L020-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#039；位置：L020-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
@@ -9936,7 +9936,7 @@
       </c>
       <c r="V104" s="2" t="inlineStr"/>
     </row>
-    <row r="105" ht="88" customHeight="1">
+    <row r="105" ht="107" customHeight="1">
       <c r="A105" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9957,7 +9957,7 @@
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
@@ -9975,7 +9975,7 @@
       <c r="J105" s="4" t="inlineStr"/>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#040；位置：L020-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#040；位置：L020-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L105" s="4" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="V105" s="4" t="inlineStr"/>
     </row>
-    <row r="106" ht="88" customHeight="1">
+    <row r="106" ht="107" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10045,7 +10045,7 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
@@ -10063,7 +10063,7 @@
       <c r="J106" s="2" t="inlineStr"/>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#041；位置：L021-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#041；位置：L021-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L106" s="2" t="inlineStr">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="V106" s="2" t="inlineStr"/>
     </row>
-    <row r="107" ht="88" customHeight="1">
+    <row r="107" ht="107" customHeight="1">
       <c r="A107" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10133,7 +10133,7 @@
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
@@ -10151,7 +10151,7 @@
       <c r="J107" s="4" t="inlineStr"/>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#042；位置：L021-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#042；位置：L021-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L107" s="4" t="inlineStr">
@@ -10200,7 +10200,7 @@
       </c>
       <c r="V107" s="4" t="inlineStr"/>
     </row>
-    <row r="108" ht="88" customHeight="1">
+    <row r="108" ht="107" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10221,7 +10221,7 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
@@ -10239,7 +10239,7 @@
       <c r="J108" s="2" t="inlineStr"/>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#043；位置：L022-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#043；位置：L022-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L108" s="2" t="inlineStr">
@@ -10288,7 +10288,7 @@
       </c>
       <c r="V108" s="2" t="inlineStr"/>
     </row>
-    <row r="109" ht="88" customHeight="1">
+    <row r="109" ht="107" customHeight="1">
       <c r="A109" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10309,7 +10309,7 @@
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
@@ -10327,7 +10327,7 @@
       <c r="J109" s="4" t="inlineStr"/>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#044；位置：L022-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#044；位置：L022-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L109" s="4" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="V109" s="4" t="inlineStr"/>
     </row>
-    <row r="110" ht="88" customHeight="1">
+    <row r="110" ht="107" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10397,7 +10397,7 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
@@ -10415,7 +10415,7 @@
       <c r="J110" s="2" t="inlineStr"/>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#045；位置：L023-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#045；位置：L023-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L110" s="2" t="inlineStr">
@@ -10464,7 +10464,7 @@
       </c>
       <c r="V110" s="2" t="inlineStr"/>
     </row>
-    <row r="111" ht="88" customHeight="1">
+    <row r="111" ht="107" customHeight="1">
       <c r="A111" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10485,7 +10485,7 @@
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
@@ -10503,7 +10503,7 @@
       <c r="J111" s="4" t="inlineStr"/>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#046；位置：L023-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#046；位置：L023-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L111" s="4" t="inlineStr">
@@ -10552,7 +10552,7 @@
       </c>
       <c r="V111" s="4" t="inlineStr"/>
     </row>
-    <row r="112" ht="88" customHeight="1">
+    <row r="112" ht="107" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10573,7 +10573,7 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
@@ -10591,7 +10591,7 @@
       <c r="J112" s="2" t="inlineStr"/>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#047；位置：L024-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#047；位置：L024-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L112" s="2" t="inlineStr">
@@ -10640,7 +10640,7 @@
       </c>
       <c r="V112" s="2" t="inlineStr"/>
     </row>
-    <row r="113" ht="88" customHeight="1">
+    <row r="113" ht="107" customHeight="1">
       <c r="A113" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10661,7 +10661,7 @@
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
@@ -10679,7 +10679,7 @@
       <c r="J113" s="4" t="inlineStr"/>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#048；位置：L024-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#048；位置：L024-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L113" s="4" t="inlineStr">
@@ -10728,7 +10728,7 @@
       </c>
       <c r="V113" s="4" t="inlineStr"/>
     </row>
-    <row r="114" ht="88" customHeight="1">
+    <row r="114" ht="107" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10749,7 +10749,7 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
@@ -10767,7 +10767,7 @@
       <c r="J114" s="2" t="inlineStr"/>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#049；位置：L025-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：发现异物，割开检查为氧化皮；结果性质：异常观察；仅转录异常观察，未新增质量合格/不合格判定或处置闭环</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#049；位置：L025-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：发现异物，割开检查为氧化皮；结果性质：异常观察；仅转录异常观察，未新增质量合格/不合格判定或处置闭环；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L114" s="2" t="inlineStr">
@@ -10820,7 +10820,7 @@
         </is>
       </c>
     </row>
-    <row r="115" ht="88" customHeight="1">
+    <row r="115" ht="107" customHeight="1">
       <c r="A115" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10841,7 +10841,7 @@
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
@@ -10859,7 +10859,7 @@
       <c r="J115" s="4" t="inlineStr"/>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#050；位置：L025-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#050；位置：L025-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L115" s="4" t="inlineStr">
@@ -10908,7 +10908,7 @@
       </c>
       <c r="V115" s="4" t="inlineStr"/>
     </row>
-    <row r="116" ht="88" customHeight="1">
+    <row r="116" ht="107" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10929,7 +10929,7 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
@@ -10947,7 +10947,7 @@
       <c r="J116" s="2" t="inlineStr"/>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#051；位置：L026-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#051；位置：L026-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L116" s="2" t="inlineStr">
@@ -10996,7 +10996,7 @@
       </c>
       <c r="V116" s="2" t="inlineStr"/>
     </row>
-    <row r="117" ht="88" customHeight="1">
+    <row r="117" ht="107" customHeight="1">
       <c r="A117" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11017,7 +11017,7 @@
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
@@ -11035,7 +11035,7 @@
       <c r="J117" s="4" t="inlineStr"/>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#052；位置：L026-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#052；位置：L026-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L117" s="4" t="inlineStr">
@@ -11084,7 +11084,7 @@
       </c>
       <c r="V117" s="4" t="inlineStr"/>
     </row>
-    <row r="118" ht="88" customHeight="1">
+    <row r="118" ht="107" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11105,7 +11105,7 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
@@ -11123,7 +11123,7 @@
       <c r="J118" s="2" t="inlineStr"/>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#053；位置：L027-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#053；位置：L027-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L118" s="2" t="inlineStr">
@@ -11172,7 +11172,7 @@
       </c>
       <c r="V118" s="2" t="inlineStr"/>
     </row>
-    <row r="119" ht="88" customHeight="1">
+    <row r="119" ht="107" customHeight="1">
       <c r="A119" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11193,7 +11193,7 @@
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
@@ -11211,7 +11211,7 @@
       <c r="J119" s="4" t="inlineStr"/>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#054；位置：L027-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#054；位置：L027-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L119" s="4" t="inlineStr">
@@ -11260,7 +11260,7 @@
       </c>
       <c r="V119" s="4" t="inlineStr"/>
     </row>
-    <row r="120" ht="88" customHeight="1">
+    <row r="120" ht="107" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11281,7 +11281,7 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
@@ -11299,7 +11299,7 @@
       <c r="J120" s="2" t="inlineStr"/>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#055；位置：L028-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#055；位置：L028-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L120" s="2" t="inlineStr">
@@ -11348,7 +11348,7 @@
       </c>
       <c r="V120" s="2" t="inlineStr"/>
     </row>
-    <row r="121" ht="88" customHeight="1">
+    <row r="121" ht="107" customHeight="1">
       <c r="A121" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11369,7 +11369,7 @@
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
@@ -11387,7 +11387,7 @@
       <c r="J121" s="4" t="inlineStr"/>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#056；位置：L028-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#056；位置：L028-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L121" s="4" t="inlineStr">
@@ -11436,7 +11436,7 @@
       </c>
       <c r="V121" s="4" t="inlineStr"/>
     </row>
-    <row r="122" ht="88" customHeight="1">
+    <row r="122" ht="107" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11457,7 +11457,7 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
@@ -11475,7 +11475,7 @@
       <c r="J122" s="2" t="inlineStr"/>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#057；位置：L029-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#057；位置：L029-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L122" s="2" t="inlineStr">
@@ -11524,7 +11524,7 @@
       </c>
       <c r="V122" s="2" t="inlineStr"/>
     </row>
-    <row r="123" ht="88" customHeight="1">
+    <row r="123" ht="107" customHeight="1">
       <c r="A123" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11545,7 +11545,7 @@
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
@@ -11563,7 +11563,7 @@
       <c r="J123" s="4" t="inlineStr"/>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#058；位置：L029-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#058；位置：L029-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L123" s="4" t="inlineStr">
@@ -11612,7 +11612,7 @@
       </c>
       <c r="V123" s="4" t="inlineStr"/>
     </row>
-    <row r="124" ht="88" customHeight="1">
+    <row r="124" ht="107" customHeight="1">
       <c r="A124" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11633,7 +11633,7 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
@@ -11651,7 +11651,7 @@
       <c r="J124" s="2" t="inlineStr"/>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#059；位置：L030-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#059；位置：L030-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L124" s="2" t="inlineStr">
@@ -11700,7 +11700,7 @@
       </c>
       <c r="V124" s="2" t="inlineStr"/>
     </row>
-    <row r="125" ht="88" customHeight="1">
+    <row r="125" ht="107" customHeight="1">
       <c r="A125" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11721,7 +11721,7 @@
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
@@ -11739,7 +11739,7 @@
       <c r="J125" s="4" t="inlineStr"/>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#060；位置：L030-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#060；位置：L030-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L125" s="4" t="inlineStr">
@@ -11788,7 +11788,7 @@
       </c>
       <c r="V125" s="4" t="inlineStr"/>
     </row>
-    <row r="126" ht="88" customHeight="1">
+    <row r="126" ht="107" customHeight="1">
       <c r="A126" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
@@ -11827,7 +11827,7 @@
       <c r="J126" s="2" t="inlineStr"/>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#061；位置：L031-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#061；位置：L031-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L126" s="2" t="inlineStr">
@@ -11876,7 +11876,7 @@
       </c>
       <c r="V126" s="2" t="inlineStr"/>
     </row>
-    <row r="127" ht="88" customHeight="1">
+    <row r="127" ht="107" customHeight="1">
       <c r="A127" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11897,7 +11897,7 @@
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
@@ -11915,7 +11915,7 @@
       <c r="J127" s="4" t="inlineStr"/>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#062；位置：L031-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#062；位置：L031-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L127" s="4" t="inlineStr">
@@ -11964,7 +11964,7 @@
       </c>
       <c r="V127" s="4" t="inlineStr"/>
     </row>
-    <row r="128" ht="88" customHeight="1">
+    <row r="128" ht="107" customHeight="1">
       <c r="A128" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11985,7 +11985,7 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
@@ -12003,7 +12003,7 @@
       <c r="J128" s="2" t="inlineStr"/>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#063；位置：L032-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#063；位置：L032-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L128" s="2" t="inlineStr">
@@ -12052,7 +12052,7 @@
       </c>
       <c r="V128" s="2" t="inlineStr"/>
     </row>
-    <row r="129" ht="88" customHeight="1">
+    <row r="129" ht="107" customHeight="1">
       <c r="A129" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -12073,7 +12073,7 @@
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
@@ -12091,7 +12091,7 @@
       <c r="J129" s="4" t="inlineStr"/>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#064；位置：L032-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#064；位置：L032-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L129" s="4" t="inlineStr">

--- a/data-cleaning/verified/导入_2026年1号机C修.xlsx
+++ b/data-cleaning/verified/导入_2026年1号机C修.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="126" customHeight="1">
+    <row r="2" ht="32" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -600,7 +600,7 @@
       <c r="J2" s="1" t="inlineStr"/>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#001；位置：L002-F004；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F004=回路4底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr">
@@ -653,7 +653,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="126" customHeight="1">
+    <row r="3" ht="32" customHeight="1">
       <c r="A3" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -692,7 +692,7 @@
       <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#002；位置：L002-F005；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F005=回路5底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr">
@@ -745,7 +745,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="126" customHeight="1">
+    <row r="4" ht="32" customHeight="1">
       <c r="A4" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -784,7 +784,7 @@
       <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#003；位置：L002-F006；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F006=回路6底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr">
@@ -837,7 +837,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="126" customHeight="1">
+    <row r="5" ht="32" customHeight="1">
       <c r="A5" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -876,7 +876,7 @@
       <c r="J5" s="1" t="inlineStr"/>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#004；位置：L002-F007；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F007=回路7底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr">
@@ -929,7 +929,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="126" customHeight="1">
+    <row r="6" ht="32" customHeight="1">
       <c r="A6" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -968,7 +968,7 @@
       <c r="J6" s="1" t="inlineStr"/>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#005；位置：L002-F008；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F008=回路8底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr">
@@ -1021,7 +1021,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="126" customHeight="1">
+    <row r="7" ht="32" customHeight="1">
       <c r="A7" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1060,7 +1060,7 @@
       <c r="J7" s="1" t="inlineStr"/>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#006；位置：L002-F009；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F009=回路9底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr">
@@ -1113,7 +1113,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="126" customHeight="1">
+    <row r="8" ht="32" customHeight="1">
       <c r="A8" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1152,7 +1152,7 @@
       <c r="J8" s="1" t="inlineStr"/>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#007；位置：L002-F010；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F010=回路10底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr">
@@ -1205,7 +1205,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="126" customHeight="1">
+    <row r="9" ht="32" customHeight="1">
       <c r="A9" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1244,7 +1244,7 @@
       <c r="J9" s="1" t="inlineStr"/>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#008；位置：L002-F014；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F014=回路11底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L9" s="1" t="inlineStr">
@@ -1297,7 +1297,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="126" customHeight="1">
+    <row r="10" ht="32" customHeight="1">
       <c r="A10" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1336,7 +1336,7 @@
       <c r="J10" s="1" t="inlineStr"/>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#009；位置：L002-F015；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F015=回路10底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L10" s="1" t="inlineStr">
@@ -1389,7 +1389,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="126" customHeight="1">
+    <row r="11" ht="32" customHeight="1">
       <c r="A11" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1428,7 +1428,7 @@
       <c r="J11" s="1" t="inlineStr"/>
       <c r="K11" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#010；位置：L002-F016；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F016=回路9底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L11" s="1" t="inlineStr">
@@ -1481,7 +1481,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="126" customHeight="1">
+    <row r="12" ht="32" customHeight="1">
       <c r="A12" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1520,7 +1520,7 @@
       <c r="J12" s="1" t="inlineStr"/>
       <c r="K12" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#011；位置：L002-F017；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F017=回路8底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L12" s="1" t="inlineStr">
@@ -1573,7 +1573,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="126" customHeight="1">
+    <row r="13" ht="32" customHeight="1">
       <c r="A13" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1612,7 +1612,7 @@
       <c r="J13" s="1" t="inlineStr"/>
       <c r="K13" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#012；位置：L002-F018；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F018=回路7底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L13" s="1" t="inlineStr">
@@ -1665,7 +1665,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="126" customHeight="1">
+    <row r="14" ht="32" customHeight="1">
       <c r="A14" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1704,7 +1704,7 @@
       <c r="J14" s="1" t="inlineStr"/>
       <c r="K14" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#013；位置：L002-F019；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F019=回路6底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L14" s="1" t="inlineStr">
@@ -1757,7 +1757,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="126" customHeight="1">
+    <row r="15" ht="32" customHeight="1">
       <c r="A15" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1796,7 +1796,7 @@
       <c r="J15" s="1" t="inlineStr"/>
       <c r="K15" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#014；位置：L002-F020；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F020=回路5底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L15" s="1" t="inlineStr">
@@ -1849,7 +1849,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="126" customHeight="1">
+    <row r="16" ht="32" customHeight="1">
       <c r="A16" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1888,7 +1888,7 @@
       <c r="J16" s="1" t="inlineStr"/>
       <c r="K16" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#015；位置：L002-F021；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F021=回路4底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L16" s="1" t="inlineStr">
@@ -1941,7 +1941,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="126" customHeight="1">
+    <row r="17" ht="32" customHeight="1">
       <c r="A17" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1980,7 +1980,7 @@
       <c r="J17" s="1" t="inlineStr"/>
       <c r="K17" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R4#016；位置：L002-F022；源位置：1号炉炉左至炉右第2屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F022=回路3底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L17" s="1" t="inlineStr">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="126" customHeight="1">
+    <row r="18" ht="32" customHeight="1">
       <c r="A18" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2072,7 +2072,7 @@
       <c r="J18" s="1" t="inlineStr"/>
       <c r="K18" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#001；位置：L031-F004；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F004=回路4底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L18" s="1" t="inlineStr">
@@ -2125,7 +2125,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="126" customHeight="1">
+    <row r="19" ht="32" customHeight="1">
       <c r="A19" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2164,7 +2164,7 @@
       <c r="J19" s="1" t="inlineStr"/>
       <c r="K19" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#002；位置：L031-F005；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F005=回路5底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L19" s="1" t="inlineStr">
@@ -2217,7 +2217,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="126" customHeight="1">
+    <row r="20" ht="32" customHeight="1">
       <c r="A20" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2256,7 +2256,7 @@
       <c r="J20" s="1" t="inlineStr"/>
       <c r="K20" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#003；位置：L031-F006；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F006=回路6底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L20" s="1" t="inlineStr">
@@ -2309,7 +2309,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="126" customHeight="1">
+    <row r="21" ht="32" customHeight="1">
       <c r="A21" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2348,7 +2348,7 @@
       <c r="J21" s="1" t="inlineStr"/>
       <c r="K21" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#004；位置：L031-F007；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F007=回路7底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L21" s="1" t="inlineStr">
@@ -2401,7 +2401,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="126" customHeight="1">
+    <row r="22" ht="32" customHeight="1">
       <c r="A22" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2440,7 +2440,7 @@
       <c r="J22" s="1" t="inlineStr"/>
       <c r="K22" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#005；位置：L031-F008；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F008=回路8底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L22" s="1" t="inlineStr">
@@ -2493,7 +2493,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="126" customHeight="1">
+    <row r="23" ht="32" customHeight="1">
       <c r="A23" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2532,7 +2532,7 @@
       <c r="J23" s="1" t="inlineStr"/>
       <c r="K23" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#006；位置：L031-F009；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F009=回路9底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L23" s="1" t="inlineStr">
@@ -2585,7 +2585,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="126" customHeight="1">
+    <row r="24" ht="32" customHeight="1">
       <c r="A24" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2624,7 +2624,7 @@
       <c r="J24" s="1" t="inlineStr"/>
       <c r="K24" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#007；位置：L031-F010；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F010=回路10底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L24" s="1" t="inlineStr">
@@ -2677,7 +2677,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="126" customHeight="1">
+    <row r="25" ht="32" customHeight="1">
       <c r="A25" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2716,7 +2716,7 @@
       <c r="J25" s="1" t="inlineStr"/>
       <c r="K25" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#008；位置：L031-F014；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F014=回路11底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L25" s="1" t="inlineStr">
@@ -2769,7 +2769,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="126" customHeight="1">
+    <row r="26" ht="32" customHeight="1">
       <c r="A26" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2808,7 +2808,7 @@
       <c r="J26" s="1" t="inlineStr"/>
       <c r="K26" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#009；位置：L031-F015；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F015=回路10底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L26" s="1" t="inlineStr">
@@ -2861,7 +2861,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="126" customHeight="1">
+    <row r="27" ht="32" customHeight="1">
       <c r="A27" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2900,7 +2900,7 @@
       <c r="J27" s="1" t="inlineStr"/>
       <c r="K27" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#010；位置：L031-F016；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F016=回路9底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L27" s="1" t="inlineStr">
@@ -2953,7 +2953,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="126" customHeight="1">
+    <row r="28" ht="32" customHeight="1">
       <c r="A28" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2992,7 +2992,7 @@
       <c r="J28" s="1" t="inlineStr"/>
       <c r="K28" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#011；位置：L031-F017；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F017=回路8底弯段→Φ51×9 12Cr1MoVG</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L28" s="1" t="inlineStr">
@@ -3045,7 +3045,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="126" customHeight="1">
+    <row r="29" ht="32" customHeight="1">
       <c r="A29" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3084,7 +3084,7 @@
       <c r="J29" s="1" t="inlineStr"/>
       <c r="K29" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#012；位置：L031-F018；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F018=回路7底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L29" s="1" t="inlineStr">
@@ -3137,7 +3137,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="126" customHeight="1">
+    <row r="30" ht="32" customHeight="1">
       <c r="A30" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3176,7 +3176,7 @@
       <c r="J30" s="1" t="inlineStr"/>
       <c r="K30" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#013；位置：L031-F019；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F019=回路6底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L30" s="1" t="inlineStr">
@@ -3229,7 +3229,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="126" customHeight="1">
+    <row r="31" ht="32" customHeight="1">
       <c r="A31" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3268,7 +3268,7 @@
       <c r="J31" s="1" t="inlineStr"/>
       <c r="K31" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#014；位置：L031-F020；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F020=回路5底弯段→Φ51×8 SA-213T91</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L31" s="1" t="inlineStr">
@@ -3321,7 +3321,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="126" customHeight="1">
+    <row r="32" ht="32" customHeight="1">
       <c r="A32" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3360,7 +3360,7 @@
       <c r="J32" s="1" t="inlineStr"/>
       <c r="K32" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#015；位置：L031-F021；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F021=回路4底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L32" s="1" t="inlineStr">
@@ -3413,7 +3413,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="126" customHeight="1">
+    <row r="33" ht="32" customHeight="1">
       <c r="A33" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3452,7 +3452,7 @@
       <c r="J33" s="1" t="inlineStr"/>
       <c r="K33" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R5#016；位置：L031-F022；源位置：1号炉炉左至炉右第31屏4/5/6/7/8/9/10/14/15/16/17/18/19/20/21/22根；方法：射线；结果：合格；结果性质：原文合格；原备注：W表示弯头,炉后往炉前数第1、24弯头为TP347H，2~4、21~23为为304H，5~7、12、13、18~20为T91，8、~11、14~17为12CrMoVG，12为T91。；材质按回路分段基准映射：F022=回路3底弯段→Φ51×8 SA-213TP304H</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L33" s="1" t="inlineStr">
@@ -3505,7 +3505,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="69" customHeight="1">
+    <row r="34" ht="32" customHeight="1">
       <c r="A34" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3544,7 +3544,7 @@
       <c r="J34" s="1" t="inlineStr"/>
       <c r="K34" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R6#001；位置：L001-F001；源位置：1号炉炉左至炉右第1屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L34" s="1" t="inlineStr">
@@ -3597,7 +3597,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="69" customHeight="1">
+    <row r="35" ht="32" customHeight="1">
       <c r="A35" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3636,7 +3636,7 @@
       <c r="J35" s="1" t="inlineStr"/>
       <c r="K35" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R7#001；位置：L002-F001；源位置：1号炉炉左至炉右第2屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L35" s="1" t="inlineStr">
@@ -3689,7 +3689,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="69" customHeight="1">
+    <row r="36" ht="32" customHeight="1">
       <c r="A36" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3728,7 +3728,7 @@
       <c r="J36" s="1" t="inlineStr"/>
       <c r="K36" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R8#001；位置：L003-F001；源位置：1号炉炉左至炉右第3屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L36" s="1" t="inlineStr">
@@ -3781,7 +3781,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="69" customHeight="1">
+    <row r="37" ht="32" customHeight="1">
       <c r="A37" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3820,7 +3820,7 @@
       <c r="J37" s="1" t="inlineStr"/>
       <c r="K37" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R9#001；位置：L004-F001；源位置：1号炉炉左至炉右第4屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L37" s="1" t="inlineStr">
@@ -3873,7 +3873,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="69" customHeight="1">
+    <row r="38" ht="32" customHeight="1">
       <c r="A38" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3912,7 +3912,7 @@
       <c r="J38" s="1" t="inlineStr"/>
       <c r="K38" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R10#001；位置：L005-F001；源位置：1号炉炉左至炉右第5屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L38" s="1" t="inlineStr">
@@ -3965,7 +3965,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="69" customHeight="1">
+    <row r="39" ht="32" customHeight="1">
       <c r="A39" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4004,7 +4004,7 @@
       <c r="J39" s="1" t="inlineStr"/>
       <c r="K39" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R11#001；位置：L006-F001；源位置：1号炉炉左至炉右第6屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L39" s="1" t="inlineStr">
@@ -4057,7 +4057,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="69" customHeight="1">
+    <row r="40" ht="32" customHeight="1">
       <c r="A40" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4096,7 +4096,7 @@
       <c r="J40" s="1" t="inlineStr"/>
       <c r="K40" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R12#001；位置：L007-F001；源位置：1号炉炉左至炉右第7屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L40" s="1" t="inlineStr">
@@ -4149,7 +4149,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="69" customHeight="1">
+    <row r="41" ht="32" customHeight="1">
       <c r="A41" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4188,7 +4188,7 @@
       <c r="J41" s="1" t="inlineStr"/>
       <c r="K41" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R13#001；位置：L008-F001；源位置：1号炉炉左至炉右第8屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L41" s="1" t="inlineStr">
@@ -4241,7 +4241,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="69" customHeight="1">
+    <row r="42" ht="32" customHeight="1">
       <c r="A42" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4280,7 +4280,7 @@
       <c r="J42" s="1" t="inlineStr"/>
       <c r="K42" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R14#001；位置：L009-F001；源位置：1号炉炉左至炉右第9屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L42" s="1" t="inlineStr">
@@ -4333,7 +4333,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="69" customHeight="1">
+    <row r="43" ht="32" customHeight="1">
       <c r="A43" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4372,7 +4372,7 @@
       <c r="J43" s="1" t="inlineStr"/>
       <c r="K43" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R15#001；位置：L010-F001；源位置：1号炉炉左至炉右第10屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L43" s="1" t="inlineStr">
@@ -4425,7 +4425,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="69" customHeight="1">
+    <row r="44" ht="32" customHeight="1">
       <c r="A44" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4464,7 +4464,7 @@
       <c r="J44" s="1" t="inlineStr"/>
       <c r="K44" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R16#001；位置：L011-F001；源位置：1号炉炉左至炉右第11屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L44" s="1" t="inlineStr">
@@ -4517,7 +4517,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="69" customHeight="1">
+    <row r="45" ht="32" customHeight="1">
       <c r="A45" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4556,7 +4556,7 @@
       <c r="J45" s="1" t="inlineStr"/>
       <c r="K45" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R17#001；位置：L012-F001；源位置：1号炉炉左至炉右第12屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L45" s="1" t="inlineStr">
@@ -4609,7 +4609,7 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="69" customHeight="1">
+    <row r="46" ht="32" customHeight="1">
       <c r="A46" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4648,7 +4648,7 @@
       <c r="J46" s="1" t="inlineStr"/>
       <c r="K46" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R18#001；位置：L013-F001；源位置：1号炉炉左至炉右第13屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L46" s="1" t="inlineStr">
@@ -4701,7 +4701,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="69" customHeight="1">
+    <row r="47" ht="32" customHeight="1">
       <c r="A47" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4740,7 +4740,7 @@
       <c r="J47" s="1" t="inlineStr"/>
       <c r="K47" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R19#001；位置：L014-F001；源位置：1号炉炉左至炉右第14屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L47" s="1" t="inlineStr">
@@ -4793,7 +4793,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="69" customHeight="1">
+    <row r="48" ht="32" customHeight="1">
       <c r="A48" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4832,7 +4832,7 @@
       <c r="J48" s="1" t="inlineStr"/>
       <c r="K48" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R20#001；位置：L015-F001；源位置：1号炉炉左至炉右第15屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L48" s="1" t="inlineStr">
@@ -4885,7 +4885,7 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="69" customHeight="1">
+    <row r="49" ht="32" customHeight="1">
       <c r="A49" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4924,7 +4924,7 @@
       <c r="J49" s="1" t="inlineStr"/>
       <c r="K49" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R21#001；位置：L016-F001；源位置：1号炉炉左至炉右第16屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L49" s="1" t="inlineStr">
@@ -4977,7 +4977,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="69" customHeight="1">
+    <row r="50" ht="32" customHeight="1">
       <c r="A50" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5016,7 +5016,7 @@
       <c r="J50" s="1" t="inlineStr"/>
       <c r="K50" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R22#001；位置：L017-F001；源位置：1号炉炉左至炉右第17屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L50" s="1" t="inlineStr">
@@ -5069,7 +5069,7 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="69" customHeight="1">
+    <row r="51" ht="32" customHeight="1">
       <c r="A51" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5108,7 +5108,7 @@
       <c r="J51" s="1" t="inlineStr"/>
       <c r="K51" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R23#001；位置：L018-F001；源位置：1号炉炉左至炉右第18屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L51" s="1" t="inlineStr">
@@ -5161,7 +5161,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="69" customHeight="1">
+    <row r="52" ht="32" customHeight="1">
       <c r="A52" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5200,7 +5200,7 @@
       <c r="J52" s="1" t="inlineStr"/>
       <c r="K52" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R24#001；位置：L019-F001；源位置：1号炉炉左至炉右第19屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L52" s="1" t="inlineStr">
@@ -5253,7 +5253,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="69" customHeight="1">
+    <row r="53" ht="32" customHeight="1">
       <c r="A53" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5292,7 +5292,7 @@
       <c r="J53" s="1" t="inlineStr"/>
       <c r="K53" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R25#001；位置：L020-F001；源位置：1号炉炉左至炉右第20屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L53" s="1" t="inlineStr">
@@ -5345,7 +5345,7 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="69" customHeight="1">
+    <row r="54" ht="32" customHeight="1">
       <c r="A54" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5384,7 +5384,7 @@
       <c r="J54" s="1" t="inlineStr"/>
       <c r="K54" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R26#001；位置：L021-F001；源位置：1号炉炉左至炉右第21屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L54" s="1" t="inlineStr">
@@ -5437,7 +5437,7 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="69" customHeight="1">
+    <row r="55" ht="32" customHeight="1">
       <c r="A55" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5476,7 +5476,7 @@
       <c r="J55" s="1" t="inlineStr"/>
       <c r="K55" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R27#001；位置：L022-F001；源位置：1号炉炉左至炉右第22屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L55" s="1" t="inlineStr">
@@ -5529,7 +5529,7 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="69" customHeight="1">
+    <row r="56" ht="32" customHeight="1">
       <c r="A56" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5568,7 +5568,7 @@
       <c r="J56" s="1" t="inlineStr"/>
       <c r="K56" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R28#001；位置：L023-F001；源位置：1号炉炉左至炉右第23屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L56" s="1" t="inlineStr">
@@ -5621,7 +5621,7 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="69" customHeight="1">
+    <row r="57" ht="32" customHeight="1">
       <c r="A57" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5660,7 +5660,7 @@
       <c r="J57" s="1" t="inlineStr"/>
       <c r="K57" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R29#001；位置：L024-F001；源位置：1号炉炉左至炉右第24屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L57" s="1" t="inlineStr">
@@ -5713,7 +5713,7 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="69" customHeight="1">
+    <row r="58" ht="32" customHeight="1">
       <c r="A58" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5752,7 +5752,7 @@
       <c r="J58" s="1" t="inlineStr"/>
       <c r="K58" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R30#001；位置：L025-F001；源位置：1号炉炉左至炉右第25屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L58" s="1" t="inlineStr">
@@ -5805,7 +5805,7 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="69" customHeight="1">
+    <row r="59" ht="32" customHeight="1">
       <c r="A59" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5844,7 +5844,7 @@
       <c r="J59" s="1" t="inlineStr"/>
       <c r="K59" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R31#001；位置：L026-F001；源位置：1号炉炉左至炉右第26屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L59" s="1" t="inlineStr">
@@ -5897,7 +5897,7 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="88" customHeight="1">
+    <row r="60" ht="32" customHeight="1">
       <c r="A60" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5936,7 +5936,7 @@
       <c r="J60" s="1" t="inlineStr"/>
       <c r="K60" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R32#001；位置：L027-F001；源位置：1号炉炉左至炉右第24屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格；用户确认源表第32行“第24屏”实为第27屏（原表笔误），编码按L027修正</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L60" s="1" t="inlineStr">
@@ -5989,7 +5989,7 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="69" customHeight="1">
+    <row r="61" ht="32" customHeight="1">
       <c r="A61" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6028,7 +6028,7 @@
       <c r="J61" s="1" t="inlineStr"/>
       <c r="K61" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R33#001；位置：L028-F001；源位置：1号炉炉左至炉右第28屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L61" s="1" t="inlineStr">
@@ -6081,7 +6081,7 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="69" customHeight="1">
+    <row r="62" ht="32" customHeight="1">
       <c r="A62" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6120,7 +6120,7 @@
       <c r="J62" s="1" t="inlineStr"/>
       <c r="K62" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R34#001；位置：L029-F001；源位置：1号炉炉左至炉右第29屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L62" s="1" t="inlineStr">
@@ -6173,7 +6173,7 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="69" customHeight="1">
+    <row r="63" ht="32" customHeight="1">
       <c r="A63" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6212,7 +6212,7 @@
       <c r="J63" s="1" t="inlineStr"/>
       <c r="K63" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R35#001；位置：L030-F001；源位置：1号炉炉左至炉右第30屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L63" s="1" t="inlineStr">
@@ -6265,7 +6265,7 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="69" customHeight="1">
+    <row r="64" ht="32" customHeight="1">
       <c r="A64" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6304,7 +6304,7 @@
       <c r="J64" s="1" t="inlineStr"/>
       <c r="K64" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R36#001；位置：L031-F001；源位置：1号炉炉左至炉右第31屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L64" s="1" t="inlineStr">
@@ -6357,7 +6357,7 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="69" customHeight="1">
+    <row r="65" ht="32" customHeight="1">
       <c r="A65" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6396,7 +6396,7 @@
       <c r="J65" s="1" t="inlineStr"/>
       <c r="K65" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R37#001；位置：L032-F001；源位置：1号炉炉左至炉右第32屏炉前至炉后第1根；方法：射线；结果：合格；结果性质：原文合格</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L65" s="1" t="inlineStr">
@@ -6449,7 +6449,7 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="107" customHeight="1">
+    <row r="66" ht="32" customHeight="1">
       <c r="A66" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6488,7 +6488,7 @@
       <c r="J66" s="1" t="inlineStr"/>
       <c r="K66" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#001；位置：L001-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L66" s="1" t="inlineStr">
@@ -6537,7 +6537,7 @@
       </c>
       <c r="V66" s="1" t="inlineStr"/>
     </row>
-    <row r="67" ht="107" customHeight="1">
+    <row r="67" ht="32" customHeight="1">
       <c r="A67" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6576,7 +6576,7 @@
       <c r="J67" s="1" t="inlineStr"/>
       <c r="K67" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#002；位置：L001-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L67" s="1" t="inlineStr">
@@ -6625,7 +6625,7 @@
       </c>
       <c r="V67" s="1" t="inlineStr"/>
     </row>
-    <row r="68" ht="107" customHeight="1">
+    <row r="68" ht="32" customHeight="1">
       <c r="A68" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6664,7 +6664,7 @@
       <c r="J68" s="1" t="inlineStr"/>
       <c r="K68" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#003；位置：L002-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L68" s="1" t="inlineStr">
@@ -6713,7 +6713,7 @@
       </c>
       <c r="V68" s="1" t="inlineStr"/>
     </row>
-    <row r="69" ht="107" customHeight="1">
+    <row r="69" ht="32" customHeight="1">
       <c r="A69" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6752,7 +6752,7 @@
       <c r="J69" s="1" t="inlineStr"/>
       <c r="K69" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#004；位置：L002-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L69" s="1" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="V69" s="1" t="inlineStr"/>
     </row>
-    <row r="70" ht="107" customHeight="1">
+    <row r="70" ht="32" customHeight="1">
       <c r="A70" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6840,7 +6840,7 @@
       <c r="J70" s="1" t="inlineStr"/>
       <c r="K70" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#005；位置：L003-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L70" s="1" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="V70" s="1" t="inlineStr"/>
     </row>
-    <row r="71" ht="107" customHeight="1">
+    <row r="71" ht="32" customHeight="1">
       <c r="A71" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6928,7 +6928,7 @@
       <c r="J71" s="1" t="inlineStr"/>
       <c r="K71" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#006；位置：L003-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L71" s="1" t="inlineStr">
@@ -6977,7 +6977,7 @@
       </c>
       <c r="V71" s="1" t="inlineStr"/>
     </row>
-    <row r="72" ht="107" customHeight="1">
+    <row r="72" ht="32" customHeight="1">
       <c r="A72" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7016,7 +7016,7 @@
       <c r="J72" s="1" t="inlineStr"/>
       <c r="K72" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#007；位置：L004-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L72" s="1" t="inlineStr">
@@ -7065,7 +7065,7 @@
       </c>
       <c r="V72" s="1" t="inlineStr"/>
     </row>
-    <row r="73" ht="107" customHeight="1">
+    <row r="73" ht="50" customHeight="1">
       <c r="A73" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7104,7 +7104,7 @@
       <c r="J73" s="1" t="inlineStr"/>
       <c r="K73" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#008；位置：L004-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：发现异物，割开检查为氧化皮；结果性质：异常观察；仅转录异常观察，未新增质量合格/不合格判定或处置闭环；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：发现异物，割开检查为氧化皮</t>
         </is>
       </c>
       <c r="L73" s="1" t="inlineStr">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="107" customHeight="1">
+    <row r="74" ht="50" customHeight="1">
       <c r="A74" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7196,7 +7196,7 @@
       <c r="J74" s="1" t="inlineStr"/>
       <c r="K74" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#009；位置：L005-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：发现异物，割开检查为氧化皮；结果性质：异常观察；仅转录异常观察，未新增质量合格/不合格判定或处置闭环；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：发现异物，割开检查为氧化皮</t>
         </is>
       </c>
       <c r="L74" s="1" t="inlineStr">
@@ -7249,7 +7249,7 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="107" customHeight="1">
+    <row r="75" ht="32" customHeight="1">
       <c r="A75" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7288,7 +7288,7 @@
       <c r="J75" s="1" t="inlineStr"/>
       <c r="K75" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#010；位置：L005-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L75" s="1" t="inlineStr">
@@ -7337,7 +7337,7 @@
       </c>
       <c r="V75" s="1" t="inlineStr"/>
     </row>
-    <row r="76" ht="107" customHeight="1">
+    <row r="76" ht="32" customHeight="1">
       <c r="A76" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7376,7 +7376,7 @@
       <c r="J76" s="1" t="inlineStr"/>
       <c r="K76" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#011；位置：L006-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L76" s="1" t="inlineStr">
@@ -7425,7 +7425,7 @@
       </c>
       <c r="V76" s="1" t="inlineStr"/>
     </row>
-    <row r="77" ht="107" customHeight="1">
+    <row r="77" ht="32" customHeight="1">
       <c r="A77" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7464,7 +7464,7 @@
       <c r="J77" s="1" t="inlineStr"/>
       <c r="K77" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#012；位置：L006-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L77" s="1" t="inlineStr">
@@ -7513,7 +7513,7 @@
       </c>
       <c r="V77" s="1" t="inlineStr"/>
     </row>
-    <row r="78" ht="107" customHeight="1">
+    <row r="78" ht="32" customHeight="1">
       <c r="A78" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7552,7 +7552,7 @@
       <c r="J78" s="1" t="inlineStr"/>
       <c r="K78" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#013；位置：L007-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L78" s="1" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="V78" s="1" t="inlineStr"/>
     </row>
-    <row r="79" ht="107" customHeight="1">
+    <row r="79" ht="32" customHeight="1">
       <c r="A79" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7640,7 +7640,7 @@
       <c r="J79" s="1" t="inlineStr"/>
       <c r="K79" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#014；位置：L007-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L79" s="1" t="inlineStr">
@@ -7689,7 +7689,7 @@
       </c>
       <c r="V79" s="1" t="inlineStr"/>
     </row>
-    <row r="80" ht="107" customHeight="1">
+    <row r="80" ht="32" customHeight="1">
       <c r="A80" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7728,7 +7728,7 @@
       <c r="J80" s="1" t="inlineStr"/>
       <c r="K80" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#015；位置：L008-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L80" s="1" t="inlineStr">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="V80" s="1" t="inlineStr"/>
     </row>
-    <row r="81" ht="107" customHeight="1">
+    <row r="81" ht="32" customHeight="1">
       <c r="A81" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7816,7 +7816,7 @@
       <c r="J81" s="1" t="inlineStr"/>
       <c r="K81" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#016；位置：L008-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L81" s="1" t="inlineStr">
@@ -7865,7 +7865,7 @@
       </c>
       <c r="V81" s="1" t="inlineStr"/>
     </row>
-    <row r="82" ht="107" customHeight="1">
+    <row r="82" ht="32" customHeight="1">
       <c r="A82" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7904,7 +7904,7 @@
       <c r="J82" s="1" t="inlineStr"/>
       <c r="K82" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#017；位置：L009-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L82" s="1" t="inlineStr">
@@ -7953,7 +7953,7 @@
       </c>
       <c r="V82" s="1" t="inlineStr"/>
     </row>
-    <row r="83" ht="107" customHeight="1">
+    <row r="83" ht="32" customHeight="1">
       <c r="A83" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7992,7 +7992,7 @@
       <c r="J83" s="1" t="inlineStr"/>
       <c r="K83" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#018；位置：L009-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L83" s="1" t="inlineStr">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="V83" s="1" t="inlineStr"/>
     </row>
-    <row r="84" ht="107" customHeight="1">
+    <row r="84" ht="50" customHeight="1">
       <c r="A84" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8080,7 +8080,7 @@
       <c r="J84" s="1" t="inlineStr"/>
       <c r="K84" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#019；位置：L010-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：发现异物，割开检查为氧化皮；结果性质：异常观察；仅转录异常观察，未新增质量合格/不合格判定或处置闭环；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：发现异物，割开检查为氧化皮</t>
         </is>
       </c>
       <c r="L84" s="1" t="inlineStr">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
     </row>
-    <row r="85" ht="107" customHeight="1">
+    <row r="85" ht="32" customHeight="1">
       <c r="A85" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8172,7 +8172,7 @@
       <c r="J85" s="1" t="inlineStr"/>
       <c r="K85" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#020；位置：L010-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L85" s="1" t="inlineStr">
@@ -8221,7 +8221,7 @@
       </c>
       <c r="V85" s="1" t="inlineStr"/>
     </row>
-    <row r="86" ht="107" customHeight="1">
+    <row r="86" ht="32" customHeight="1">
       <c r="A86" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8260,7 +8260,7 @@
       <c r="J86" s="1" t="inlineStr"/>
       <c r="K86" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#021；位置：L011-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L86" s="1" t="inlineStr">
@@ -8309,7 +8309,7 @@
       </c>
       <c r="V86" s="1" t="inlineStr"/>
     </row>
-    <row r="87" ht="107" customHeight="1">
+    <row r="87" ht="32" customHeight="1">
       <c r="A87" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8348,7 +8348,7 @@
       <c r="J87" s="1" t="inlineStr"/>
       <c r="K87" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#022；位置：L011-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L87" s="1" t="inlineStr">
@@ -8397,7 +8397,7 @@
       </c>
       <c r="V87" s="1" t="inlineStr"/>
     </row>
-    <row r="88" ht="107" customHeight="1">
+    <row r="88" ht="32" customHeight="1">
       <c r="A88" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8436,7 +8436,7 @@
       <c r="J88" s="1" t="inlineStr"/>
       <c r="K88" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#023；位置：L012-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L88" s="1" t="inlineStr">
@@ -8485,7 +8485,7 @@
       </c>
       <c r="V88" s="1" t="inlineStr"/>
     </row>
-    <row r="89" ht="107" customHeight="1">
+    <row r="89" ht="32" customHeight="1">
       <c r="A89" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8524,7 +8524,7 @@
       <c r="J89" s="1" t="inlineStr"/>
       <c r="K89" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#024；位置：L012-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L89" s="1" t="inlineStr">
@@ -8573,7 +8573,7 @@
       </c>
       <c r="V89" s="1" t="inlineStr"/>
     </row>
-    <row r="90" ht="107" customHeight="1">
+    <row r="90" ht="50" customHeight="1">
       <c r="A90" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8612,7 +8612,7 @@
       <c r="J90" s="1" t="inlineStr"/>
       <c r="K90" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#025；位置：L013-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：发现异物，割开检查为氧化皮；结果性质：异常观察；仅转录异常观察，未新增质量合格/不合格判定或处置闭环；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：发现异物，割开检查为氧化皮</t>
         </is>
       </c>
       <c r="L90" s="1" t="inlineStr">
@@ -8665,7 +8665,7 @@
         </is>
       </c>
     </row>
-    <row r="91" ht="107" customHeight="1">
+    <row r="91" ht="32" customHeight="1">
       <c r="A91" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8704,7 +8704,7 @@
       <c r="J91" s="1" t="inlineStr"/>
       <c r="K91" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#026；位置：L013-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L91" s="1" t="inlineStr">
@@ -8753,7 +8753,7 @@
       </c>
       <c r="V91" s="1" t="inlineStr"/>
     </row>
-    <row r="92" ht="107" customHeight="1">
+    <row r="92" ht="32" customHeight="1">
       <c r="A92" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8792,7 +8792,7 @@
       <c r="J92" s="1" t="inlineStr"/>
       <c r="K92" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#027；位置：L014-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L92" s="1" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="V92" s="1" t="inlineStr"/>
     </row>
-    <row r="93" ht="107" customHeight="1">
+    <row r="93" ht="32" customHeight="1">
       <c r="A93" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8880,7 +8880,7 @@
       <c r="J93" s="1" t="inlineStr"/>
       <c r="K93" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#028；位置：L014-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L93" s="1" t="inlineStr">
@@ -8929,7 +8929,7 @@
       </c>
       <c r="V93" s="1" t="inlineStr"/>
     </row>
-    <row r="94" ht="107" customHeight="1">
+    <row r="94" ht="32" customHeight="1">
       <c r="A94" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8968,7 +8968,7 @@
       <c r="J94" s="1" t="inlineStr"/>
       <c r="K94" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#029；位置：L015-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L94" s="1" t="inlineStr">
@@ -9017,7 +9017,7 @@
       </c>
       <c r="V94" s="1" t="inlineStr"/>
     </row>
-    <row r="95" ht="107" customHeight="1">
+    <row r="95" ht="32" customHeight="1">
       <c r="A95" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9056,7 +9056,7 @@
       <c r="J95" s="1" t="inlineStr"/>
       <c r="K95" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#030；位置：L015-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L95" s="1" t="inlineStr">
@@ -9105,7 +9105,7 @@
       </c>
       <c r="V95" s="1" t="inlineStr"/>
     </row>
-    <row r="96" ht="107" customHeight="1">
+    <row r="96" ht="32" customHeight="1">
       <c r="A96" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9144,7 +9144,7 @@
       <c r="J96" s="1" t="inlineStr"/>
       <c r="K96" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#031；位置：L016-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L96" s="1" t="inlineStr">
@@ -9193,7 +9193,7 @@
       </c>
       <c r="V96" s="1" t="inlineStr"/>
     </row>
-    <row r="97" ht="107" customHeight="1">
+    <row r="97" ht="32" customHeight="1">
       <c r="A97" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9232,7 +9232,7 @@
       <c r="J97" s="1" t="inlineStr"/>
       <c r="K97" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#032；位置：L016-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L97" s="1" t="inlineStr">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="V97" s="1" t="inlineStr"/>
     </row>
-    <row r="98" ht="107" customHeight="1">
+    <row r="98" ht="32" customHeight="1">
       <c r="A98" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9320,7 +9320,7 @@
       <c r="J98" s="1" t="inlineStr"/>
       <c r="K98" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#033；位置：L017-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L98" s="1" t="inlineStr">
@@ -9369,7 +9369,7 @@
       </c>
       <c r="V98" s="1" t="inlineStr"/>
     </row>
-    <row r="99" ht="107" customHeight="1">
+    <row r="99" ht="32" customHeight="1">
       <c r="A99" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9408,7 +9408,7 @@
       <c r="J99" s="1" t="inlineStr"/>
       <c r="K99" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#034；位置：L017-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L99" s="1" t="inlineStr">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="V99" s="1" t="inlineStr"/>
     </row>
-    <row r="100" ht="107" customHeight="1">
+    <row r="100" ht="32" customHeight="1">
       <c r="A100" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9496,7 +9496,7 @@
       <c r="J100" s="1" t="inlineStr"/>
       <c r="K100" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#035；位置：L018-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L100" s="1" t="inlineStr">
@@ -9545,7 +9545,7 @@
       </c>
       <c r="V100" s="1" t="inlineStr"/>
     </row>
-    <row r="101" ht="107" customHeight="1">
+    <row r="101" ht="32" customHeight="1">
       <c r="A101" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9584,7 +9584,7 @@
       <c r="J101" s="1" t="inlineStr"/>
       <c r="K101" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#036；位置：L018-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L101" s="1" t="inlineStr">
@@ -9633,7 +9633,7 @@
       </c>
       <c r="V101" s="1" t="inlineStr"/>
     </row>
-    <row r="102" ht="107" customHeight="1">
+    <row r="102" ht="32" customHeight="1">
       <c r="A102" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9672,7 +9672,7 @@
       <c r="J102" s="1" t="inlineStr"/>
       <c r="K102" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#037；位置：L019-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L102" s="1" t="inlineStr">
@@ -9721,7 +9721,7 @@
       </c>
       <c r="V102" s="1" t="inlineStr"/>
     </row>
-    <row r="103" ht="107" customHeight="1">
+    <row r="103" ht="32" customHeight="1">
       <c r="A103" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9760,7 +9760,7 @@
       <c r="J103" s="1" t="inlineStr"/>
       <c r="K103" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#038；位置：L019-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L103" s="1" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="V103" s="1" t="inlineStr"/>
     </row>
-    <row r="104" ht="107" customHeight="1">
+    <row r="104" ht="32" customHeight="1">
       <c r="A104" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9848,7 +9848,7 @@
       <c r="J104" s="1" t="inlineStr"/>
       <c r="K104" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#039；位置：L020-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L104" s="1" t="inlineStr">
@@ -9897,7 +9897,7 @@
       </c>
       <c r="V104" s="1" t="inlineStr"/>
     </row>
-    <row r="105" ht="107" customHeight="1">
+    <row r="105" ht="32" customHeight="1">
       <c r="A105" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -9936,7 +9936,7 @@
       <c r="J105" s="1" t="inlineStr"/>
       <c r="K105" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#040；位置：L020-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L105" s="1" t="inlineStr">
@@ -9985,7 +9985,7 @@
       </c>
       <c r="V105" s="1" t="inlineStr"/>
     </row>
-    <row r="106" ht="107" customHeight="1">
+    <row r="106" ht="32" customHeight="1">
       <c r="A106" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10024,7 +10024,7 @@
       <c r="J106" s="1" t="inlineStr"/>
       <c r="K106" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#041；位置：L021-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L106" s="1" t="inlineStr">
@@ -10073,7 +10073,7 @@
       </c>
       <c r="V106" s="1" t="inlineStr"/>
     </row>
-    <row r="107" ht="107" customHeight="1">
+    <row r="107" ht="32" customHeight="1">
       <c r="A107" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10112,7 +10112,7 @@
       <c r="J107" s="1" t="inlineStr"/>
       <c r="K107" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#042；位置：L021-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L107" s="1" t="inlineStr">
@@ -10161,7 +10161,7 @@
       </c>
       <c r="V107" s="1" t="inlineStr"/>
     </row>
-    <row r="108" ht="107" customHeight="1">
+    <row r="108" ht="32" customHeight="1">
       <c r="A108" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10200,7 +10200,7 @@
       <c r="J108" s="1" t="inlineStr"/>
       <c r="K108" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#043；位置：L022-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L108" s="1" t="inlineStr">
@@ -10249,7 +10249,7 @@
       </c>
       <c r="V108" s="1" t="inlineStr"/>
     </row>
-    <row r="109" ht="107" customHeight="1">
+    <row r="109" ht="32" customHeight="1">
       <c r="A109" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10288,7 +10288,7 @@
       <c r="J109" s="1" t="inlineStr"/>
       <c r="K109" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#044；位置：L022-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L109" s="1" t="inlineStr">
@@ -10337,7 +10337,7 @@
       </c>
       <c r="V109" s="1" t="inlineStr"/>
     </row>
-    <row r="110" ht="107" customHeight="1">
+    <row r="110" ht="32" customHeight="1">
       <c r="A110" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10376,7 +10376,7 @@
       <c r="J110" s="1" t="inlineStr"/>
       <c r="K110" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#045；位置：L023-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L110" s="1" t="inlineStr">
@@ -10425,7 +10425,7 @@
       </c>
       <c r="V110" s="1" t="inlineStr"/>
     </row>
-    <row r="111" ht="107" customHeight="1">
+    <row r="111" ht="32" customHeight="1">
       <c r="A111" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10464,7 +10464,7 @@
       <c r="J111" s="1" t="inlineStr"/>
       <c r="K111" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#046；位置：L023-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L111" s="1" t="inlineStr">
@@ -10513,7 +10513,7 @@
       </c>
       <c r="V111" s="1" t="inlineStr"/>
     </row>
-    <row r="112" ht="107" customHeight="1">
+    <row r="112" ht="32" customHeight="1">
       <c r="A112" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10552,7 +10552,7 @@
       <c r="J112" s="1" t="inlineStr"/>
       <c r="K112" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#047；位置：L024-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L112" s="1" t="inlineStr">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="V112" s="1" t="inlineStr"/>
     </row>
-    <row r="113" ht="107" customHeight="1">
+    <row r="113" ht="32" customHeight="1">
       <c r="A113" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10640,7 +10640,7 @@
       <c r="J113" s="1" t="inlineStr"/>
       <c r="K113" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#048；位置：L024-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L113" s="1" t="inlineStr">
@@ -10689,7 +10689,7 @@
       </c>
       <c r="V113" s="1" t="inlineStr"/>
     </row>
-    <row r="114" ht="107" customHeight="1">
+    <row r="114" ht="50" customHeight="1">
       <c r="A114" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10728,7 +10728,7 @@
       <c r="J114" s="1" t="inlineStr"/>
       <c r="K114" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#049；位置：L025-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：发现异物，割开检查为氧化皮；结果性质：异常观察；仅转录异常观察，未新增质量合格/不合格判定或处置闭环；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：发现异物，割开检查为氧化皮</t>
         </is>
       </c>
       <c r="L114" s="1" t="inlineStr">
@@ -10781,7 +10781,7 @@
         </is>
       </c>
     </row>
-    <row r="115" ht="107" customHeight="1">
+    <row r="115" ht="32" customHeight="1">
       <c r="A115" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10820,7 +10820,7 @@
       <c r="J115" s="1" t="inlineStr"/>
       <c r="K115" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#050；位置：L025-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L115" s="1" t="inlineStr">
@@ -10869,7 +10869,7 @@
       </c>
       <c r="V115" s="1" t="inlineStr"/>
     </row>
-    <row r="116" ht="107" customHeight="1">
+    <row r="116" ht="32" customHeight="1">
       <c r="A116" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10908,7 +10908,7 @@
       <c r="J116" s="1" t="inlineStr"/>
       <c r="K116" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#051；位置：L026-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L116" s="1" t="inlineStr">
@@ -10957,7 +10957,7 @@
       </c>
       <c r="V116" s="1" t="inlineStr"/>
     </row>
-    <row r="117" ht="107" customHeight="1">
+    <row r="117" ht="32" customHeight="1">
       <c r="A117" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -10996,7 +10996,7 @@
       <c r="J117" s="1" t="inlineStr"/>
       <c r="K117" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#052；位置：L026-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L117" s="1" t="inlineStr">
@@ -11045,7 +11045,7 @@
       </c>
       <c r="V117" s="1" t="inlineStr"/>
     </row>
-    <row r="118" ht="107" customHeight="1">
+    <row r="118" ht="32" customHeight="1">
       <c r="A118" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11084,7 +11084,7 @@
       <c r="J118" s="1" t="inlineStr"/>
       <c r="K118" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#053；位置：L027-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L118" s="1" t="inlineStr">
@@ -11133,7 +11133,7 @@
       </c>
       <c r="V118" s="1" t="inlineStr"/>
     </row>
-    <row r="119" ht="107" customHeight="1">
+    <row r="119" ht="32" customHeight="1">
       <c r="A119" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11172,7 +11172,7 @@
       <c r="J119" s="1" t="inlineStr"/>
       <c r="K119" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#054；位置：L027-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L119" s="1" t="inlineStr">
@@ -11221,7 +11221,7 @@
       </c>
       <c r="V119" s="1" t="inlineStr"/>
     </row>
-    <row r="120" ht="107" customHeight="1">
+    <row r="120" ht="32" customHeight="1">
       <c r="A120" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11260,7 +11260,7 @@
       <c r="J120" s="1" t="inlineStr"/>
       <c r="K120" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#055；位置：L028-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L120" s="1" t="inlineStr">
@@ -11309,7 +11309,7 @@
       </c>
       <c r="V120" s="1" t="inlineStr"/>
     </row>
-    <row r="121" ht="107" customHeight="1">
+    <row r="121" ht="32" customHeight="1">
       <c r="A121" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11348,7 +11348,7 @@
       <c r="J121" s="1" t="inlineStr"/>
       <c r="K121" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#056；位置：L028-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L121" s="1" t="inlineStr">
@@ -11397,7 +11397,7 @@
       </c>
       <c r="V121" s="1" t="inlineStr"/>
     </row>
-    <row r="122" ht="107" customHeight="1">
+    <row r="122" ht="32" customHeight="1">
       <c r="A122" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11436,7 +11436,7 @@
       <c r="J122" s="1" t="inlineStr"/>
       <c r="K122" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#057；位置：L029-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L122" s="1" t="inlineStr">
@@ -11485,7 +11485,7 @@
       </c>
       <c r="V122" s="1" t="inlineStr"/>
     </row>
-    <row r="123" ht="107" customHeight="1">
+    <row r="123" ht="32" customHeight="1">
       <c r="A123" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11524,7 +11524,7 @@
       <c r="J123" s="1" t="inlineStr"/>
       <c r="K123" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#058；位置：L029-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L123" s="1" t="inlineStr">
@@ -11573,7 +11573,7 @@
       </c>
       <c r="V123" s="1" t="inlineStr"/>
     </row>
-    <row r="124" ht="107" customHeight="1">
+    <row r="124" ht="32" customHeight="1">
       <c r="A124" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11612,7 +11612,7 @@
       <c r="J124" s="1" t="inlineStr"/>
       <c r="K124" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#059；位置：L030-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L124" s="1" t="inlineStr">
@@ -11661,7 +11661,7 @@
       </c>
       <c r="V124" s="1" t="inlineStr"/>
     </row>
-    <row r="125" ht="107" customHeight="1">
+    <row r="125" ht="32" customHeight="1">
       <c r="A125" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11700,7 +11700,7 @@
       <c r="J125" s="1" t="inlineStr"/>
       <c r="K125" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#060；位置：L030-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L125" s="1" t="inlineStr">
@@ -11749,7 +11749,7 @@
       </c>
       <c r="V125" s="1" t="inlineStr"/>
     </row>
-    <row r="126" ht="107" customHeight="1">
+    <row r="126" ht="32" customHeight="1">
       <c r="A126" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11788,7 +11788,7 @@
       <c r="J126" s="1" t="inlineStr"/>
       <c r="K126" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#061；位置：L031-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L126" s="1" t="inlineStr">
@@ -11837,7 +11837,7 @@
       </c>
       <c r="V126" s="1" t="inlineStr"/>
     </row>
-    <row r="127" ht="107" customHeight="1">
+    <row r="127" ht="32" customHeight="1">
       <c r="A127" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11876,7 +11876,7 @@
       <c r="J127" s="1" t="inlineStr"/>
       <c r="K127" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#062；位置：L031-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L127" s="1" t="inlineStr">
@@ -11925,7 +11925,7 @@
       </c>
       <c r="V127" s="1" t="inlineStr"/>
     </row>
-    <row r="128" ht="107" customHeight="1">
+    <row r="128" ht="32" customHeight="1">
       <c r="A128" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -11964,7 +11964,7 @@
       <c r="J128" s="1" t="inlineStr"/>
       <c r="K128" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#063；位置：L032-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L128" s="1" t="inlineStr">
@@ -12013,7 +12013,7 @@
       </c>
       <c r="V128" s="1" t="inlineStr"/>
     </row>
-    <row r="129" ht="107" customHeight="1">
+    <row r="129" ht="32" customHeight="1">
       <c r="A129" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -12052,7 +12052,7 @@
       <c r="J129" s="1" t="inlineStr"/>
       <c r="K129" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#064；位置：L032-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L129" s="1" t="inlineStr">
@@ -12101,7 +12101,7 @@
       </c>
       <c r="V129" s="1" t="inlineStr"/>
     </row>
-    <row r="130" ht="107" customHeight="1">
+    <row r="130" ht="32" customHeight="1">
       <c r="A130" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -12140,7 +12140,7 @@
       <c r="J130" s="1" t="inlineStr"/>
       <c r="K130" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#001；位置：L001-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L130" s="1" t="inlineStr">
@@ -12189,7 +12189,7 @@
       </c>
       <c r="V130" s="1" t="inlineStr"/>
     </row>
-    <row r="131" ht="107" customHeight="1">
+    <row r="131" ht="32" customHeight="1">
       <c r="A131" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -12228,7 +12228,7 @@
       <c r="J131" s="1" t="inlineStr"/>
       <c r="K131" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#002；位置：L002-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L131" s="1" t="inlineStr">
@@ -12277,7 +12277,7 @@
       </c>
       <c r="V131" s="1" t="inlineStr"/>
     </row>
-    <row r="132" ht="107" customHeight="1">
+    <row r="132" ht="32" customHeight="1">
       <c r="A132" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -12316,7 +12316,7 @@
       <c r="J132" s="1" t="inlineStr"/>
       <c r="K132" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#003；位置：L003-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L132" s="1" t="inlineStr">
@@ -12365,7 +12365,7 @@
       </c>
       <c r="V132" s="1" t="inlineStr"/>
     </row>
-    <row r="133" ht="107" customHeight="1">
+    <row r="133" ht="32" customHeight="1">
       <c r="A133" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -12404,7 +12404,7 @@
       <c r="J133" s="1" t="inlineStr"/>
       <c r="K133" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#004；位置：L004-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L133" s="1" t="inlineStr">
@@ -12453,7 +12453,7 @@
       </c>
       <c r="V133" s="1" t="inlineStr"/>
     </row>
-    <row r="134" ht="107" customHeight="1">
+    <row r="134" ht="32" customHeight="1">
       <c r="A134" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -12492,7 +12492,7 @@
       <c r="J134" s="1" t="inlineStr"/>
       <c r="K134" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#005；位置：L005-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L134" s="1" t="inlineStr">
@@ -12541,7 +12541,7 @@
       </c>
       <c r="V134" s="1" t="inlineStr"/>
     </row>
-    <row r="135" ht="107" customHeight="1">
+    <row r="135" ht="32" customHeight="1">
       <c r="A135" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -12580,7 +12580,7 @@
       <c r="J135" s="1" t="inlineStr"/>
       <c r="K135" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#006；位置：L006-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L135" s="1" t="inlineStr">
@@ -12629,7 +12629,7 @@
       </c>
       <c r="V135" s="1" t="inlineStr"/>
     </row>
-    <row r="136" ht="107" customHeight="1">
+    <row r="136" ht="32" customHeight="1">
       <c r="A136" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -12668,7 +12668,7 @@
       <c r="J136" s="1" t="inlineStr"/>
       <c r="K136" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#007；位置：L007-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L136" s="1" t="inlineStr">
@@ -12717,7 +12717,7 @@
       </c>
       <c r="V136" s="1" t="inlineStr"/>
     </row>
-    <row r="137" ht="107" customHeight="1">
+    <row r="137" ht="32" customHeight="1">
       <c r="A137" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -12756,7 +12756,7 @@
       <c r="J137" s="1" t="inlineStr"/>
       <c r="K137" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#008；位置：L008-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L137" s="1" t="inlineStr">
@@ -12805,7 +12805,7 @@
       </c>
       <c r="V137" s="1" t="inlineStr"/>
     </row>
-    <row r="138" ht="107" customHeight="1">
+    <row r="138" ht="32" customHeight="1">
       <c r="A138" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -12844,7 +12844,7 @@
       <c r="J138" s="1" t="inlineStr"/>
       <c r="K138" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#009；位置：L009-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L138" s="1" t="inlineStr">
@@ -12893,7 +12893,7 @@
       </c>
       <c r="V138" s="1" t="inlineStr"/>
     </row>
-    <row r="139" ht="107" customHeight="1">
+    <row r="139" ht="32" customHeight="1">
       <c r="A139" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -12932,7 +12932,7 @@
       <c r="J139" s="1" t="inlineStr"/>
       <c r="K139" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#010；位置：L010-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L139" s="1" t="inlineStr">
@@ -12981,7 +12981,7 @@
       </c>
       <c r="V139" s="1" t="inlineStr"/>
     </row>
-    <row r="140" ht="107" customHeight="1">
+    <row r="140" ht="32" customHeight="1">
       <c r="A140" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -13020,7 +13020,7 @@
       <c r="J140" s="1" t="inlineStr"/>
       <c r="K140" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#011；位置：L011-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L140" s="1" t="inlineStr">
@@ -13069,7 +13069,7 @@
       </c>
       <c r="V140" s="1" t="inlineStr"/>
     </row>
-    <row r="141" ht="107" customHeight="1">
+    <row r="141" ht="32" customHeight="1">
       <c r="A141" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -13108,7 +13108,7 @@
       <c r="J141" s="1" t="inlineStr"/>
       <c r="K141" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#012；位置：L012-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L141" s="1" t="inlineStr">
@@ -13157,7 +13157,7 @@
       </c>
       <c r="V141" s="1" t="inlineStr"/>
     </row>
-    <row r="142" ht="107" customHeight="1">
+    <row r="142" ht="32" customHeight="1">
       <c r="A142" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -13196,7 +13196,7 @@
       <c r="J142" s="1" t="inlineStr"/>
       <c r="K142" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#013；位置：L013-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L142" s="1" t="inlineStr">
@@ -13245,7 +13245,7 @@
       </c>
       <c r="V142" s="1" t="inlineStr"/>
     </row>
-    <row r="143" ht="107" customHeight="1">
+    <row r="143" ht="32" customHeight="1">
       <c r="A143" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -13284,7 +13284,7 @@
       <c r="J143" s="1" t="inlineStr"/>
       <c r="K143" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#014；位置：L014-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L143" s="1" t="inlineStr">
@@ -13333,7 +13333,7 @@
       </c>
       <c r="V143" s="1" t="inlineStr"/>
     </row>
-    <row r="144" ht="107" customHeight="1">
+    <row r="144" ht="32" customHeight="1">
       <c r="A144" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -13372,7 +13372,7 @@
       <c r="J144" s="1" t="inlineStr"/>
       <c r="K144" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#015；位置：L015-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L144" s="1" t="inlineStr">
@@ -13421,7 +13421,7 @@
       </c>
       <c r="V144" s="1" t="inlineStr"/>
     </row>
-    <row r="145" ht="107" customHeight="1">
+    <row r="145" ht="32" customHeight="1">
       <c r="A145" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -13460,7 +13460,7 @@
       <c r="J145" s="1" t="inlineStr"/>
       <c r="K145" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#016；位置：L016-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L145" s="1" t="inlineStr">
@@ -13509,7 +13509,7 @@
       </c>
       <c r="V145" s="1" t="inlineStr"/>
     </row>
-    <row r="146" ht="107" customHeight="1">
+    <row r="146" ht="32" customHeight="1">
       <c r="A146" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -13548,7 +13548,7 @@
       <c r="J146" s="1" t="inlineStr"/>
       <c r="K146" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#017；位置：L017-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L146" s="1" t="inlineStr">
@@ -13597,7 +13597,7 @@
       </c>
       <c r="V146" s="1" t="inlineStr"/>
     </row>
-    <row r="147" ht="107" customHeight="1">
+    <row r="147" ht="32" customHeight="1">
       <c r="A147" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -13636,7 +13636,7 @@
       <c r="J147" s="1" t="inlineStr"/>
       <c r="K147" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#018；位置：L018-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L147" s="1" t="inlineStr">
@@ -13685,7 +13685,7 @@
       </c>
       <c r="V147" s="1" t="inlineStr"/>
     </row>
-    <row r="148" ht="107" customHeight="1">
+    <row r="148" ht="32" customHeight="1">
       <c r="A148" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -13724,7 +13724,7 @@
       <c r="J148" s="1" t="inlineStr"/>
       <c r="K148" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#019；位置：L019-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L148" s="1" t="inlineStr">
@@ -13773,7 +13773,7 @@
       </c>
       <c r="V148" s="1" t="inlineStr"/>
     </row>
-    <row r="149" ht="107" customHeight="1">
+    <row r="149" ht="32" customHeight="1">
       <c r="A149" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -13812,7 +13812,7 @@
       <c r="J149" s="1" t="inlineStr"/>
       <c r="K149" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#020；位置：L020-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L149" s="1" t="inlineStr">
@@ -13861,7 +13861,7 @@
       </c>
       <c r="V149" s="1" t="inlineStr"/>
     </row>
-    <row r="150" ht="107" customHeight="1">
+    <row r="150" ht="32" customHeight="1">
       <c r="A150" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -13900,7 +13900,7 @@
       <c r="J150" s="1" t="inlineStr"/>
       <c r="K150" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#021；位置：L021-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L150" s="1" t="inlineStr">
@@ -13949,7 +13949,7 @@
       </c>
       <c r="V150" s="1" t="inlineStr"/>
     </row>
-    <row r="151" ht="107" customHeight="1">
+    <row r="151" ht="32" customHeight="1">
       <c r="A151" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -13988,7 +13988,7 @@
       <c r="J151" s="1" t="inlineStr"/>
       <c r="K151" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#022；位置：L022-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L151" s="1" t="inlineStr">
@@ -14037,7 +14037,7 @@
       </c>
       <c r="V151" s="1" t="inlineStr"/>
     </row>
-    <row r="152" ht="107" customHeight="1">
+    <row r="152" ht="32" customHeight="1">
       <c r="A152" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -14076,7 +14076,7 @@
       <c r="J152" s="1" t="inlineStr"/>
       <c r="K152" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#023；位置：L023-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L152" s="1" t="inlineStr">
@@ -14125,7 +14125,7 @@
       </c>
       <c r="V152" s="1" t="inlineStr"/>
     </row>
-    <row r="153" ht="107" customHeight="1">
+    <row r="153" ht="32" customHeight="1">
       <c r="A153" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -14164,7 +14164,7 @@
       <c r="J153" s="1" t="inlineStr"/>
       <c r="K153" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#024；位置：L024-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L153" s="1" t="inlineStr">
@@ -14213,7 +14213,7 @@
       </c>
       <c r="V153" s="1" t="inlineStr"/>
     </row>
-    <row r="154" ht="107" customHeight="1">
+    <row r="154" ht="32" customHeight="1">
       <c r="A154" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -14252,7 +14252,7 @@
       <c r="J154" s="1" t="inlineStr"/>
       <c r="K154" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#025；位置：L025-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L154" s="1" t="inlineStr">
@@ -14301,7 +14301,7 @@
       </c>
       <c r="V154" s="1" t="inlineStr"/>
     </row>
-    <row r="155" ht="107" customHeight="1">
+    <row r="155" ht="32" customHeight="1">
       <c r="A155" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -14340,7 +14340,7 @@
       <c r="J155" s="1" t="inlineStr"/>
       <c r="K155" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#026；位置：L026-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L155" s="1" t="inlineStr">
@@ -14389,7 +14389,7 @@
       </c>
       <c r="V155" s="1" t="inlineStr"/>
     </row>
-    <row r="156" ht="107" customHeight="1">
+    <row r="156" ht="32" customHeight="1">
       <c r="A156" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -14428,7 +14428,7 @@
       <c r="J156" s="1" t="inlineStr"/>
       <c r="K156" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#027；位置：L027-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L156" s="1" t="inlineStr">
@@ -14477,7 +14477,7 @@
       </c>
       <c r="V156" s="1" t="inlineStr"/>
     </row>
-    <row r="157" ht="107" customHeight="1">
+    <row r="157" ht="32" customHeight="1">
       <c r="A157" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -14516,7 +14516,7 @@
       <c r="J157" s="1" t="inlineStr"/>
       <c r="K157" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#028；位置：L028-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L157" s="1" t="inlineStr">
@@ -14565,7 +14565,7 @@
       </c>
       <c r="V157" s="1" t="inlineStr"/>
     </row>
-    <row r="158" ht="107" customHeight="1">
+    <row r="158" ht="32" customHeight="1">
       <c r="A158" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -14604,7 +14604,7 @@
       <c r="J158" s="1" t="inlineStr"/>
       <c r="K158" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#029；位置：L029-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L158" s="1" t="inlineStr">
@@ -14653,7 +14653,7 @@
       </c>
       <c r="V158" s="1" t="inlineStr"/>
     </row>
-    <row r="159" ht="107" customHeight="1">
+    <row r="159" ht="32" customHeight="1">
       <c r="A159" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -14692,7 +14692,7 @@
       <c r="J159" s="1" t="inlineStr"/>
       <c r="K159" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#030；位置：L030-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L159" s="1" t="inlineStr">
@@ -14741,7 +14741,7 @@
       </c>
       <c r="V159" s="1" t="inlineStr"/>
     </row>
-    <row r="160" ht="107" customHeight="1">
+    <row r="160" ht="32" customHeight="1">
       <c r="A160" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -14780,7 +14780,7 @@
       <c r="J160" s="1" t="inlineStr"/>
       <c r="K160" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#031；位置：L031-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L160" s="1" t="inlineStr">
@@ -14829,7 +14829,7 @@
       </c>
       <c r="V160" s="1" t="inlineStr"/>
     </row>
-    <row r="161" ht="107" customHeight="1">
+    <row r="161" ht="32" customHeight="1">
       <c r="A161" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -14868,7 +14868,7 @@
       <c r="J161" s="1" t="inlineStr"/>
       <c r="K161" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#032；位置：L032-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L161" s="1" t="inlineStr">
